--- a/down.xlsx
+++ b/down.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G150"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -431,19 +431,19 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Pnb Housing Finance Limited</v>
+        <v>Delhivery Ltd</v>
       </c>
       <c r="C2" t="str">
-        <v>PNBHOUSING</v>
+        <v>DELHIVERY</v>
       </c>
       <c r="D2" s="1">
-        <v>1200.3</v>
+        <v>420.75</v>
       </c>
       <c r="E2" s="2">
-        <v>3.65</v>
+        <v>5.06</v>
       </c>
       <c r="F2" s="1">
-        <v>601702</v>
+        <v>5183677</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -454,19 +454,19 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Angel One Ltd</v>
+        <v>Suzlon Energy Limited</v>
       </c>
       <c r="C3" t="str">
-        <v>ANGELONE</v>
+        <v>SUZLON</v>
       </c>
       <c r="D3" s="1">
-        <v>302.2</v>
+        <v>39.17</v>
       </c>
       <c r="E3" s="2">
-        <v>3.49</v>
+        <v>4.18</v>
       </c>
       <c r="F3" s="1">
-        <v>2969372</v>
+        <v>62356958</v>
       </c>
       <c r="G3" t="str">
         <v/>
@@ -477,19 +477,19 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Siemens Limited</v>
+        <v>Tata Elxsi Limited</v>
       </c>
       <c r="C4" t="str">
-        <v>SIEMENS</v>
+        <v>TATAELXSI</v>
       </c>
       <c r="D4" s="1">
-        <v>3704.7</v>
+        <v>3251.9</v>
       </c>
       <c r="E4" s="2">
-        <v>3.05</v>
+        <v>3.89</v>
       </c>
       <c r="F4" s="1">
-        <v>99287</v>
+        <v>389873</v>
       </c>
       <c r="G4" t="str">
         <v/>
@@ -500,19 +500,19 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Abb India Limited</v>
+        <v>Indian Railway Finance Corporation Ltd</v>
       </c>
       <c r="C5" t="str">
-        <v>ABB</v>
+        <v>IRFC</v>
       </c>
       <c r="D5" s="1">
-        <v>6956</v>
+        <v>77.2</v>
       </c>
       <c r="E5" s="2">
-        <v>2.6</v>
+        <v>3.35</v>
       </c>
       <c r="F5" s="1">
-        <v>79378</v>
+        <v>7531260</v>
       </c>
       <c r="G5" t="str">
         <v/>
@@ -523,19 +523,19 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Polycab India Ltd</v>
+        <v>Bajaj Auto Limited</v>
       </c>
       <c r="C6" t="str">
-        <v>POLYCAB</v>
+        <v>BAJAJ-AUTO</v>
       </c>
       <c r="D6" s="1">
-        <v>8458.5</v>
+        <v>10080</v>
       </c>
       <c r="E6" s="2">
-        <v>2.47</v>
+        <v>3.09</v>
       </c>
       <c r="F6" s="1">
-        <v>184170</v>
+        <v>182806</v>
       </c>
       <c r="G6" t="str">
         <v/>
@@ -546,19 +546,19 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Motilal Oswal Financial Services Limited</v>
+        <v>Tube Investments of India Ltd</v>
       </c>
       <c r="C7" t="str">
-        <v>MOTILALOFS</v>
+        <v>TIINDIA</v>
       </c>
       <c r="D7" s="1">
-        <v>1050</v>
+        <v>2278.3</v>
       </c>
       <c r="E7" s="2">
-        <v>2.34</v>
+        <v>2.95</v>
       </c>
       <c r="F7" s="1">
-        <v>313210</v>
+        <v>254201</v>
       </c>
       <c r="G7" t="str">
         <v/>
@@ -569,19 +569,19 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Hitachi Energy India Ltd</v>
+        <v>Mazagon Dock Shipbuilders Ltd</v>
       </c>
       <c r="C8" t="str">
-        <v>POWERINDIA</v>
+        <v>MAZDOCK</v>
       </c>
       <c r="D8" s="1">
-        <v>31315</v>
+        <v>2064</v>
       </c>
       <c r="E8" s="2">
-        <v>2.32</v>
+        <v>2.69</v>
       </c>
       <c r="F8" s="1">
-        <v>30986</v>
+        <v>347192</v>
       </c>
       <c r="G8" t="str">
         <v/>
@@ -592,19 +592,19 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>Hindustan Aeronautics Ltd</v>
+        <v>PB Fintech Ltd</v>
       </c>
       <c r="C9" t="str">
-        <v>HAL</v>
+        <v>POLICYBZR</v>
       </c>
       <c r="D9" s="1">
-        <v>4758.5</v>
+        <v>1037</v>
       </c>
       <c r="E9" s="2">
-        <v>2.21</v>
+        <v>2.47</v>
       </c>
       <c r="F9" s="1">
-        <v>125189</v>
+        <v>709680</v>
       </c>
       <c r="G9" t="str">
         <v/>
@@ -615,19 +615,19 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Ujjivan Small Finance Bank Ltd</v>
+        <v>Nbcc (india) Limited</v>
       </c>
       <c r="C10" t="str">
-        <v>UJJIVANSFB</v>
+        <v>NBCC</v>
       </c>
       <c r="D10" s="1">
-        <v>62.64</v>
+        <v>76.3</v>
       </c>
       <c r="E10" s="2">
-        <v>1.94</v>
+        <v>2.47</v>
       </c>
       <c r="F10" s="1">
-        <v>8107061</v>
+        <v>2884837</v>
       </c>
       <c r="G10" t="str">
         <v/>
@@ -638,19 +638,19 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Apl Apollo Tubes Limited</v>
+        <v>Dr. Reddy's Laboratories Limited</v>
       </c>
       <c r="C11" t="str">
-        <v>APLAPOLLO</v>
+        <v>DRREDDY</v>
       </c>
       <c r="D11" s="1">
-        <v>2152.9</v>
+        <v>1223.6</v>
       </c>
       <c r="E11" s="2">
-        <v>1.84</v>
+        <v>2.22</v>
       </c>
       <c r="F11" s="1">
-        <v>67227</v>
+        <v>364106</v>
       </c>
       <c r="G11" t="str">
         <v/>
@@ -661,19 +661,19 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>GE Vernova T&amp;D India Ltd</v>
+        <v>Rail Vikas Nigam Ltd</v>
       </c>
       <c r="C12" t="str">
-        <v>GVT&amp;D</v>
+        <v>RVNL</v>
       </c>
       <c r="D12" s="1">
-        <v>4271.3</v>
+        <v>194.5</v>
       </c>
       <c r="E12" s="2">
-        <v>1.83</v>
+        <v>2.02</v>
       </c>
       <c r="F12" s="1">
-        <v>78716</v>
+        <v>1928951</v>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -684,19 +684,19 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Tvs Motor Company Limited</v>
+        <v>Kei Industries Limited</v>
       </c>
       <c r="C13" t="str">
-        <v>TVSMOTOR</v>
+        <v>KEI</v>
       </c>
       <c r="D13" s="1">
-        <v>3937.4</v>
+        <v>4674.5</v>
       </c>
       <c r="E13" s="2">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="F13" s="1">
-        <v>261706</v>
+        <v>96397</v>
       </c>
       <c r="G13" t="str">
         <v/>
@@ -707,19 +707,19 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Ather Energy Ltd</v>
+        <v>Hindustan Petroleum Corporation Limited</v>
       </c>
       <c r="C14" t="str">
-        <v>ATHERENERG</v>
+        <v>HINDPETRO</v>
       </c>
       <c r="D14" s="1">
-        <v>1456.5</v>
+        <v>332.3</v>
       </c>
       <c r="E14" s="2">
-        <v>1.54</v>
+        <v>1.93</v>
       </c>
       <c r="F14" s="1">
-        <v>1389407</v>
+        <v>1219737</v>
       </c>
       <c r="G14" t="str">
         <v/>
@@ -730,19 +730,19 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Manappuram Finance Limited</v>
+        <v>Astral Ltd</v>
       </c>
       <c r="C15" t="str">
-        <v>MANAPPURAM</v>
+        <v>ASTRAL</v>
       </c>
       <c r="D15" s="1">
-        <v>319.3</v>
+        <v>1435.9</v>
       </c>
       <c r="E15" s="2">
-        <v>1.43</v>
+        <v>1.85</v>
       </c>
       <c r="F15" s="1">
-        <v>1679234</v>
+        <v>111440</v>
       </c>
       <c r="G15" t="str">
         <v/>
@@ -753,19 +753,19 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>CG Power and Industrial Solutions Ltd</v>
+        <v>Cochin Shipyard Ltd</v>
       </c>
       <c r="C16" t="str">
-        <v>CGPOWER</v>
+        <v>COCHINSHIP</v>
       </c>
       <c r="D16" s="1">
-        <v>867.3</v>
+        <v>1252.7</v>
       </c>
       <c r="E16" s="2">
-        <v>1.37</v>
+        <v>1.85</v>
       </c>
       <c r="F16" s="1">
-        <v>669763</v>
+        <v>418499</v>
       </c>
       <c r="G16" t="str">
         <v/>
@@ -776,19 +776,19 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>Bharat Heavy Electricals Limited</v>
+        <v>L&amp;T Finance Ltd</v>
       </c>
       <c r="C17" t="str">
-        <v>BHEL</v>
+        <v>LTF</v>
       </c>
       <c r="D17" s="1">
-        <v>439.45</v>
+        <v>265.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1.35</v>
+        <v>1.78</v>
       </c>
       <c r="F17" s="1">
-        <v>3376619</v>
+        <v>904964</v>
       </c>
       <c r="G17" t="str">
         <v/>
@@ -799,19 +799,19 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Anand Rathi Wealth Ltd</v>
+        <v>Bharat Dynamics Ltd</v>
       </c>
       <c r="C18" t="str">
-        <v>ANANDRATHI</v>
+        <v>BDL</v>
       </c>
       <c r="D18" s="1">
-        <v>2065.3</v>
+        <v>1094.3</v>
       </c>
       <c r="E18" s="2">
-        <v>1.3</v>
+        <v>1.71</v>
       </c>
       <c r="F18" s="1">
-        <v>476701</v>
+        <v>263332</v>
       </c>
       <c r="G18" t="str">
         <v/>
@@ -822,19 +822,19 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>Multi Commodity Exchange Of India Limited</v>
+        <v>REC Ltd</v>
       </c>
       <c r="C19" t="str">
-        <v>MCX</v>
+        <v>RECLTD</v>
       </c>
       <c r="D19" s="1">
-        <v>3360.2</v>
+        <v>305</v>
       </c>
       <c r="E19" s="2">
-        <v>1.27</v>
+        <v>1.67</v>
       </c>
       <c r="F19" s="1">
-        <v>709642</v>
+        <v>2140161</v>
       </c>
       <c r="G19" t="str">
         <v/>
@@ -845,19 +845,19 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>BSE (Bombay stock exchange) Ltd</v>
+        <v>Amber Enterprises India Ltd</v>
       </c>
       <c r="C20" t="str">
-        <v>BSE</v>
+        <v>AMBER</v>
       </c>
       <c r="D20" s="1">
-        <v>3325.9</v>
+        <v>6551</v>
       </c>
       <c r="E20" s="2">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="F20" s="1">
-        <v>1513355</v>
+        <v>50540</v>
       </c>
       <c r="G20" t="str">
         <v/>
@@ -868,19 +868,19 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Gail (india) Limited</v>
+        <v>Bandhan Bank Ltd</v>
       </c>
       <c r="C21" t="str">
-        <v>GAIL</v>
+        <v>BANDHANBNK</v>
       </c>
       <c r="D21" s="1">
-        <v>168.61</v>
+        <v>159.53</v>
       </c>
       <c r="E21" s="2">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="F21" s="1">
-        <v>1192901</v>
+        <v>3719452</v>
       </c>
       <c r="G21" t="str">
         <v/>
@@ -891,19 +891,19 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Aditya Birla Capital Ltd</v>
+        <v>Bharat Electronics Limited</v>
       </c>
       <c r="C22" t="str">
-        <v>ABCAPITAL</v>
+        <v>BEL</v>
       </c>
       <c r="D22" s="1">
-        <v>385.15</v>
+        <v>374.05</v>
       </c>
       <c r="E22" s="2">
-        <v>1.17</v>
+        <v>1.6</v>
       </c>
       <c r="F22" s="1">
-        <v>918375</v>
+        <v>2014111</v>
       </c>
       <c r="G22" t="str">
         <v/>
@@ -914,19 +914,19 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Mankind Pharma Ltd</v>
+        <v>Power Finance Corporation Limited</v>
       </c>
       <c r="C23" t="str">
-        <v>MANKIND</v>
+        <v>PFC</v>
       </c>
       <c r="D23" s="1">
-        <v>2395.7</v>
+        <v>333</v>
       </c>
       <c r="E23" s="2">
-        <v>1.15</v>
+        <v>1.59</v>
       </c>
       <c r="F23" s="1">
-        <v>35384</v>
+        <v>1867672</v>
       </c>
       <c r="G23" t="str">
         <v/>
@@ -937,19 +937,19 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Steel Authority Of India Limited</v>
+        <v>Computer Age Management Services Ltd</v>
       </c>
       <c r="C24" t="str">
-        <v>SAIL</v>
+        <v>CAMS</v>
       </c>
       <c r="D24" s="1">
-        <v>173.52</v>
+        <v>683.15</v>
       </c>
       <c r="E24" s="2">
-        <v>1.15</v>
+        <v>1.58</v>
       </c>
       <c r="F24" s="1">
-        <v>9004297</v>
+        <v>412315</v>
       </c>
       <c r="G24" t="str">
         <v/>
@@ -960,19 +960,19 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Samvardhana Motherson International Ltd</v>
+        <v>Hindustan Zinc Limited</v>
       </c>
       <c r="C25" t="str">
-        <v>MOTHERSON</v>
+        <v>HINDZINC</v>
       </c>
       <c r="D25" s="1">
-        <v>154.61</v>
+        <v>552.05</v>
       </c>
       <c r="E25" s="2">
-        <v>1.05</v>
+        <v>1.57</v>
       </c>
       <c r="F25" s="1">
-        <v>1547172</v>
+        <v>1212942</v>
       </c>
       <c r="G25" t="str">
         <v/>
@@ -983,19 +983,19 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>One 97 Communications Ltd</v>
+        <v>Supreme Industries Limited</v>
       </c>
       <c r="C26" t="str">
-        <v>PAYTM</v>
+        <v>SUPREMEIND</v>
       </c>
       <c r="D26" s="1">
-        <v>1652.4</v>
+        <v>3528.9</v>
       </c>
       <c r="E26" s="2">
-        <v>1</v>
+        <v>1.56</v>
       </c>
       <c r="F26" s="1">
-        <v>644290</v>
+        <v>33414</v>
       </c>
       <c r="G26" t="str">
         <v/>
@@ -1006,19 +1006,19 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>The Phoenix Mills Limited</v>
+        <v>Havells India Limited</v>
       </c>
       <c r="C27" t="str">
-        <v>PHOENIXLTD</v>
+        <v>HAVELLS</v>
       </c>
       <c r="D27" s="1">
-        <v>1831</v>
+        <v>1057.4</v>
       </c>
       <c r="E27" s="2">
-        <v>0.99</v>
+        <v>1.53</v>
       </c>
       <c r="F27" s="1">
-        <v>102884</v>
+        <v>90755</v>
       </c>
       <c r="G27" t="str">
         <v/>
@@ -1029,19 +1029,19 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>Nippon Life India Asset Management Ltd</v>
+        <v>HDFC Asset Management Company Ltd</v>
       </c>
       <c r="C28" t="str">
-        <v>NAM-INDIA</v>
+        <v>HDFCAMC</v>
       </c>
       <c r="D28" s="1">
-        <v>1054.5</v>
+        <v>2296.7</v>
       </c>
       <c r="E28" s="2">
-        <v>0.91</v>
+        <v>1.51</v>
       </c>
       <c r="F28" s="1">
-        <v>130639</v>
+        <v>143643</v>
       </c>
       <c r="G28" t="str">
         <v/>
@@ -1052,19 +1052,19 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Sona BLW Precision Forgings Ltd</v>
+        <v>Cummins India Limited</v>
       </c>
       <c r="C29" t="str">
-        <v>SONACOMS</v>
+        <v>CUMMINSIND</v>
       </c>
       <c r="D29" s="1">
-        <v>789.9</v>
+        <v>4894.8</v>
       </c>
       <c r="E29" s="2">
-        <v>0.84</v>
+        <v>1.34</v>
       </c>
       <c r="F29" s="1">
-        <v>289459</v>
+        <v>57073</v>
       </c>
       <c r="G29" t="str">
         <v/>
@@ -1075,19 +1075,19 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Trent Limited</v>
+        <v>Mahindra &amp; Mahindra Limited</v>
       </c>
       <c r="C30" t="str">
-        <v>TRENT</v>
+        <v>M&amp;M</v>
       </c>
       <c r="D30" s="1">
-        <v>2940.5</v>
+        <v>2830.8</v>
       </c>
       <c r="E30" s="2">
-        <v>0.76</v>
+        <v>1.24</v>
       </c>
       <c r="F30" s="1">
-        <v>363417</v>
+        <v>549504</v>
       </c>
       <c r="G30" t="str">
         <v/>
@@ -1098,19 +1098,19 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Solar Industries India Limited</v>
+        <v>Pg Electroplast Limited</v>
       </c>
       <c r="C31" t="str">
-        <v>SOLARINDS</v>
+        <v>PGEL</v>
       </c>
       <c r="D31" s="1">
-        <v>20136</v>
+        <v>518.1</v>
       </c>
       <c r="E31" s="2">
-        <v>0.68</v>
+        <v>1.23</v>
       </c>
       <c r="F31" s="1">
-        <v>42690</v>
+        <v>359184</v>
       </c>
       <c r="G31" t="str">
         <v/>
@@ -1121,19 +1121,19 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>Bosch Limited</v>
+        <v>360 ONE WAM Ltd</v>
       </c>
       <c r="C32" t="str">
-        <v>BOSCHLTD</v>
+        <v>360ONE</v>
       </c>
       <c r="D32" s="1">
-        <v>43810</v>
+        <v>1060.5</v>
       </c>
       <c r="E32" s="2">
-        <v>0.61</v>
+        <v>1.19</v>
       </c>
       <c r="F32" s="1">
-        <v>4632</v>
+        <v>160594</v>
       </c>
       <c r="G32" t="str">
         <v/>
@@ -1144,19 +1144,19 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Lic Housing Finance Limited</v>
+        <v>Jindal Steel Ltd</v>
       </c>
       <c r="C33" t="str">
-        <v>LICHSGFIN</v>
+        <v>JINDALSTEL</v>
       </c>
       <c r="D33" s="1">
-        <v>555</v>
+        <v>1028.5</v>
       </c>
       <c r="E33" s="2">
-        <v>0.61</v>
+        <v>1.16</v>
       </c>
       <c r="F33" s="1">
-        <v>777806</v>
+        <v>363968</v>
       </c>
       <c r="G33" t="str">
         <v/>
@@ -1167,19 +1167,19 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Interglobe Aviation Limited</v>
+        <v>Waaree Energies Ltd</v>
       </c>
       <c r="C34" t="str">
-        <v>INDIGO</v>
+        <v>WAAREEENER</v>
       </c>
       <c r="D34" s="1">
-        <v>4861.7</v>
+        <v>2347.8</v>
       </c>
       <c r="E34" s="2">
-        <v>0.59</v>
+        <v>1.07</v>
       </c>
       <c r="F34" s="1">
-        <v>174589</v>
+        <v>202323</v>
       </c>
       <c r="G34" t="str">
         <v/>
@@ -1190,19 +1190,19 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Bajaj Holdings &amp; Investment Limited</v>
+        <v>Ashok Leyland Limited</v>
       </c>
       <c r="C35" t="str">
-        <v>BAJAJHLDNG</v>
+        <v>ASHOKLEY</v>
       </c>
       <c r="D35" s="1">
-        <v>10883</v>
+        <v>146.59</v>
       </c>
       <c r="E35" s="2">
-        <v>0.58</v>
+        <v>1.05</v>
       </c>
       <c r="F35" s="1">
-        <v>7420</v>
+        <v>3957664</v>
       </c>
       <c r="G35" t="str">
         <v/>
@@ -1213,19 +1213,19 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Rbl Bank Limited</v>
+        <v>Inox Wind Limited</v>
       </c>
       <c r="C36" t="str">
-        <v>RBLBANK</v>
+        <v>INOXWIND</v>
       </c>
       <c r="D36" s="1">
-        <v>420.3</v>
+        <v>67.34</v>
       </c>
       <c r="E36" s="2">
-        <v>0.55</v>
+        <v>1.04</v>
       </c>
       <c r="F36" s="1">
-        <v>1282860</v>
+        <v>7275581</v>
       </c>
       <c r="G36" t="str">
         <v/>
@@ -1236,19 +1236,19 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Lodha Developers Ltd</v>
+        <v>Prestige Estates Projects Limited</v>
       </c>
       <c r="C37" t="str">
-        <v>LODHA</v>
+        <v>PRESTIGE</v>
       </c>
       <c r="D37" s="1">
-        <v>1070</v>
+        <v>1420</v>
       </c>
       <c r="E37" s="2">
-        <v>0.49</v>
+        <v>0.94</v>
       </c>
       <c r="F37" s="1">
-        <v>105124</v>
+        <v>64292</v>
       </c>
       <c r="G37" t="str">
         <v/>
@@ -1259,19 +1259,19 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Oracle Financial Services Software Limited</v>
+        <v>Hero Motocorp Limited</v>
       </c>
       <c r="C38" t="str">
-        <v>OFSS</v>
+        <v>HEROMOTOCO</v>
       </c>
       <c r="D38" s="1">
-        <v>10560</v>
+        <v>4940</v>
       </c>
       <c r="E38" s="2">
-        <v>0.48</v>
+        <v>0.91</v>
       </c>
       <c r="F38" s="1">
-        <v>32788</v>
+        <v>109130</v>
       </c>
       <c r="G38" t="str">
         <v/>
@@ -1282,19 +1282,19 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Adani Green Energy Ltd</v>
+        <v>Adani Energy Solutions Ltd</v>
       </c>
       <c r="C39" t="str">
-        <v>ADANIGREEN</v>
+        <v>ADANIENSOL</v>
       </c>
       <c r="D39" s="1">
-        <v>1261</v>
+        <v>1273</v>
       </c>
       <c r="E39" s="2">
-        <v>0.41</v>
+        <v>0.87</v>
       </c>
       <c r="F39" s="1">
-        <v>653725</v>
+        <v>220309</v>
       </c>
       <c r="G39" t="str">
         <v/>
@@ -1305,19 +1305,19 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Adani Enterprises Limited</v>
+        <v>Pi Industries Limited</v>
       </c>
       <c r="C40" t="str">
-        <v>ADANIENT</v>
+        <v>PIIND</v>
       </c>
       <c r="D40" s="1">
-        <v>2642</v>
+        <v>2136.1</v>
       </c>
       <c r="E40" s="2">
-        <v>0.29</v>
+        <v>0.85</v>
       </c>
       <c r="F40" s="1">
-        <v>413162</v>
+        <v>27594</v>
       </c>
       <c r="G40" t="str">
         <v/>
@@ -1328,19 +1328,19 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Kalyan Jewellers India Ltd</v>
+        <v>Upl Limited</v>
       </c>
       <c r="C41" t="str">
-        <v>KALYANKJIL</v>
+        <v>UPL</v>
       </c>
       <c r="D41" s="1">
-        <v>555.6</v>
+        <v>492.6</v>
       </c>
       <c r="E41" s="2">
-        <v>0.29</v>
+        <v>0.85</v>
       </c>
       <c r="F41" s="1">
-        <v>1183623</v>
+        <v>830602</v>
       </c>
       <c r="G41" t="str">
         <v/>
@@ -1351,19 +1351,19 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Laurus Labs Limited</v>
+        <v>Indian Oil Corporation Limited</v>
       </c>
       <c r="C42" t="str">
-        <v>LAURUSLABS</v>
+        <v>IOC</v>
       </c>
       <c r="D42" s="1">
-        <v>2041.3</v>
+        <v>127.4</v>
       </c>
       <c r="E42" s="2">
-        <v>0.23</v>
+        <v>0.83</v>
       </c>
       <c r="F42" s="1">
-        <v>496299</v>
+        <v>2466772</v>
       </c>
       <c r="G42" t="str">
         <v/>
@@ -1374,19 +1374,19 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>Eternal Ltd</v>
+        <v>KFin Technologies Ltd</v>
       </c>
       <c r="C43" t="str">
-        <v>ETERNAL</v>
+        <v>KFINTECH</v>
       </c>
       <c r="D43" s="1">
-        <v>324.2</v>
+        <v>849.2</v>
       </c>
       <c r="E43" s="2">
-        <v>0.23</v>
+        <v>0.81</v>
       </c>
       <c r="F43" s="1">
-        <v>4172180</v>
+        <v>67328</v>
       </c>
       <c r="G43" t="str">
         <v/>
@@ -1397,19 +1397,19 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>Persistent Systems Limited</v>
+        <v>HDFC Life Insurance Company Ltd</v>
       </c>
       <c r="C44" t="str">
-        <v>PERSISTENT</v>
+        <v>HDFCLIFE</v>
       </c>
       <c r="D44" s="1">
-        <v>5779.5</v>
+        <v>561.15</v>
       </c>
       <c r="E44" s="2">
-        <v>0.16</v>
+        <v>0.81</v>
       </c>
       <c r="F44" s="1">
-        <v>176431</v>
+        <v>803057</v>
       </c>
       <c r="G44" t="str">
         <v/>
@@ -1420,19 +1420,19 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Siemens Energy India Ltd</v>
+        <v>Jsw Steel Limited</v>
       </c>
       <c r="C45" t="str">
-        <v>ENRIN</v>
+        <v>JSWSTEEL</v>
       </c>
       <c r="D45" s="1">
-        <v>3104.1</v>
+        <v>1177.1</v>
       </c>
       <c r="E45" s="2">
-        <v>0.1</v>
+        <v>0.78</v>
       </c>
       <c r="F45" s="1">
-        <v>168986</v>
+        <v>306452</v>
       </c>
       <c r="G45" t="str">
         <v/>
@@ -1443,19 +1443,19 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Divi's Laboratories Limited</v>
+        <v>Eicher Motors Limited</v>
       </c>
       <c r="C46" t="str">
-        <v>DIVISLAB</v>
+        <v>EICHERMOT</v>
       </c>
       <c r="D46" s="1">
-        <v>9338.5</v>
+        <v>7104</v>
       </c>
       <c r="E46" s="2">
-        <v>-0.02</v>
+        <v>0.77</v>
       </c>
       <c r="F46" s="1">
-        <v>117530</v>
+        <v>118807</v>
       </c>
       <c r="G46" t="str">
         <v/>
@@ -1466,19 +1466,19 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Dlf Limited</v>
+        <v>Jsw Energy Limited</v>
       </c>
       <c r="C47" t="str">
-        <v>DLF</v>
+        <v>JSWENERGY</v>
       </c>
       <c r="D47" s="1">
-        <v>648.35</v>
+        <v>465.55</v>
       </c>
       <c r="E47" s="2">
-        <v>-0.04</v>
+        <v>0.7</v>
       </c>
       <c r="F47" s="1">
-        <v>341508</v>
+        <v>397169</v>
       </c>
       <c r="G47" t="str">
         <v/>
@@ -1489,19 +1489,19 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Page Industries Limited</v>
+        <v>Icici Prudential Life Insurance Company Limited</v>
       </c>
       <c r="C48" t="str">
-        <v>PAGEIND</v>
+        <v>ICICIPRULI</v>
       </c>
       <c r="D48" s="1">
-        <v>36845</v>
+        <v>463.65</v>
       </c>
       <c r="E48" s="2">
-        <v>-0.08</v>
+        <v>0.67</v>
       </c>
       <c r="F48" s="1">
-        <v>1824</v>
+        <v>126736</v>
       </c>
       <c r="G48" t="str">
         <v/>
@@ -1512,19 +1512,19 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Kotak Mahindra Bank Limited</v>
+        <v>Hyundai Motor India Ltd</v>
       </c>
       <c r="C49" t="str">
-        <v>KOTAKBANK</v>
+        <v>HYUNDAI</v>
       </c>
       <c r="D49" s="1">
-        <v>440.65</v>
+        <v>1952.8</v>
       </c>
       <c r="E49" s="2">
-        <v>-0.08</v>
+        <v>0.66</v>
       </c>
       <c r="F49" s="1">
-        <v>3166965</v>
+        <v>154981</v>
       </c>
       <c r="G49" t="str">
         <v/>
@@ -1535,19 +1535,19 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Oberoi Realty Limited</v>
+        <v>Indian Renewable Energy Development Agency Ltd</v>
       </c>
       <c r="C50" t="str">
-        <v>OBEROIRLTY</v>
+        <v>IREDA</v>
       </c>
       <c r="D50" s="1">
-        <v>1697</v>
+        <v>105.09</v>
       </c>
       <c r="E50" s="2">
-        <v>-0.11</v>
+        <v>0.66</v>
       </c>
       <c r="F50" s="1">
-        <v>147912</v>
+        <v>1706044</v>
       </c>
       <c r="G50" t="str">
         <v/>
@@ -1558,19 +1558,19 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Info Edge (india) Limited</v>
+        <v>Swiggy Ltd</v>
       </c>
       <c r="C51" t="str">
-        <v>NAUKRI</v>
+        <v>SWIGGY</v>
       </c>
       <c r="D51" s="1">
-        <v>1217.7</v>
+        <v>235.4</v>
       </c>
       <c r="E51" s="2">
-        <v>-0.11</v>
+        <v>0.51</v>
       </c>
       <c r="F51" s="1">
-        <v>99544</v>
+        <v>1816838</v>
       </c>
       <c r="G51" t="str">
         <v/>
@@ -1581,19 +1581,19 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Aurobindo Pharma Limited</v>
+        <v>Indian Energy Exchange Ltd</v>
       </c>
       <c r="C52" t="str">
-        <v>AUROPHARMA</v>
+        <v>IEX</v>
       </c>
       <c r="D52" s="1">
-        <v>1689.9</v>
+        <v>105.28</v>
       </c>
       <c r="E52" s="2">
-        <v>-0.18</v>
+        <v>0.48</v>
       </c>
       <c r="F52" s="1">
-        <v>378540</v>
+        <v>797992</v>
       </c>
       <c r="G52" t="str">
         <v/>
@@ -1604,19 +1604,19 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>IDFC First Bank Ltd</v>
+        <v>KPIT Technologies Ltd</v>
       </c>
       <c r="C53" t="str">
-        <v>IDFCFIRSTB</v>
+        <v>KPITTECH</v>
       </c>
       <c r="D53" s="1">
-        <v>79.35</v>
+        <v>481.25</v>
       </c>
       <c r="E53" s="2">
-        <v>-0.21</v>
+        <v>0.47</v>
       </c>
       <c r="F53" s="1">
-        <v>3488171</v>
+        <v>478752</v>
       </c>
       <c r="G53" t="str">
         <v/>
@@ -1627,19 +1627,19 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Radico Khaitan Limited</v>
+        <v>Bharat Forge Limited</v>
       </c>
       <c r="C54" t="str">
-        <v>RADICO</v>
+        <v>BHARATFORG</v>
       </c>
       <c r="D54" s="1">
-        <v>4537.1</v>
+        <v>1823.9</v>
       </c>
       <c r="E54" s="2">
-        <v>-0.28</v>
+        <v>0.39</v>
       </c>
       <c r="F54" s="1">
-        <v>68451</v>
+        <v>147071</v>
       </c>
       <c r="G54" t="str">
         <v/>
@@ -1650,19 +1650,19 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>The Indian Hotels Company Limited</v>
+        <v>Cholamandalam Investment And Finance Company Limited</v>
       </c>
       <c r="C55" t="str">
-        <v>INDHOTEL</v>
+        <v>CHOLAFIN</v>
       </c>
       <c r="D55" s="1">
-        <v>713.5</v>
+        <v>1593.8</v>
       </c>
       <c r="E55" s="2">
-        <v>-0.3</v>
+        <v>0.39</v>
       </c>
       <c r="F55" s="1">
-        <v>208021</v>
+        <v>353297</v>
       </c>
       <c r="G55" t="str">
         <v/>
@@ -1673,19 +1673,19 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Petronet Lng Limited</v>
+        <v>Muthoot Finance Limited</v>
       </c>
       <c r="C56" t="str">
-        <v>PETRONET</v>
+        <v>MUTHOOTFIN</v>
       </c>
       <c r="D56" s="1">
-        <v>290.45</v>
+        <v>2634.7</v>
       </c>
       <c r="E56" s="2">
-        <v>-0.36</v>
+        <v>0.38</v>
       </c>
       <c r="F56" s="1">
-        <v>452528</v>
+        <v>54521</v>
       </c>
       <c r="G56" t="str">
         <v/>
@@ -1696,19 +1696,19 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Bank Of Maharashtra Ltd</v>
+        <v>Ultratech Cement Limited</v>
       </c>
       <c r="C57" t="str">
-        <v>MAHABANK</v>
+        <v>ULTRACEMCO</v>
       </c>
       <c r="D57" s="1">
-        <v>82.86</v>
+        <v>10714</v>
       </c>
       <c r="E57" s="2">
-        <v>-0.36</v>
+        <v>0.37</v>
       </c>
       <c r="F57" s="1">
-        <v>3166707</v>
+        <v>17649</v>
       </c>
       <c r="G57" t="str">
         <v/>
@@ -1719,19 +1719,19 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>The Federal Bank  Limited</v>
+        <v>TATA Consumer Products Ltd</v>
       </c>
       <c r="C58" t="str">
-        <v>FEDERALBNK</v>
+        <v>TATACONSUM</v>
       </c>
       <c r="D58" s="1">
-        <v>328.55</v>
+        <v>958.55</v>
       </c>
       <c r="E58" s="2">
-        <v>-0.44</v>
+        <v>0.37</v>
       </c>
       <c r="F58" s="1">
-        <v>1109248</v>
+        <v>155149</v>
       </c>
       <c r="G58" t="str">
         <v/>
@@ -1742,19 +1742,19 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Adani Ports And Special Economic Zone Limited</v>
+        <v>Cipla Limited</v>
       </c>
       <c r="C59" t="str">
-        <v>ADANIPORTS</v>
+        <v>CIPLA</v>
       </c>
       <c r="D59" s="1">
-        <v>1752.9</v>
+        <v>1305.3</v>
       </c>
       <c r="E59" s="2">
-        <v>-0.46</v>
+        <v>0.33</v>
       </c>
       <c r="F59" s="1">
-        <v>630980</v>
+        <v>99631</v>
       </c>
       <c r="G59" t="str">
         <v/>
@@ -1765,19 +1765,19 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Dixon Technologies Ltd</v>
+        <v>Tata Steel Limited</v>
       </c>
       <c r="C60" t="str">
-        <v>DIXON</v>
+        <v>TATASTEEL</v>
       </c>
       <c r="D60" s="1">
-        <v>12695</v>
+        <v>174.36</v>
       </c>
       <c r="E60" s="2">
-        <v>-0.62</v>
+        <v>0.32</v>
       </c>
       <c r="F60" s="1">
-        <v>67281</v>
+        <v>16724030</v>
       </c>
       <c r="G60" t="str">
         <v/>
@@ -1788,19 +1788,19 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Zydus Lifesciences Ltd</v>
+        <v>Shree Cements Limited</v>
       </c>
       <c r="C61" t="str">
-        <v>ZYDUSLIFE</v>
+        <v>SHREECEM</v>
       </c>
       <c r="D61" s="1">
-        <v>1110</v>
+        <v>22145</v>
       </c>
       <c r="E61" s="2">
-        <v>-0.67</v>
+        <v>0.29</v>
       </c>
       <c r="F61" s="1">
-        <v>152023</v>
+        <v>3475</v>
       </c>
       <c r="G61" t="str">
         <v/>
@@ -1811,19 +1811,19 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Torrent Pharmaceuticals Limited</v>
+        <v>Blue Star Limited</v>
       </c>
       <c r="C62" t="str">
-        <v>TORNTPHARM</v>
+        <v>BLUESTARCO</v>
       </c>
       <c r="D62" s="1">
-        <v>4619.7</v>
+        <v>1578.4</v>
       </c>
       <c r="E62" s="2">
-        <v>-0.8</v>
+        <v>0.28</v>
       </c>
       <c r="F62" s="1">
-        <v>121121</v>
+        <v>68814</v>
       </c>
       <c r="G62" t="str">
         <v/>
@@ -1834,19 +1834,19 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Glenmark Pharmaceuticals Limited</v>
+        <v>Max Healthcare Institute Ltd</v>
       </c>
       <c r="C63" t="str">
-        <v>GLENMARK</v>
+        <v>MAXHEALTH</v>
       </c>
       <c r="D63" s="1">
-        <v>2268.4</v>
+        <v>886.2</v>
       </c>
       <c r="E63" s="2">
-        <v>-1.07</v>
+        <v>0.27</v>
       </c>
       <c r="F63" s="1">
-        <v>136893</v>
+        <v>306635</v>
       </c>
       <c r="G63" t="str">
         <v/>
@@ -1857,19 +1857,19 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>FSN E-Commerce Ventures Ltd</v>
+        <v>Asian Paints Limited</v>
       </c>
       <c r="C64" t="str">
-        <v>NYKAA</v>
+        <v>ASIANPAINT</v>
       </c>
       <c r="D64" s="1">
-        <v>339.1</v>
+        <v>2345.2</v>
       </c>
       <c r="E64" s="2">
-        <v>-1.14</v>
+        <v>0.26</v>
       </c>
       <c r="F64" s="1">
-        <v>962612</v>
+        <v>113301</v>
       </c>
       <c r="G64" t="str">
         <v/>
@@ -1880,19 +1880,19 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Coforge (Niit Tech) Ltd</v>
+        <v>Uno Minda Ltd</v>
       </c>
       <c r="C65" t="str">
-        <v>COFORGE</v>
+        <v>UNOMINDA</v>
       </c>
       <c r="D65" s="1">
-        <v>1846.4</v>
+        <v>1110.7</v>
       </c>
       <c r="E65" s="2">
-        <v>-1.15</v>
+        <v>0.24</v>
       </c>
       <c r="F65" s="1">
-        <v>411646</v>
+        <v>81274</v>
       </c>
       <c r="G65" t="str">
         <v/>
@@ -1903,19 +1903,19 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Punjab National Bank Ltd</v>
+        <v>Bharat Petroleum Corporation Limited</v>
       </c>
       <c r="C66" t="str">
-        <v>PNB</v>
+        <v>BPCL</v>
       </c>
       <c r="D66" s="1">
-        <v>115.34</v>
+        <v>288.5</v>
       </c>
       <c r="E66" s="2">
-        <v>-1.4</v>
+        <v>0.24</v>
       </c>
       <c r="F66" s="1">
-        <v>3498675</v>
+        <v>701419</v>
       </c>
       <c r="G66" t="str">
         <v/>
@@ -1926,27 +1926,1936 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Vodafone Idea Ltd</v>
+        <v>Crompton Greaves Consumer Electricals Limited</v>
       </c>
       <c r="C67" t="str">
-        <v>IDEA</v>
+        <v>CROMPTON</v>
       </c>
       <c r="D67" s="1">
-        <v>12.72</v>
+        <v>205.56</v>
       </c>
       <c r="E67" s="2">
-        <v>-2.15</v>
+        <v>0.22</v>
       </c>
       <c r="F67" s="1">
-        <v>163888675</v>
+        <v>394888</v>
       </c>
       <c r="G67" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68">
+        <v>67</v>
+      </c>
+      <c r="B68" t="str">
+        <v>SBI Cards &amp; Payment Services Ltd</v>
+      </c>
+      <c r="C68" t="str">
+        <v>SBICARD</v>
+      </c>
+      <c r="D68" s="1">
+        <v>563.2</v>
+      </c>
+      <c r="E68" s="2">
+        <v>0.21</v>
+      </c>
+      <c r="F68" s="1">
+        <v>134356</v>
+      </c>
+      <c r="G68" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69">
+        <v>68</v>
+      </c>
+      <c r="B69" t="str">
+        <v>Tata Consultancy Services Limited</v>
+      </c>
+      <c r="C69" t="str">
+        <v>TCS</v>
+      </c>
+      <c r="D69" s="1">
+        <v>2159.3</v>
+      </c>
+      <c r="E69" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="F69" s="1">
+        <v>1409739</v>
+      </c>
+      <c r="G69" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70">
+        <v>69</v>
+      </c>
+      <c r="B70" t="str">
+        <v>Voltas Limited</v>
+      </c>
+      <c r="C70" t="str">
+        <v>VOLTAS</v>
+      </c>
+      <c r="D70" s="1">
+        <v>1035.3</v>
+      </c>
+      <c r="E70" s="2">
+        <v>0.15</v>
+      </c>
+      <c r="F70" s="1">
+        <v>89238</v>
+      </c>
+      <c r="G70" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71">
+        <v>70</v>
+      </c>
+      <c r="B71" t="str">
+        <v>Godrej Properties Limited</v>
+      </c>
+      <c r="C71" t="str">
+        <v>GODREJPROP</v>
+      </c>
+      <c r="D71" s="1">
+        <v>1552</v>
+      </c>
+      <c r="E71" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F71" s="1">
+        <v>79373</v>
+      </c>
+      <c r="G71" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72">
+        <v>71</v>
+      </c>
+      <c r="B72" t="str">
+        <v>Force Motors Ltd</v>
+      </c>
+      <c r="C72" t="str">
+        <v>FORCEMOT</v>
+      </c>
+      <c r="D72" s="1">
+        <v>16921</v>
+      </c>
+      <c r="E72" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="F72" s="1">
+        <v>12136</v>
+      </c>
+      <c r="G72" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73">
+        <v>72</v>
+      </c>
+      <c r="B73" t="str">
+        <v>Max Financial Services Limited</v>
+      </c>
+      <c r="C73" t="str">
+        <v>MFSL</v>
+      </c>
+      <c r="D73" s="1">
+        <v>1311</v>
+      </c>
+      <c r="E73" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F73" s="1">
+        <v>72611</v>
+      </c>
+      <c r="G73" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74">
+        <v>73</v>
+      </c>
+      <c r="B74" t="str">
+        <v>Central Depository Services Ltd</v>
+      </c>
+      <c r="C74" t="str">
+        <v>CDSL</v>
+      </c>
+      <c r="D74" s="1">
+        <v>1261.2</v>
+      </c>
+      <c r="E74" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="F74" s="1">
+        <v>252216</v>
+      </c>
+      <c r="G74" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75">
+        <v>74</v>
+      </c>
+      <c r="B75" t="str">
+        <v>Power Grid Corporation Of India Limited</v>
+      </c>
+      <c r="C75" t="str">
+        <v>POWERGRID</v>
+      </c>
+      <c r="D75" s="1">
+        <v>249.35</v>
+      </c>
+      <c r="E75" s="2">
+        <v>0.08</v>
+      </c>
+      <c r="F75" s="1">
+        <v>1830610</v>
+      </c>
+      <c r="G75" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76">
+        <v>75</v>
+      </c>
+      <c r="B76" t="str">
+        <v>Container Corporation Of India Limited</v>
+      </c>
+      <c r="C76" t="str">
+        <v>CONCOR</v>
+      </c>
+      <c r="D76" s="1">
+        <v>442.25</v>
+      </c>
+      <c r="E76" s="2">
+        <v>0.06</v>
+      </c>
+      <c r="F76" s="1">
+        <v>126678</v>
+      </c>
+      <c r="G76" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77">
+        <v>76</v>
+      </c>
+      <c r="B77" t="str">
+        <v>Vedanta Limited</v>
+      </c>
+      <c r="C77" t="str">
+        <v>VEDL</v>
+      </c>
+      <c r="D77" s="1">
+        <v>264.1</v>
+      </c>
+      <c r="E77" s="2">
+        <v>0.04</v>
+      </c>
+      <c r="F77" s="1">
+        <v>3986903</v>
+      </c>
+      <c r="G77" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78">
+        <v>77</v>
+      </c>
+      <c r="B78" t="str">
+        <v>Tata Power Company Limited</v>
+      </c>
+      <c r="C78" t="str">
+        <v>TATAPOWER</v>
+      </c>
+      <c r="D78" s="1">
+        <v>342.25</v>
+      </c>
+      <c r="E78" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F78" s="1">
+        <v>751591</v>
+      </c>
+      <c r="G78" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79">
+        <v>78</v>
+      </c>
+      <c r="B79" t="str">
+        <v>Wipro Limited</v>
+      </c>
+      <c r="C79" t="str">
+        <v>WIPRO</v>
+      </c>
+      <c r="D79" s="1">
+        <v>162.62</v>
+      </c>
+      <c r="E79" s="2">
+        <v>0.03</v>
+      </c>
+      <c r="F79" s="1">
+        <v>2571699</v>
+      </c>
+      <c r="G79" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80">
+        <v>79</v>
+      </c>
+      <c r="B80" t="str">
+        <v>Vishal Mega Mart Ltd</v>
+      </c>
+      <c r="C80" t="str">
+        <v>VMM</v>
+      </c>
+      <c r="D80" s="1">
+        <v>97.52</v>
+      </c>
+      <c r="E80" s="2">
+        <v>0.02</v>
+      </c>
+      <c r="F80" s="1">
+        <v>1151216</v>
+      </c>
+      <c r="G80" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81">
+        <v>80</v>
+      </c>
+      <c r="B81" t="str">
+        <v>Jio Financial Services Ltd</v>
+      </c>
+      <c r="C81" t="str">
+        <v>JIOFIN</v>
+      </c>
+      <c r="D81" s="1">
+        <v>214.62</v>
+      </c>
+      <c r="E81" s="2">
+        <v>0</v>
+      </c>
+      <c r="F81" s="1">
+        <v>3267960</v>
+      </c>
+      <c r="G81" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82">
+        <v>81</v>
+      </c>
+      <c r="B82" t="str">
+        <v>Maruti Suzuki India Limited</v>
+      </c>
+      <c r="C82" t="str">
+        <v>MARUTI</v>
+      </c>
+      <c r="D82" s="1">
+        <v>11418</v>
+      </c>
+      <c r="E82" s="2">
+        <v>-0.02</v>
+      </c>
+      <c r="F82" s="1">
+        <v>78725</v>
+      </c>
+      <c r="G82" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83">
+        <v>82</v>
+      </c>
+      <c r="B83" t="str">
+        <v>Bajaj Finserv Limited</v>
+      </c>
+      <c r="C83" t="str">
+        <v>BAJAJFINSV</v>
+      </c>
+      <c r="D83" s="1">
+        <v>1734</v>
+      </c>
+      <c r="E83" s="2">
+        <v>-0.04</v>
+      </c>
+      <c r="F83" s="1">
+        <v>142596</v>
+      </c>
+      <c r="G83" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84">
+        <v>83</v>
+      </c>
+      <c r="B84" t="str">
+        <v>Tata Motors Passenger Vehicles Ltd</v>
+      </c>
+      <c r="C84" t="str">
+        <v>TMPV</v>
+      </c>
+      <c r="D84" s="1">
+        <v>279.8</v>
+      </c>
+      <c r="E84" s="2">
+        <v>-0.04</v>
+      </c>
+      <c r="F84" s="1">
+        <v>2196490</v>
+      </c>
+      <c r="G84" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85">
+        <v>84</v>
+      </c>
+      <c r="B85" t="str">
+        <v>Bajaj Finance Limited</v>
+      </c>
+      <c r="C85" t="str">
+        <v>BAJFINANCE</v>
+      </c>
+      <c r="D85" s="1">
+        <v>959.4</v>
+      </c>
+      <c r="E85" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="F85" s="1">
+        <v>1388307</v>
+      </c>
+      <c r="G85" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86">
+        <v>85</v>
+      </c>
+      <c r="B86" t="str">
+        <v>Oil India Limited</v>
+      </c>
+      <c r="C86" t="str">
+        <v>OIL</v>
+      </c>
+      <c r="D86" s="1">
+        <v>443.25</v>
+      </c>
+      <c r="E86" s="2">
+        <v>-0.06</v>
+      </c>
+      <c r="F86" s="1">
+        <v>277233</v>
+      </c>
+      <c r="G86" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87">
+        <v>86</v>
+      </c>
+      <c r="B87" t="str">
+        <v>LTIMindtree Ltd</v>
+      </c>
+      <c r="C87" t="str">
+        <v>LTM</v>
+      </c>
+      <c r="D87" s="1">
+        <v>4065.3</v>
+      </c>
+      <c r="E87" s="2">
+        <v>-0.12</v>
+      </c>
+      <c r="F87" s="1">
+        <v>105649</v>
+      </c>
+      <c r="G87" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88">
+        <v>87</v>
+      </c>
+      <c r="B88" t="str">
+        <v>Alkem Laboratories Limited</v>
+      </c>
+      <c r="C88" t="str">
+        <v>ALKEM</v>
+      </c>
+      <c r="D88" s="1">
+        <v>5272</v>
+      </c>
+      <c r="E88" s="2">
+        <v>-0.13</v>
+      </c>
+      <c r="F88" s="1">
+        <v>64534</v>
+      </c>
+      <c r="G88" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89">
+        <v>88</v>
+      </c>
+      <c r="B89" t="str">
+        <v>Godfrey Phillips India Limited</v>
+      </c>
+      <c r="C89" t="str">
+        <v>GODFRYPHLP</v>
+      </c>
+      <c r="D89" s="1">
+        <v>1810.9</v>
+      </c>
+      <c r="E89" s="2">
+        <v>-0.13</v>
+      </c>
+      <c r="F89" s="1">
+        <v>41067</v>
+      </c>
+      <c r="G89" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90">
+        <v>89</v>
+      </c>
+      <c r="B90" t="str">
+        <v>Nestle India Limited</v>
+      </c>
+      <c r="C90" t="str">
+        <v>NESTLEIND</v>
+      </c>
+      <c r="D90" s="1">
+        <v>1331.3</v>
+      </c>
+      <c r="E90" s="2">
+        <v>-0.13</v>
+      </c>
+      <c r="F90" s="1">
+        <v>279890</v>
+      </c>
+      <c r="G90" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91">
+        <v>90</v>
+      </c>
+      <c r="B91" t="str">
+        <v>Jubilant Foodworks Limited</v>
+      </c>
+      <c r="C91" t="str">
+        <v>JUBLFOOD</v>
+      </c>
+      <c r="D91" s="1">
+        <v>422.2</v>
+      </c>
+      <c r="E91" s="2">
+        <v>-0.13</v>
+      </c>
+      <c r="F91" s="1">
+        <v>279837</v>
+      </c>
+      <c r="G91" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92">
+        <v>91</v>
+      </c>
+      <c r="B92" t="str">
+        <v>Shriram Finance Ltd</v>
+      </c>
+      <c r="C92" t="str">
+        <v>SHRIRAMFIN</v>
+      </c>
+      <c r="D92" s="1">
+        <v>939</v>
+      </c>
+      <c r="E92" s="2">
+        <v>-0.15</v>
+      </c>
+      <c r="F92" s="1">
+        <v>399522</v>
+      </c>
+      <c r="G92" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93">
+        <v>92</v>
+      </c>
+      <c r="B93" t="str">
+        <v>Godrej Consumer Products Limited</v>
+      </c>
+      <c r="C93" t="str">
+        <v>GODREJCP</v>
+      </c>
+      <c r="D93" s="1">
+        <v>859.1</v>
+      </c>
+      <c r="E93" s="2">
+        <v>-0.16</v>
+      </c>
+      <c r="F93" s="1">
+        <v>74669</v>
+      </c>
+      <c r="G93" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94">
+        <v>93</v>
+      </c>
+      <c r="B94" t="str">
+        <v>Grasim Industries Limited</v>
+      </c>
+      <c r="C94" t="str">
+        <v>GRASIM</v>
+      </c>
+      <c r="D94" s="1">
+        <v>2883.9</v>
+      </c>
+      <c r="E94" s="2">
+        <v>-0.21</v>
+      </c>
+      <c r="F94" s="1">
+        <v>35017</v>
+      </c>
+      <c r="G94" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95">
+        <v>94</v>
+      </c>
+      <c r="B95" t="str">
+        <v>Hdfc Bank Limited</v>
+      </c>
+      <c r="C95" t="str">
+        <v>HDFCBANK</v>
+      </c>
+      <c r="D95" s="1">
+        <v>705.7</v>
+      </c>
+      <c r="E95" s="2">
+        <v>-0.22</v>
+      </c>
+      <c r="F95" s="1">
+        <v>7070219</v>
+      </c>
+      <c r="G95" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96">
+        <v>95</v>
+      </c>
+      <c r="B96" t="str">
+        <v>National Aluminium Company Limited</v>
+      </c>
+      <c r="C96" t="str">
+        <v>NATIONALUM</v>
+      </c>
+      <c r="D96" s="1">
+        <v>315.2</v>
+      </c>
+      <c r="E96" s="2">
+        <v>-0.22</v>
+      </c>
+      <c r="F96" s="1">
+        <v>895834</v>
+      </c>
+      <c r="G96" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97">
+        <v>96</v>
+      </c>
+      <c r="B97" t="str">
+        <v>Mphasis Limited</v>
+      </c>
+      <c r="C97" t="str">
+        <v>MPHASIS</v>
+      </c>
+      <c r="D97" s="1">
+        <v>2354.6</v>
+      </c>
+      <c r="E97" s="2">
+        <v>-0.23</v>
+      </c>
+      <c r="F97" s="1">
+        <v>164677</v>
+      </c>
+      <c r="G97" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98">
+        <v>97</v>
+      </c>
+      <c r="B98" t="str">
+        <v>AU Small Finance Bank Ltd</v>
+      </c>
+      <c r="C98" t="str">
+        <v>AUBANK</v>
+      </c>
+      <c r="D98" s="1">
+        <v>979.5</v>
+      </c>
+      <c r="E98" s="2">
+        <v>-0.25</v>
+      </c>
+      <c r="F98" s="1">
+        <v>177673</v>
+      </c>
+      <c r="G98" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>98</v>
+      </c>
+      <c r="B99" t="str">
+        <v>Hcl Technologies Limited</v>
+      </c>
+      <c r="C99" t="str">
+        <v>HCLTECH</v>
+      </c>
+      <c r="D99" s="1">
+        <v>1213.4</v>
+      </c>
+      <c r="E99" s="2">
+        <v>-0.27</v>
+      </c>
+      <c r="F99" s="1">
+        <v>824092</v>
+      </c>
+      <c r="G99" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>99</v>
+      </c>
+      <c r="B100" t="str">
+        <v>Infosys Limited</v>
+      </c>
+      <c r="C100" t="str">
+        <v>INFY</v>
+      </c>
+      <c r="D100" s="1">
+        <v>1020.6</v>
+      </c>
+      <c r="E100" s="2">
+        <v>-0.27</v>
+      </c>
+      <c r="F100" s="1">
+        <v>2603857</v>
+      </c>
+      <c r="G100" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>100</v>
+      </c>
+      <c r="B101" t="str">
+        <v>Sun Pharmaceuticals Industries Limited</v>
+      </c>
+      <c r="C101" t="str">
+        <v>SUNPHARMA</v>
+      </c>
+      <c r="D101" s="1">
+        <v>1755</v>
+      </c>
+      <c r="E101" s="2">
+        <v>-0.28</v>
+      </c>
+      <c r="F101" s="1">
+        <v>314714</v>
+      </c>
+      <c r="G101" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>101</v>
+      </c>
+      <c r="B102" t="str">
+        <v>Titan Company Limited</v>
+      </c>
+      <c r="C102" t="str">
+        <v>TITAN</v>
+      </c>
+      <c r="D102" s="1">
+        <v>4395.4</v>
+      </c>
+      <c r="E102" s="2">
+        <v>-0.33</v>
+      </c>
+      <c r="F102" s="1">
+        <v>119347</v>
+      </c>
+      <c r="G102" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>102</v>
+      </c>
+      <c r="B103" t="str">
+        <v>Indusind Bank Limited</v>
+      </c>
+      <c r="C103" t="str">
+        <v>INDUSINDBK</v>
+      </c>
+      <c r="D103" s="1">
+        <v>858.7</v>
+      </c>
+      <c r="E103" s="2">
+        <v>-0.34</v>
+      </c>
+      <c r="F103" s="1">
+        <v>2374609</v>
+      </c>
+      <c r="G103" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>103</v>
+      </c>
+      <c r="B104" t="str">
+        <v>Premier Energies Ltd</v>
+      </c>
+      <c r="C104" t="str">
+        <v>PREMIERENE</v>
+      </c>
+      <c r="D104" s="1">
+        <v>892.1</v>
+      </c>
+      <c r="E104" s="2">
+        <v>-0.36</v>
+      </c>
+      <c r="F104" s="1">
+        <v>695204</v>
+      </c>
+      <c r="G104" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>104</v>
+      </c>
+      <c r="B105" t="str">
+        <v>NIFTY</v>
+      </c>
+      <c r="C105" t="str">
+        <v>NIFTY</v>
+      </c>
+      <c r="D105" s="1">
+        <v>22430.35</v>
+      </c>
+      <c r="E105" s="2">
+        <v>-0.4</v>
+      </c>
+      <c r="F105" s="1">
+        <v>0</v>
+      </c>
+      <c r="G105" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>105</v>
+      </c>
+      <c r="B106" t="str">
+        <v>Kaynes Technology India Ltd</v>
+      </c>
+      <c r="C106" t="str">
+        <v>KAYNES</v>
+      </c>
+      <c r="D106" s="1">
+        <v>3250.2</v>
+      </c>
+      <c r="E106" s="2">
+        <v>-0.42</v>
+      </c>
+      <c r="F106" s="1">
+        <v>227700</v>
+      </c>
+      <c r="G106" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>106</v>
+      </c>
+      <c r="B107" t="str">
+        <v>ICICI Lombard General Insurance Company Ltd</v>
+      </c>
+      <c r="C107" t="str">
+        <v>ICICIGI</v>
+      </c>
+      <c r="D107" s="1">
+        <v>1683.1</v>
+      </c>
+      <c r="E107" s="2">
+        <v>-0.42</v>
+      </c>
+      <c r="F107" s="1">
+        <v>74003</v>
+      </c>
+      <c r="G107" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>107</v>
+      </c>
+      <c r="B108" t="str">
+        <v>United Spirits Ltd</v>
+      </c>
+      <c r="C108" t="str">
+        <v>UNITDSPR</v>
+      </c>
+      <c r="D108" s="1">
+        <v>1360</v>
+      </c>
+      <c r="E108" s="2">
+        <v>-0.44</v>
+      </c>
+      <c r="F108" s="1">
+        <v>67084</v>
+      </c>
+      <c r="G108" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>108</v>
+      </c>
+      <c r="B109" t="str">
+        <v>SBI Life Insurance Company Ltd</v>
+      </c>
+      <c r="C109" t="str">
+        <v>SBILIFE</v>
+      </c>
+      <c r="D109" s="1">
+        <v>1677.1</v>
+      </c>
+      <c r="E109" s="2">
+        <v>-0.45</v>
+      </c>
+      <c r="F109" s="1">
+        <v>71035</v>
+      </c>
+      <c r="G109" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>109</v>
+      </c>
+      <c r="B110" t="str">
+        <v>Lupin Limited</v>
+      </c>
+      <c r="C110" t="str">
+        <v>LUPIN</v>
+      </c>
+      <c r="D110" s="1">
+        <v>1947.2</v>
+      </c>
+      <c r="E110" s="2">
+        <v>-0.48</v>
+      </c>
+      <c r="F110" s="1">
+        <v>69216</v>
+      </c>
+      <c r="G110" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>110</v>
+      </c>
+      <c r="B111" t="str">
+        <v>Nhpc Limited</v>
+      </c>
+      <c r="C111" t="str">
+        <v>NHPC</v>
+      </c>
+      <c r="D111" s="1">
+        <v>72.63</v>
+      </c>
+      <c r="E111" s="2">
+        <v>-0.49</v>
+      </c>
+      <c r="F111" s="1">
+        <v>1270613</v>
+      </c>
+      <c r="G111" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>111</v>
+      </c>
+      <c r="B112" t="str">
+        <v>Hindalco Industries Limited</v>
+      </c>
+      <c r="C112" t="str">
+        <v>HINDALCO</v>
+      </c>
+      <c r="D112" s="1">
+        <v>895.45</v>
+      </c>
+      <c r="E112" s="2">
+        <v>-0.54</v>
+      </c>
+      <c r="F112" s="1">
+        <v>768519</v>
+      </c>
+      <c r="G112" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>112</v>
+      </c>
+      <c r="B113" t="str">
+        <v>Sagility India Ltd</v>
+      </c>
+      <c r="C113" t="str">
+        <v>SAGILITY</v>
+      </c>
+      <c r="D113" s="1">
+        <v>43.76</v>
+      </c>
+      <c r="E113" s="2">
+        <v>-0.55</v>
+      </c>
+      <c r="F113" s="1">
+        <v>1950154</v>
+      </c>
+      <c r="G113" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>113</v>
+      </c>
+      <c r="B114" t="str">
+        <v>Coal India Limited</v>
+      </c>
+      <c r="C114" t="str">
+        <v>COALINDIA</v>
+      </c>
+      <c r="D114" s="1">
+        <v>409.05</v>
+      </c>
+      <c r="E114" s="2">
+        <v>-0.61</v>
+      </c>
+      <c r="F114" s="1">
+        <v>523739</v>
+      </c>
+      <c r="G114" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>114</v>
+      </c>
+      <c r="B115" t="str">
+        <v>Ambuja Cements Limited</v>
+      </c>
+      <c r="C115" t="str">
+        <v>AMBUJACEM</v>
+      </c>
+      <c r="D115" s="1">
+        <v>349.35</v>
+      </c>
+      <c r="E115" s="2">
+        <v>-0.61</v>
+      </c>
+      <c r="F115" s="1">
+        <v>635153</v>
+      </c>
+      <c r="G115" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>115</v>
+      </c>
+      <c r="B116" t="str">
+        <v>Apollo Hospitals Enterprise Limited</v>
+      </c>
+      <c r="C116" t="str">
+        <v>APOLLOHOSP</v>
+      </c>
+      <c r="D116" s="1">
+        <v>7978</v>
+      </c>
+      <c r="E116" s="2">
+        <v>-0.62</v>
+      </c>
+      <c r="F116" s="1">
+        <v>258835</v>
+      </c>
+      <c r="G116" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>116</v>
+      </c>
+      <c r="B117" t="str">
+        <v>Nmdc Limited</v>
+      </c>
+      <c r="C117" t="str">
+        <v>NMDC</v>
+      </c>
+      <c r="D117" s="1">
+        <v>71.35</v>
+      </c>
+      <c r="E117" s="2">
+        <v>-0.63</v>
+      </c>
+      <c r="F117" s="1">
+        <v>4615481</v>
+      </c>
+      <c r="G117" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>117</v>
+      </c>
+      <c r="B118" t="str">
+        <v>Reliance Industries Limited</v>
+      </c>
+      <c r="C118" t="str">
+        <v>RELIANCE</v>
+      </c>
+      <c r="D118" s="1">
+        <v>1162.7</v>
+      </c>
+      <c r="E118" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="F118" s="1">
+        <v>3246642</v>
+      </c>
+      <c r="G118" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>118</v>
+      </c>
+      <c r="B119" t="str">
+        <v>Varun Beverages Limited</v>
+      </c>
+      <c r="C119" t="str">
+        <v>VBL</v>
+      </c>
+      <c r="D119" s="1">
+        <v>438.15</v>
+      </c>
+      <c r="E119" s="2">
+        <v>-0.65</v>
+      </c>
+      <c r="F119" s="1">
+        <v>1015791</v>
+      </c>
+      <c r="G119" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>119</v>
+      </c>
+      <c r="B120" t="str">
+        <v>Pidilite Industries Limited</v>
+      </c>
+      <c r="C120" t="str">
+        <v>PIDILITIND</v>
+      </c>
+      <c r="D120" s="1">
+        <v>1472</v>
+      </c>
+      <c r="E120" s="2">
+        <v>-0.67</v>
+      </c>
+      <c r="F120" s="1">
+        <v>187352</v>
+      </c>
+      <c r="G120" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>120</v>
+      </c>
+      <c r="B121" t="str">
+        <v>BANKNIFTY</v>
+      </c>
+      <c r="C121" t="str">
+        <v>BANKNIFTY</v>
+      </c>
+      <c r="D121" s="1">
+        <v>54875</v>
+      </c>
+      <c r="E121" s="2">
+        <v>-0.69</v>
+      </c>
+      <c r="F121" s="1">
+        <v>0</v>
+      </c>
+      <c r="G121" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>121</v>
+      </c>
+      <c r="B122" t="str">
+        <v>Biocon Limited</v>
+      </c>
+      <c r="C122" t="str">
+        <v>BIOCON</v>
+      </c>
+      <c r="D122" s="1">
+        <v>346.95</v>
+      </c>
+      <c r="E122" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="F122" s="1">
+        <v>558267</v>
+      </c>
+      <c r="G122" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>122</v>
+      </c>
+      <c r="B123" t="str">
+        <v>Oil &amp; Natural Gas Corporation Limited</v>
+      </c>
+      <c r="C123" t="str">
+        <v>ONGC</v>
+      </c>
+      <c r="D123" s="1">
+        <v>219.72</v>
+      </c>
+      <c r="E123" s="2">
+        <v>-0.7</v>
+      </c>
+      <c r="F123" s="1">
+        <v>2016053</v>
+      </c>
+      <c r="G123" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>123</v>
+      </c>
+      <c r="B124" t="str">
+        <v>Adani Power Limited</v>
+      </c>
+      <c r="C124" t="str">
+        <v>ADANIPOWER</v>
+      </c>
+      <c r="D124" s="1">
+        <v>187.65</v>
+      </c>
+      <c r="E124" s="2">
+        <v>-0.71</v>
+      </c>
+      <c r="F124" s="1">
+        <v>5758954</v>
+      </c>
+      <c r="G124" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>124</v>
+      </c>
+      <c r="B125" t="str">
+        <v>Britannia Industries Limited</v>
+      </c>
+      <c r="C125" t="str">
+        <v>BRITANNIA</v>
+      </c>
+      <c r="D125" s="1">
+        <v>4788.4</v>
+      </c>
+      <c r="E125" s="2">
+        <v>-0.76</v>
+      </c>
+      <c r="F125" s="1">
+        <v>12448</v>
+      </c>
+      <c r="G125" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>125</v>
+      </c>
+      <c r="B126" t="str">
+        <v>Axis Bank Limited</v>
+      </c>
+      <c r="C126" t="str">
+        <v>AXISBANK</v>
+      </c>
+      <c r="D126" s="1">
+        <v>1249.5</v>
+      </c>
+      <c r="E126" s="2">
+        <v>-0.76</v>
+      </c>
+      <c r="F126" s="1">
+        <v>2035872</v>
+      </c>
+      <c r="G126" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>126</v>
+      </c>
+      <c r="B127" t="str">
+        <v>Yes Bank Limited</v>
+      </c>
+      <c r="C127" t="str">
+        <v>YESBANK</v>
+      </c>
+      <c r="D127" s="1">
+        <v>20.34</v>
+      </c>
+      <c r="E127" s="2">
+        <v>-0.78</v>
+      </c>
+      <c r="F127" s="1">
+        <v>24727698</v>
+      </c>
+      <c r="G127" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>127</v>
+      </c>
+      <c r="B128" t="str">
+        <v>Indian Bank Ltd</v>
+      </c>
+      <c r="C128" t="str">
+        <v>INDIANB</v>
+      </c>
+      <c r="D128" s="1">
+        <v>823.15</v>
+      </c>
+      <c r="E128" s="2">
+        <v>-0.8</v>
+      </c>
+      <c r="F128" s="1">
+        <v>205942</v>
+      </c>
+      <c r="G128" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>128</v>
+      </c>
+      <c r="B129" t="str">
+        <v>Marico Limited</v>
+      </c>
+      <c r="C129" t="str">
+        <v>MARICO</v>
+      </c>
+      <c r="D129" s="1">
+        <v>779.65</v>
+      </c>
+      <c r="E129" s="2">
+        <v>-0.83</v>
+      </c>
+      <c r="F129" s="1">
+        <v>228041</v>
+      </c>
+      <c r="G129" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>129</v>
+      </c>
+      <c r="B130" t="str">
+        <v>Life Insurance Corporation of India Ltd</v>
+      </c>
+      <c r="C130" t="str">
+        <v>LICI</v>
+      </c>
+      <c r="D130" s="1">
+        <v>390.95</v>
+      </c>
+      <c r="E130" s="2">
+        <v>-0.84</v>
+      </c>
+      <c r="F130" s="1">
+        <v>1141131</v>
+      </c>
+      <c r="G130" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>130</v>
+      </c>
+      <c r="B131" t="str">
+        <v>Bank Of Baroda Ltd</v>
+      </c>
+      <c r="C131" t="str">
+        <v>BANKBARODA</v>
+      </c>
+      <c r="D131" s="1">
+        <v>233.8</v>
+      </c>
+      <c r="E131" s="2">
+        <v>-0.85</v>
+      </c>
+      <c r="F131" s="1">
+        <v>1124252</v>
+      </c>
+      <c r="G131" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>131</v>
+      </c>
+      <c r="B132" t="str">
+        <v>Fortis Healthcare Limited</v>
+      </c>
+      <c r="C132" t="str">
+        <v>FORTIS</v>
+      </c>
+      <c r="D132" s="1">
+        <v>779.2</v>
+      </c>
+      <c r="E132" s="2">
+        <v>-0.9</v>
+      </c>
+      <c r="F132" s="1">
+        <v>165258</v>
+      </c>
+      <c r="G132" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>132</v>
+      </c>
+      <c r="B133" t="str">
+        <v>Larsen &amp; Toubro Limited</v>
+      </c>
+      <c r="C133" t="str">
+        <v>LT</v>
+      </c>
+      <c r="D133" s="1">
+        <v>3669.5</v>
+      </c>
+      <c r="E133" s="2">
+        <v>-0.91</v>
+      </c>
+      <c r="F133" s="1">
+        <v>233863</v>
+      </c>
+      <c r="G133" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>133</v>
+      </c>
+      <c r="B134" t="str">
+        <v>Colgate Palmolive (india) Limited</v>
+      </c>
+      <c r="C134" t="str">
+        <v>COLPAL</v>
+      </c>
+      <c r="D134" s="1">
+        <v>1801.2</v>
+      </c>
+      <c r="E134" s="2">
+        <v>-0.91</v>
+      </c>
+      <c r="F134" s="1">
+        <v>123331</v>
+      </c>
+      <c r="G134" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>134</v>
+      </c>
+      <c r="B135" t="str">
+        <v>Patanjali Foods Ltd</v>
+      </c>
+      <c r="C135" t="str">
+        <v>PATANJALI</v>
+      </c>
+      <c r="D135" s="1">
+        <v>357.15</v>
+      </c>
+      <c r="E135" s="2">
+        <v>-0.92</v>
+      </c>
+      <c r="F135" s="1">
+        <v>651653</v>
+      </c>
+      <c r="G135" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>135</v>
+      </c>
+      <c r="B136" t="str">
+        <v>Icici Bank Limited</v>
+      </c>
+      <c r="C136" t="str">
+        <v>ICICIBANK</v>
+      </c>
+      <c r="D136" s="1">
+        <v>1342</v>
+      </c>
+      <c r="E136" s="2">
+        <v>-0.96</v>
+      </c>
+      <c r="F136" s="1">
+        <v>3282871</v>
+      </c>
+      <c r="G136" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>136</v>
+      </c>
+      <c r="B137" t="str">
+        <v>Srf Limited</v>
+      </c>
+      <c r="C137" t="str">
+        <v>SRF</v>
+      </c>
+      <c r="D137" s="1">
+        <v>2495</v>
+      </c>
+      <c r="E137" s="2">
+        <v>-0.97</v>
+      </c>
+      <c r="F137" s="1">
+        <v>28696</v>
+      </c>
+      <c r="G137" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>137</v>
+      </c>
+      <c r="B138" t="str">
+        <v>Hindustan Unilever Limited</v>
+      </c>
+      <c r="C138" t="str">
+        <v>HINDUNILVR</v>
+      </c>
+      <c r="D138" s="1">
+        <v>1838.5</v>
+      </c>
+      <c r="E138" s="2">
+        <v>-0.98</v>
+      </c>
+      <c r="F138" s="1">
+        <v>309075</v>
+      </c>
+      <c r="G138" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139">
+        <v>138</v>
+      </c>
+      <c r="B139" t="str">
+        <v>Canara Bank Ltd</v>
+      </c>
+      <c r="C139" t="str">
+        <v>CANBK</v>
+      </c>
+      <c r="D139" s="1">
+        <v>118.35</v>
+      </c>
+      <c r="E139" s="2">
+        <v>-1.04</v>
+      </c>
+      <c r="F139" s="1">
+        <v>3711831</v>
+      </c>
+      <c r="G139" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140">
+        <v>139</v>
+      </c>
+      <c r="B140" t="str">
+        <v>Indus Towers Ltd (Bharti Infratel)</v>
+      </c>
+      <c r="C140" t="str">
+        <v>INDUSTOWER</v>
+      </c>
+      <c r="D140" s="1">
+        <v>376.7</v>
+      </c>
+      <c r="E140" s="2">
+        <v>-1.09</v>
+      </c>
+      <c r="F140" s="1">
+        <v>974392</v>
+      </c>
+      <c r="G140" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141">
+        <v>140</v>
+      </c>
+      <c r="B141" t="str">
+        <v>Bank Of India Ltd</v>
+      </c>
+      <c r="C141" t="str">
+        <v>BANKINDIA</v>
+      </c>
+      <c r="D141" s="1">
+        <v>132.75</v>
+      </c>
+      <c r="E141" s="2">
+        <v>-1.27</v>
+      </c>
+      <c r="F141" s="1">
+        <v>2947517</v>
+      </c>
+      <c r="G141" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142">
+        <v>141</v>
+      </c>
+      <c r="B142" t="str">
+        <v>Dabur India Limited</v>
+      </c>
+      <c r="C142" t="str">
+        <v>DABUR</v>
+      </c>
+      <c r="D142" s="1">
+        <v>381.45</v>
+      </c>
+      <c r="E142" s="2">
+        <v>-1.36</v>
+      </c>
+      <c r="F142" s="1">
+        <v>194550</v>
+      </c>
+      <c r="G142" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143">
+        <v>142</v>
+      </c>
+      <c r="B143" t="str">
+        <v>Union Bank Of India Ltd</v>
+      </c>
+      <c r="C143" t="str">
+        <v>UNIONBANK</v>
+      </c>
+      <c r="D143" s="1">
+        <v>170.7</v>
+      </c>
+      <c r="E143" s="2">
+        <v>-1.36</v>
+      </c>
+      <c r="F143" s="1">
+        <v>2101493</v>
+      </c>
+      <c r="G143" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144">
+        <v>143</v>
+      </c>
+      <c r="B144" t="str">
+        <v>Ntpc Limited</v>
+      </c>
+      <c r="C144" t="str">
+        <v>NTPC</v>
+      </c>
+      <c r="D144" s="1">
+        <v>307.4</v>
+      </c>
+      <c r="E144" s="2">
+        <v>-1.47</v>
+      </c>
+      <c r="F144" s="1">
+        <v>3661773</v>
+      </c>
+      <c r="G144" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145">
+        <v>144</v>
+      </c>
+      <c r="B145" t="str">
+        <v>Bharti Airtel Limited</v>
+      </c>
+      <c r="C145" t="str">
+        <v>BHARTIARTL</v>
+      </c>
+      <c r="D145" s="1">
+        <v>1773.1</v>
+      </c>
+      <c r="E145" s="2">
+        <v>-1.77</v>
+      </c>
+      <c r="F145" s="1">
+        <v>2055425</v>
+      </c>
+      <c r="G145" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146">
+        <v>145</v>
+      </c>
+      <c r="B146" t="str">
+        <v>State Bank Of India Ltd</v>
+      </c>
+      <c r="C146" t="str">
+        <v>SBIN</v>
+      </c>
+      <c r="D146" s="1">
+        <v>940.9</v>
+      </c>
+      <c r="E146" s="2">
+        <v>-1.9</v>
+      </c>
+      <c r="F146" s="1">
+        <v>2453218</v>
+      </c>
+      <c r="G146" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147">
+        <v>146</v>
+      </c>
+      <c r="B147" t="str">
+        <v>Itc Limited</v>
+      </c>
+      <c r="C147" t="str">
+        <v>ITC</v>
+      </c>
+      <c r="D147" s="1">
+        <v>259.95</v>
+      </c>
+      <c r="E147" s="2">
+        <v>-2.27</v>
+      </c>
+      <c r="F147" s="1">
+        <v>4721248</v>
+      </c>
+      <c r="G147" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148">
+        <v>147</v>
+      </c>
+      <c r="B148" t="str">
+        <v>GMR Airports Ltd</v>
+      </c>
+      <c r="C148" t="str">
+        <v>GMRAIRPORT</v>
+      </c>
+      <c r="D148" s="1">
+        <v>90.17</v>
+      </c>
+      <c r="E148" s="2">
+        <v>-2.32</v>
+      </c>
+      <c r="F148" s="1">
+        <v>5233987</v>
+      </c>
+      <c r="G148" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149">
+        <v>148</v>
+      </c>
+      <c r="B149" t="str">
+        <v>Avenue Supermarts Ltd</v>
+      </c>
+      <c r="C149" t="str">
+        <v>DMART</v>
+      </c>
+      <c r="D149" s="1">
+        <v>3417.4</v>
+      </c>
+      <c r="E149" s="2">
+        <v>-2.83</v>
+      </c>
+      <c r="F149" s="1">
+        <v>1605429</v>
+      </c>
+      <c r="G149" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150">
+        <v>149</v>
+      </c>
+      <c r="B150" t="str">
+        <v>Tech Mahindra Limited</v>
+      </c>
+      <c r="C150" t="str">
+        <v>TECHM</v>
+      </c>
+      <c r="D150" s="1">
+        <v>1464.3</v>
+      </c>
+      <c r="E150" s="2">
+        <v>-3.29</v>
+      </c>
+      <c r="F150" s="1">
+        <v>1966286</v>
+      </c>
+      <c r="G150" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G67"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G150"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/down.xlsx
+++ b/down.xlsx
@@ -401,7 +401,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G150"/>
+  <dimension ref="A1:J143"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -423,6 +423,15 @@
         <v>volume</v>
       </c>
       <c r="G1" t="str">
+        <v>200 DMA</v>
+      </c>
+      <c r="H1" t="str">
+        <v>EMA10</v>
+      </c>
+      <c r="I1" t="str">
+        <v>SMA50</v>
+      </c>
+      <c r="J1" t="str">
         <v>Add Column</v>
       </c>
     </row>
@@ -431,21 +440,30 @@
         <v>1</v>
       </c>
       <c r="B2" t="str">
-        <v>Delhivery Ltd</v>
+        <v>Bandhan Bank Ltd</v>
       </c>
       <c r="C2" t="str">
-        <v>DELHIVERY</v>
+        <v>BANDHANBNK</v>
       </c>
       <c r="D2" s="1">
-        <v>420.75</v>
+        <v>172</v>
       </c>
       <c r="E2" s="2">
-        <v>5.06</v>
+        <v>9.21</v>
       </c>
       <c r="F2" s="1">
-        <v>5183677</v>
-      </c>
-      <c r="G2" t="str">
+        <v>51524125</v>
+      </c>
+      <c r="G2" s="1">
+        <v>176.3</v>
+      </c>
+      <c r="H2" s="1">
+        <v>166.89</v>
+      </c>
+      <c r="I2" s="1">
+        <v>172.26</v>
+      </c>
+      <c r="J2" t="str">
         <v/>
       </c>
     </row>
@@ -454,21 +472,30 @@
         <v>2</v>
       </c>
       <c r="B3" t="str">
-        <v>Suzlon Energy Limited</v>
+        <v>Hcl Technologies Limited</v>
       </c>
       <c r="C3" t="str">
-        <v>SUZLON</v>
+        <v>HCLTECH</v>
       </c>
       <c r="D3" s="1">
-        <v>39.17</v>
+        <v>1326</v>
       </c>
       <c r="E3" s="2">
-        <v>4.18</v>
+        <v>8.42</v>
       </c>
       <c r="F3" s="1">
-        <v>62356958</v>
-      </c>
-      <c r="G3" t="str">
+        <v>21500714</v>
+      </c>
+      <c r="G3" s="1">
+        <v>1340.07</v>
+      </c>
+      <c r="H3" s="1">
+        <v>1236.65</v>
+      </c>
+      <c r="I3" s="1">
+        <v>1286.51</v>
+      </c>
+      <c r="J3" t="str">
         <v/>
       </c>
     </row>
@@ -477,21 +504,30 @@
         <v>3</v>
       </c>
       <c r="B4" t="str">
-        <v>Tata Elxsi Limited</v>
+        <v>KPIT Technologies Ltd</v>
       </c>
       <c r="C4" t="str">
-        <v>TATAELXSI</v>
+        <v>KPITTECH</v>
       </c>
       <c r="D4" s="1">
-        <v>3251.9</v>
+        <v>513.75</v>
       </c>
       <c r="E4" s="2">
-        <v>3.89</v>
+        <v>6.81</v>
       </c>
       <c r="F4" s="1">
-        <v>389873</v>
-      </c>
-      <c r="G4" t="str">
+        <v>6095949</v>
+      </c>
+      <c r="G4" s="1">
+        <v>742.34</v>
+      </c>
+      <c r="H4" s="1">
+        <v>496.31</v>
+      </c>
+      <c r="I4" s="1">
+        <v>562.64</v>
+      </c>
+      <c r="J4" t="str">
         <v/>
       </c>
     </row>
@@ -500,21 +536,30 @@
         <v>4</v>
       </c>
       <c r="B5" t="str">
-        <v>Indian Railway Finance Corporation Ltd</v>
+        <v>Tata Consultancy Services Limited</v>
       </c>
       <c r="C5" t="str">
-        <v>IRFC</v>
+        <v>TCS</v>
       </c>
       <c r="D5" s="1">
-        <v>77.2</v>
+        <v>2269.3</v>
       </c>
       <c r="E5" s="2">
-        <v>3.35</v>
+        <v>6.79</v>
       </c>
       <c r="F5" s="1">
-        <v>7531260</v>
-      </c>
-      <c r="G5" t="str">
+        <v>10608917</v>
+      </c>
+      <c r="G5" s="1">
+        <v>2479.57</v>
+      </c>
+      <c r="H5" s="1">
+        <v>2136.55</v>
+      </c>
+      <c r="I5" s="1">
+        <v>2246.16</v>
+      </c>
+      <c r="J5" t="str">
         <v/>
       </c>
     </row>
@@ -523,21 +568,30 @@
         <v>5</v>
       </c>
       <c r="B6" t="str">
-        <v>Bajaj Auto Limited</v>
+        <v>Shriram Finance Ltd</v>
       </c>
       <c r="C6" t="str">
-        <v>BAJAJ-AUTO</v>
+        <v>SHRIRAMFIN</v>
       </c>
       <c r="D6" s="1">
-        <v>10080</v>
+        <v>988</v>
       </c>
       <c r="E6" s="2">
-        <v>3.09</v>
+        <v>6.31</v>
       </c>
       <c r="F6" s="1">
-        <v>182806</v>
-      </c>
-      <c r="G6" t="str">
+        <v>7934105</v>
+      </c>
+      <c r="G6" s="1">
+        <v>1009.03</v>
+      </c>
+      <c r="H6" s="1">
+        <v>959.94</v>
+      </c>
+      <c r="I6" s="1">
+        <v>1046.54</v>
+      </c>
+      <c r="J6" t="str">
         <v/>
       </c>
     </row>
@@ -546,21 +600,30 @@
         <v>6</v>
       </c>
       <c r="B7" t="str">
-        <v>Tube Investments of India Ltd</v>
+        <v>Tata Elxsi Limited</v>
       </c>
       <c r="C7" t="str">
-        <v>TIINDIA</v>
+        <v>TATAELXSI</v>
       </c>
       <c r="D7" s="1">
-        <v>2278.3</v>
+        <v>3426.7</v>
       </c>
       <c r="E7" s="2">
-        <v>2.95</v>
+        <v>5.21</v>
       </c>
       <c r="F7" s="1">
-        <v>254201</v>
-      </c>
-      <c r="G7" t="str">
+        <v>1034747</v>
+      </c>
+      <c r="G7" s="1">
+        <v>4218.11</v>
+      </c>
+      <c r="H7" s="1">
+        <v>3199.61</v>
+      </c>
+      <c r="I7" s="1">
+        <v>3474.42</v>
+      </c>
+      <c r="J7" t="str">
         <v/>
       </c>
     </row>
@@ -569,21 +632,30 @@
         <v>7</v>
       </c>
       <c r="B8" t="str">
-        <v>Mazagon Dock Shipbuilders Ltd</v>
+        <v>LTIMindtree Ltd</v>
       </c>
       <c r="C8" t="str">
-        <v>MAZDOCK</v>
+        <v>LTM</v>
       </c>
       <c r="D8" s="1">
-        <v>2064</v>
+        <v>4215</v>
       </c>
       <c r="E8" s="2">
-        <v>2.69</v>
+        <v>4.88</v>
       </c>
       <c r="F8" s="1">
-        <v>347192</v>
-      </c>
-      <c r="G8" t="str">
+        <v>497168</v>
+      </c>
+      <c r="G8" s="1">
+        <v>4583.57</v>
+      </c>
+      <c r="H8" s="1">
+        <v>4058.97</v>
+      </c>
+      <c r="I8" s="1">
+        <v>4382.56</v>
+      </c>
+      <c r="J8" t="str">
         <v/>
       </c>
     </row>
@@ -592,21 +664,30 @@
         <v>8</v>
       </c>
       <c r="B9" t="str">
-        <v>PB Fintech Ltd</v>
+        <v>Mazagon Dock Shipbuilders Ltd</v>
       </c>
       <c r="C9" t="str">
-        <v>POLICYBZR</v>
+        <v>MAZDOCK</v>
       </c>
       <c r="D9" s="1">
-        <v>1037</v>
+        <v>2120</v>
       </c>
       <c r="E9" s="2">
-        <v>2.47</v>
+        <v>4.59</v>
       </c>
       <c r="F9" s="1">
-        <v>709680</v>
-      </c>
-      <c r="G9" t="str">
+        <v>838975</v>
+      </c>
+      <c r="G9" s="1">
+        <v>2419.62</v>
+      </c>
+      <c r="H9" s="1">
+        <v>2082.79</v>
+      </c>
+      <c r="I9" s="1">
+        <v>2360.34</v>
+      </c>
+      <c r="J9" t="str">
         <v/>
       </c>
     </row>
@@ -615,21 +696,30 @@
         <v>9</v>
       </c>
       <c r="B10" t="str">
-        <v>Nbcc (india) Limited</v>
+        <v>Waaree Energies Ltd</v>
       </c>
       <c r="C10" t="str">
-        <v>NBCC</v>
+        <v>WAAREEENER</v>
       </c>
       <c r="D10" s="1">
-        <v>76.3</v>
+        <v>2451</v>
       </c>
       <c r="E10" s="2">
-        <v>2.47</v>
+        <v>4.52</v>
       </c>
       <c r="F10" s="1">
-        <v>2884837</v>
-      </c>
-      <c r="G10" t="str">
+        <v>1105841</v>
+      </c>
+      <c r="G10" s="1">
+        <v>2863.78</v>
+      </c>
+      <c r="H10" s="1">
+        <v>2390.59</v>
+      </c>
+      <c r="I10" s="1">
+        <v>2562.75</v>
+      </c>
+      <c r="J10" t="str">
         <v/>
       </c>
     </row>
@@ -638,21 +728,30 @@
         <v>10</v>
       </c>
       <c r="B11" t="str">
-        <v>Dr. Reddy's Laboratories Limited</v>
+        <v>Wipro Limited</v>
       </c>
       <c r="C11" t="str">
-        <v>DRREDDY</v>
+        <v>WIPRO</v>
       </c>
       <c r="D11" s="1">
-        <v>1223.6</v>
+        <v>169</v>
       </c>
       <c r="E11" s="2">
-        <v>2.22</v>
+        <v>4.45</v>
       </c>
       <c r="F11" s="1">
-        <v>364106</v>
-      </c>
-      <c r="G11" t="str">
+        <v>18836244</v>
+      </c>
+      <c r="G11" s="1">
+        <v>198.29</v>
+      </c>
+      <c r="H11" s="1">
+        <v>162.82</v>
+      </c>
+      <c r="I11" s="1">
+        <v>173.19</v>
+      </c>
+      <c r="J11" t="str">
         <v/>
       </c>
     </row>
@@ -661,21 +760,30 @@
         <v>11</v>
       </c>
       <c r="B12" t="str">
-        <v>Rail Vikas Nigam Ltd</v>
+        <v>Crompton Greaves Consumer Electricals Limited</v>
       </c>
       <c r="C12" t="str">
-        <v>RVNL</v>
+        <v>CROMPTON</v>
       </c>
       <c r="D12" s="1">
-        <v>194.5</v>
+        <v>211.5</v>
       </c>
       <c r="E12" s="2">
-        <v>2.02</v>
+        <v>4.44</v>
       </c>
       <c r="F12" s="1">
-        <v>1928951</v>
-      </c>
-      <c r="G12" t="str">
+        <v>9726864</v>
+      </c>
+      <c r="G12" s="1">
+        <v>252.21</v>
+      </c>
+      <c r="H12" s="1">
+        <v>209.68</v>
+      </c>
+      <c r="I12" s="1">
+        <v>232.24</v>
+      </c>
+      <c r="J12" t="str">
         <v/>
       </c>
     </row>
@@ -684,21 +792,30 @@
         <v>12</v>
       </c>
       <c r="B13" t="str">
-        <v>Kei Industries Limited</v>
+        <v>Infosys Limited</v>
       </c>
       <c r="C13" t="str">
-        <v>KEI</v>
+        <v>INFY</v>
       </c>
       <c r="D13" s="1">
-        <v>4674.5</v>
+        <v>1062.1</v>
       </c>
       <c r="E13" s="2">
-        <v>1.95</v>
+        <v>4.13</v>
       </c>
       <c r="F13" s="1">
-        <v>96397</v>
-      </c>
-      <c r="G13" t="str">
+        <v>21269738</v>
+      </c>
+      <c r="G13" s="1">
+        <v>1245.01</v>
+      </c>
+      <c r="H13" s="1">
+        <v>1024.08</v>
+      </c>
+      <c r="I13" s="1">
+        <v>1090.51</v>
+      </c>
+      <c r="J13" t="str">
         <v/>
       </c>
     </row>
@@ -707,21 +824,30 @@
         <v>13</v>
       </c>
       <c r="B14" t="str">
-        <v>Hindustan Petroleum Corporation Limited</v>
+        <v>Inox Wind Limited</v>
       </c>
       <c r="C14" t="str">
-        <v>HINDPETRO</v>
+        <v>INOXWIND</v>
       </c>
       <c r="D14" s="1">
-        <v>332.3</v>
+        <v>69.94</v>
       </c>
       <c r="E14" s="2">
-        <v>1.93</v>
+        <v>4.12</v>
       </c>
       <c r="F14" s="1">
-        <v>1219737</v>
-      </c>
-      <c r="G14" t="str">
+        <v>10757947</v>
+      </c>
+      <c r="G14" s="1">
+        <v>89.77</v>
+      </c>
+      <c r="H14" s="1">
+        <v>68.55</v>
+      </c>
+      <c r="I14" s="1">
+        <v>73.43</v>
+      </c>
+      <c r="J14" t="str">
         <v/>
       </c>
     </row>
@@ -730,21 +856,30 @@
         <v>14</v>
       </c>
       <c r="B15" t="str">
-        <v>Astral Ltd</v>
+        <v>Indian Renewable Energy Development Agency Ltd</v>
       </c>
       <c r="C15" t="str">
-        <v>ASTRAL</v>
+        <v>IREDA</v>
       </c>
       <c r="D15" s="1">
-        <v>1435.9</v>
+        <v>108.39</v>
       </c>
       <c r="E15" s="2">
-        <v>1.85</v>
+        <v>3.62</v>
       </c>
       <c r="F15" s="1">
-        <v>111440</v>
-      </c>
-      <c r="G15" t="str">
+        <v>5511468</v>
+      </c>
+      <c r="G15" s="1">
+        <v>123.65</v>
+      </c>
+      <c r="H15" s="1">
+        <v>107.69</v>
+      </c>
+      <c r="I15" s="1">
+        <v>113.67</v>
+      </c>
+      <c r="J15" t="str">
         <v/>
       </c>
     </row>
@@ -753,21 +888,30 @@
         <v>15</v>
       </c>
       <c r="B16" t="str">
-        <v>Cochin Shipyard Ltd</v>
+        <v>Bharat Dynamics Ltd</v>
       </c>
       <c r="C16" t="str">
-        <v>COCHINSHIP</v>
+        <v>BDL</v>
       </c>
       <c r="D16" s="1">
-        <v>1252.7</v>
+        <v>1125.9</v>
       </c>
       <c r="E16" s="2">
-        <v>1.85</v>
+        <v>3.39</v>
       </c>
       <c r="F16" s="1">
-        <v>418499</v>
-      </c>
-      <c r="G16" t="str">
+        <v>796654</v>
+      </c>
+      <c r="G16" s="1">
+        <v>1308.25</v>
+      </c>
+      <c r="H16" s="1">
+        <v>1101.45</v>
+      </c>
+      <c r="I16" s="1">
+        <v>1229.14</v>
+      </c>
+      <c r="J16" t="str">
         <v/>
       </c>
     </row>
@@ -776,21 +920,30 @@
         <v>16</v>
       </c>
       <c r="B17" t="str">
-        <v>L&amp;T Finance Ltd</v>
+        <v>Indian Bank Ltd</v>
       </c>
       <c r="C17" t="str">
-        <v>LTF</v>
+        <v>INDIANB</v>
       </c>
       <c r="D17" s="1">
-        <v>265.85</v>
+        <v>841.55</v>
       </c>
       <c r="E17" s="2">
-        <v>1.78</v>
+        <v>3.37</v>
       </c>
       <c r="F17" s="1">
-        <v>904964</v>
-      </c>
-      <c r="G17" t="str">
+        <v>2281494</v>
+      </c>
+      <c r="G17" s="1">
+        <v>863.07</v>
+      </c>
+      <c r="H17" s="1">
+        <v>822.2</v>
+      </c>
+      <c r="I17" s="1">
+        <v>854.99</v>
+      </c>
+      <c r="J17" t="str">
         <v/>
       </c>
     </row>
@@ -799,21 +952,30 @@
         <v>17</v>
       </c>
       <c r="B18" t="str">
-        <v>Bharat Dynamics Ltd</v>
+        <v>National Aluminium Company Limited</v>
       </c>
       <c r="C18" t="str">
-        <v>BDL</v>
+        <v>NATIONALUM</v>
       </c>
       <c r="D18" s="1">
-        <v>1094.3</v>
+        <v>321</v>
       </c>
       <c r="E18" s="2">
-        <v>1.71</v>
+        <v>3.28</v>
       </c>
       <c r="F18" s="1">
-        <v>263332</v>
-      </c>
-      <c r="G18" t="str">
+        <v>4688752</v>
+      </c>
+      <c r="G18" s="1">
+        <v>372.53</v>
+      </c>
+      <c r="H18" s="1">
+        <v>327.24</v>
+      </c>
+      <c r="I18" s="1">
+        <v>366.65</v>
+      </c>
+      <c r="J18" t="str">
         <v/>
       </c>
     </row>
@@ -822,21 +984,30 @@
         <v>18</v>
       </c>
       <c r="B19" t="str">
-        <v>REC Ltd</v>
+        <v>Godfrey Phillips India Limited</v>
       </c>
       <c r="C19" t="str">
-        <v>RECLTD</v>
+        <v>GODFRYPHLP</v>
       </c>
       <c r="D19" s="1">
-        <v>305</v>
+        <v>1850</v>
       </c>
       <c r="E19" s="2">
-        <v>1.67</v>
+        <v>3.25</v>
       </c>
       <c r="F19" s="1">
-        <v>2140161</v>
-      </c>
-      <c r="G19" t="str">
+        <v>162552</v>
+      </c>
+      <c r="G19" s="1">
+        <v>2146.17</v>
+      </c>
+      <c r="H19" s="1">
+        <v>1853.01</v>
+      </c>
+      <c r="I19" s="1">
+        <v>2040.1</v>
+      </c>
+      <c r="J19" t="str">
         <v/>
       </c>
     </row>
@@ -845,21 +1016,30 @@
         <v>19</v>
       </c>
       <c r="B20" t="str">
-        <v>Amber Enterprises India Ltd</v>
+        <v>Computer Age Management Services Ltd</v>
       </c>
       <c r="C20" t="str">
-        <v>AMBER</v>
+        <v>CAMS</v>
       </c>
       <c r="D20" s="1">
-        <v>6551</v>
+        <v>701</v>
       </c>
       <c r="E20" s="2">
-        <v>1.64</v>
+        <v>3.23</v>
       </c>
       <c r="F20" s="1">
-        <v>50540</v>
-      </c>
-      <c r="G20" t="str">
+        <v>1582114</v>
+      </c>
+      <c r="G20" s="1">
+        <v>737.44</v>
+      </c>
+      <c r="H20" s="1">
+        <v>686.49</v>
+      </c>
+      <c r="I20" s="1">
+        <v>734</v>
+      </c>
+      <c r="J20" t="str">
         <v/>
       </c>
     </row>
@@ -868,21 +1048,30 @@
         <v>20</v>
       </c>
       <c r="B21" t="str">
-        <v>Bandhan Bank Ltd</v>
+        <v>Godrej Properties Limited</v>
       </c>
       <c r="C21" t="str">
-        <v>BANDHANBNK</v>
+        <v>GODREJPROP</v>
       </c>
       <c r="D21" s="1">
-        <v>159.53</v>
+        <v>1594.3</v>
       </c>
       <c r="E21" s="2">
-        <v>1.61</v>
+        <v>3.22</v>
       </c>
       <c r="F21" s="1">
-        <v>3719452</v>
-      </c>
-      <c r="G21" t="str">
+        <v>364591</v>
+      </c>
+      <c r="G21" s="1">
+        <v>1819.39</v>
+      </c>
+      <c r="H21" s="1">
+        <v>1594.45</v>
+      </c>
+      <c r="I21" s="1">
+        <v>1857.06</v>
+      </c>
+      <c r="J21" t="str">
         <v/>
       </c>
     </row>
@@ -891,21 +1080,30 @@
         <v>21</v>
       </c>
       <c r="B22" t="str">
-        <v>Bharat Electronics Limited</v>
+        <v>Hindustan Unilever Limited</v>
       </c>
       <c r="C22" t="str">
-        <v>BEL</v>
+        <v>HINDUNILVR</v>
       </c>
       <c r="D22" s="1">
-        <v>374.05</v>
+        <v>1875.5</v>
       </c>
       <c r="E22" s="2">
-        <v>1.6</v>
+        <v>3.01</v>
       </c>
       <c r="F22" s="1">
-        <v>2014111</v>
-      </c>
-      <c r="G22" t="str">
+        <v>2070355</v>
+      </c>
+      <c r="G22" s="1">
+        <v>2171.41</v>
+      </c>
+      <c r="H22" s="1">
+        <v>1866.62</v>
+      </c>
+      <c r="I22" s="1">
+        <v>1974.15</v>
+      </c>
+      <c r="J22" t="str">
         <v/>
       </c>
     </row>
@@ -914,21 +1112,30 @@
         <v>22</v>
       </c>
       <c r="B23" t="str">
-        <v>Power Finance Corporation Limited</v>
+        <v>Havells India Limited</v>
       </c>
       <c r="C23" t="str">
-        <v>PFC</v>
+        <v>HAVELLS</v>
       </c>
       <c r="D23" s="1">
-        <v>333</v>
+        <v>1082</v>
       </c>
       <c r="E23" s="2">
-        <v>1.59</v>
+        <v>2.85</v>
       </c>
       <c r="F23" s="1">
-        <v>1867672</v>
-      </c>
-      <c r="G23" t="str">
+        <v>596696</v>
+      </c>
+      <c r="G23" s="1">
+        <v>1253.97</v>
+      </c>
+      <c r="H23" s="1">
+        <v>1058.84</v>
+      </c>
+      <c r="I23" s="1">
+        <v>1172.06</v>
+      </c>
+      <c r="J23" t="str">
         <v/>
       </c>
     </row>
@@ -937,21 +1144,30 @@
         <v>23</v>
       </c>
       <c r="B24" t="str">
-        <v>Computer Age Management Services Ltd</v>
+        <v>Indusind Bank Limited</v>
       </c>
       <c r="C24" t="str">
-        <v>CAMS</v>
+        <v>INDUSINDBK</v>
       </c>
       <c r="D24" s="1">
-        <v>683.15</v>
+        <v>877.35</v>
       </c>
       <c r="E24" s="2">
-        <v>1.58</v>
+        <v>2.85</v>
       </c>
       <c r="F24" s="1">
-        <v>412315</v>
-      </c>
-      <c r="G24" t="str">
+        <v>5235608</v>
+      </c>
+      <c r="G24" s="1">
+        <v>924.04</v>
+      </c>
+      <c r="H24" s="1">
+        <v>882.8</v>
+      </c>
+      <c r="I24" s="1">
+        <v>970.05</v>
+      </c>
+      <c r="J24" t="str">
         <v/>
       </c>
     </row>
@@ -960,21 +1176,30 @@
         <v>24</v>
       </c>
       <c r="B25" t="str">
-        <v>Hindustan Zinc Limited</v>
+        <v>KFin Technologies Ltd</v>
       </c>
       <c r="C25" t="str">
-        <v>HINDZINC</v>
+        <v>KFINTECH</v>
       </c>
       <c r="D25" s="1">
-        <v>552.05</v>
+        <v>889.9</v>
       </c>
       <c r="E25" s="2">
-        <v>1.57</v>
+        <v>2.76</v>
       </c>
       <c r="F25" s="1">
-        <v>1212942</v>
-      </c>
-      <c r="G25" t="str">
+        <v>1609556</v>
+      </c>
+      <c r="G25" s="1">
+        <v>932.32</v>
+      </c>
+      <c r="H25" s="1">
+        <v>865.19</v>
+      </c>
+      <c r="I25" s="1">
+        <v>915.28</v>
+      </c>
+      <c r="J25" t="str">
         <v/>
       </c>
     </row>
@@ -983,21 +1208,30 @@
         <v>25</v>
       </c>
       <c r="B26" t="str">
-        <v>Supreme Industries Limited</v>
+        <v>Indian Railway Finance Corporation Ltd</v>
       </c>
       <c r="C26" t="str">
-        <v>SUPREMEIND</v>
+        <v>IRFC</v>
       </c>
       <c r="D26" s="1">
-        <v>3528.9</v>
+        <v>79.62</v>
       </c>
       <c r="E26" s="2">
-        <v>1.56</v>
+        <v>2.74</v>
       </c>
       <c r="F26" s="1">
-        <v>33414</v>
-      </c>
-      <c r="G26" t="str">
+        <v>14371343</v>
+      </c>
+      <c r="G26" s="1">
+        <v>98.07</v>
+      </c>
+      <c r="H26" s="1">
+        <v>77.52</v>
+      </c>
+      <c r="I26" s="1">
+        <v>82.76</v>
+      </c>
+      <c r="J26" t="str">
         <v/>
       </c>
     </row>
@@ -1006,21 +1240,30 @@
         <v>26</v>
       </c>
       <c r="B27" t="str">
-        <v>Havells India Limited</v>
+        <v>Cochin Shipyard Ltd</v>
       </c>
       <c r="C27" t="str">
-        <v>HAVELLS</v>
+        <v>COCHINSHIP</v>
       </c>
       <c r="D27" s="1">
-        <v>1057.4</v>
+        <v>1265</v>
       </c>
       <c r="E27" s="2">
-        <v>1.53</v>
+        <v>2.68</v>
       </c>
       <c r="F27" s="1">
-        <v>90755</v>
-      </c>
-      <c r="G27" t="str">
+        <v>724528</v>
+      </c>
+      <c r="G27" s="1">
+        <v>1478.97</v>
+      </c>
+      <c r="H27" s="1">
+        <v>1271.67</v>
+      </c>
+      <c r="I27" s="1">
+        <v>1422.02</v>
+      </c>
+      <c r="J27" t="str">
         <v/>
       </c>
     </row>
@@ -1029,21 +1272,30 @@
         <v>27</v>
       </c>
       <c r="B28" t="str">
-        <v>HDFC Asset Management Company Ltd</v>
+        <v>Cholamandalam Investment And Finance Company Limited</v>
       </c>
       <c r="C28" t="str">
-        <v>HDFCAMC</v>
+        <v>CHOLAFIN</v>
       </c>
       <c r="D28" s="1">
-        <v>2296.7</v>
+        <v>1620.7</v>
       </c>
       <c r="E28" s="2">
-        <v>1.51</v>
+        <v>2.53</v>
       </c>
       <c r="F28" s="1">
-        <v>143643</v>
-      </c>
-      <c r="G28" t="str">
+        <v>1728004</v>
+      </c>
+      <c r="G28" s="1">
+        <v>1678.28</v>
+      </c>
+      <c r="H28" s="1">
+        <v>1610.05</v>
+      </c>
+      <c r="I28" s="1">
+        <v>1789.17</v>
+      </c>
+      <c r="J28" t="str">
         <v/>
       </c>
     </row>
@@ -1052,21 +1304,30 @@
         <v>28</v>
       </c>
       <c r="B29" t="str">
-        <v>Cummins India Limited</v>
+        <v>SBI Cards &amp; Payment Services Ltd</v>
       </c>
       <c r="C29" t="str">
-        <v>CUMMINSIND</v>
+        <v>SBICARD</v>
       </c>
       <c r="D29" s="1">
-        <v>4894.8</v>
+        <v>572.3</v>
       </c>
       <c r="E29" s="2">
-        <v>1.34</v>
+        <v>2.43</v>
       </c>
       <c r="F29" s="1">
-        <v>57073</v>
-      </c>
-      <c r="G29" t="str">
+        <v>490365</v>
+      </c>
+      <c r="G29" s="1">
+        <v>679.66</v>
+      </c>
+      <c r="H29" s="1">
+        <v>571.91</v>
+      </c>
+      <c r="I29" s="1">
+        <v>628.79</v>
+      </c>
+      <c r="J29" t="str">
         <v/>
       </c>
     </row>
@@ -1075,21 +1336,30 @@
         <v>29</v>
       </c>
       <c r="B30" t="str">
-        <v>Mahindra &amp; Mahindra Limited</v>
+        <v>Rail Vikas Nigam Ltd</v>
       </c>
       <c r="C30" t="str">
-        <v>M&amp;M</v>
+        <v>RVNL</v>
       </c>
       <c r="D30" s="1">
-        <v>2830.8</v>
+        <v>197.3</v>
       </c>
       <c r="E30" s="2">
-        <v>1.24</v>
+        <v>2.37</v>
       </c>
       <c r="F30" s="1">
-        <v>549504</v>
-      </c>
-      <c r="G30" t="str">
+        <v>3422969</v>
+      </c>
+      <c r="G30" s="1">
+        <v>265.21</v>
+      </c>
+      <c r="H30" s="1">
+        <v>196.24</v>
+      </c>
+      <c r="I30" s="1">
+        <v>212.56</v>
+      </c>
+      <c r="J30" t="str">
         <v/>
       </c>
     </row>
@@ -1098,21 +1368,30 @@
         <v>30</v>
       </c>
       <c r="B31" t="str">
-        <v>Pg Electroplast Limited</v>
+        <v>Hindalco Industries Limited</v>
       </c>
       <c r="C31" t="str">
-        <v>PGEL</v>
+        <v>HINDALCO</v>
       </c>
       <c r="D31" s="1">
-        <v>518.1</v>
+        <v>902.25</v>
       </c>
       <c r="E31" s="2">
-        <v>1.23</v>
+        <v>2.24</v>
       </c>
       <c r="F31" s="1">
-        <v>359184</v>
-      </c>
-      <c r="G31" t="str">
+        <v>5029502</v>
+      </c>
+      <c r="G31" s="1">
+        <v>980.59</v>
+      </c>
+      <c r="H31" s="1">
+        <v>918.48</v>
+      </c>
+      <c r="I31" s="1">
+        <v>997.81</v>
+      </c>
+      <c r="J31" t="str">
         <v/>
       </c>
     </row>
@@ -1121,21 +1400,30 @@
         <v>31</v>
       </c>
       <c r="B32" t="str">
-        <v>360 ONE WAM Ltd</v>
+        <v>Ultratech Cement Limited</v>
       </c>
       <c r="C32" t="str">
-        <v>360ONE</v>
+        <v>ULTRACEMCO</v>
       </c>
       <c r="D32" s="1">
-        <v>1060.5</v>
+        <v>10750</v>
       </c>
       <c r="E32" s="2">
-        <v>1.19</v>
+        <v>2.19</v>
       </c>
       <c r="F32" s="1">
-        <v>160594</v>
-      </c>
-      <c r="G32" t="str">
+        <v>186561</v>
+      </c>
+      <c r="G32" s="1">
+        <v>11676.61</v>
+      </c>
+      <c r="H32" s="1">
+        <v>10720.79</v>
+      </c>
+      <c r="I32" s="1">
+        <v>11282.58</v>
+      </c>
+      <c r="J32" t="str">
         <v/>
       </c>
     </row>
@@ -1144,21 +1432,30 @@
         <v>32</v>
       </c>
       <c r="B33" t="str">
-        <v>Jindal Steel Ltd</v>
+        <v>Ashok Leyland Limited</v>
       </c>
       <c r="C33" t="str">
-        <v>JINDALSTEL</v>
+        <v>ASHOKLEY</v>
       </c>
       <c r="D33" s="1">
-        <v>1028.5</v>
+        <v>147.37</v>
       </c>
       <c r="E33" s="2">
-        <v>1.16</v>
+        <v>2.16</v>
       </c>
       <c r="F33" s="1">
-        <v>363968</v>
-      </c>
-      <c r="G33" t="str">
+        <v>10361478</v>
+      </c>
+      <c r="G33" s="1">
+        <v>170.94</v>
+      </c>
+      <c r="H33" s="1">
+        <v>149.53</v>
+      </c>
+      <c r="I33" s="1">
+        <v>165.62</v>
+      </c>
+      <c r="J33" t="str">
         <v/>
       </c>
     </row>
@@ -1167,21 +1464,30 @@
         <v>33</v>
       </c>
       <c r="B34" t="str">
-        <v>Waaree Energies Ltd</v>
+        <v>Jubilant Foodworks Limited</v>
       </c>
       <c r="C34" t="str">
-        <v>WAAREEENER</v>
+        <v>JUBLFOOD</v>
       </c>
       <c r="D34" s="1">
-        <v>2347.8</v>
+        <v>425</v>
       </c>
       <c r="E34" s="2">
-        <v>1.07</v>
+        <v>2.15</v>
       </c>
       <c r="F34" s="1">
-        <v>202323</v>
-      </c>
-      <c r="G34" t="str">
+        <v>1086564</v>
+      </c>
+      <c r="G34" s="1">
+        <v>474.29</v>
+      </c>
+      <c r="H34" s="1">
+        <v>440.17</v>
+      </c>
+      <c r="I34" s="1">
+        <v>478.48</v>
+      </c>
+      <c r="J34" t="str">
         <v/>
       </c>
     </row>
@@ -1190,21 +1496,30 @@
         <v>34</v>
       </c>
       <c r="B35" t="str">
-        <v>Ashok Leyland Limited</v>
+        <v>Kaynes Technology India Ltd</v>
       </c>
       <c r="C35" t="str">
-        <v>ASHOKLEY</v>
+        <v>KAYNES</v>
       </c>
       <c r="D35" s="1">
-        <v>146.59</v>
+        <v>3290</v>
       </c>
       <c r="E35" s="2">
-        <v>1.05</v>
+        <v>2.11</v>
       </c>
       <c r="F35" s="1">
-        <v>3957664</v>
-      </c>
-      <c r="G35" t="str">
+        <v>504077</v>
+      </c>
+      <c r="G35" s="1">
+        <v>3628.09</v>
+      </c>
+      <c r="H35" s="1">
+        <v>3346.41</v>
+      </c>
+      <c r="I35" s="1">
+        <v>3622.43</v>
+      </c>
+      <c r="J35" t="str">
         <v/>
       </c>
     </row>
@@ -1213,21 +1528,30 @@
         <v>35</v>
       </c>
       <c r="B36" t="str">
-        <v>Inox Wind Limited</v>
+        <v>Bajaj Finserv Limited</v>
       </c>
       <c r="C36" t="str">
-        <v>INOXWIND</v>
+        <v>BAJAJFINSV</v>
       </c>
       <c r="D36" s="1">
-        <v>67.34</v>
+        <v>1755.7</v>
       </c>
       <c r="E36" s="2">
-        <v>1.04</v>
+        <v>2.08</v>
       </c>
       <c r="F36" s="1">
-        <v>7275581</v>
-      </c>
-      <c r="G36" t="str">
+        <v>1554535</v>
+      </c>
+      <c r="G36" s="1">
+        <v>1876.28</v>
+      </c>
+      <c r="H36" s="1">
+        <v>1748.1</v>
+      </c>
+      <c r="I36" s="1">
+        <v>1915.56</v>
+      </c>
+      <c r="J36" t="str">
         <v/>
       </c>
     </row>
@@ -1236,21 +1560,30 @@
         <v>36</v>
       </c>
       <c r="B37" t="str">
-        <v>Prestige Estates Projects Limited</v>
+        <v>Voltas Limited</v>
       </c>
       <c r="C37" t="str">
-        <v>PRESTIGE</v>
+        <v>VOLTAS</v>
       </c>
       <c r="D37" s="1">
-        <v>1420</v>
+        <v>1041</v>
       </c>
       <c r="E37" s="2">
-        <v>0.94</v>
+        <v>2.06</v>
       </c>
       <c r="F37" s="1">
-        <v>64292</v>
-      </c>
-      <c r="G37" t="str">
+        <v>459584</v>
+      </c>
+      <c r="G37" s="1">
+        <v>1320.46</v>
+      </c>
+      <c r="H37" s="1">
+        <v>1055.4</v>
+      </c>
+      <c r="I37" s="1">
+        <v>1174.73</v>
+      </c>
+      <c r="J37" t="str">
         <v/>
       </c>
     </row>
@@ -1259,21 +1592,30 @@
         <v>37</v>
       </c>
       <c r="B38" t="str">
-        <v>Hero Motocorp Limited</v>
+        <v>Central Depository Services Ltd</v>
       </c>
       <c r="C38" t="str">
-        <v>HEROMOTOCO</v>
+        <v>CDSL</v>
       </c>
       <c r="D38" s="1">
-        <v>4940</v>
+        <v>1292</v>
       </c>
       <c r="E38" s="2">
-        <v>0.91</v>
+        <v>2.05</v>
       </c>
       <c r="F38" s="1">
-        <v>109130</v>
-      </c>
-      <c r="G38" t="str">
+        <v>757404</v>
+      </c>
+      <c r="G38" s="1">
+        <v>1316.6</v>
+      </c>
+      <c r="H38" s="1">
+        <v>1276.82</v>
+      </c>
+      <c r="I38" s="1">
+        <v>1339.53</v>
+      </c>
+      <c r="J38" t="str">
         <v/>
       </c>
     </row>
@@ -1282,21 +1624,30 @@
         <v>38</v>
       </c>
       <c r="B39" t="str">
-        <v>Adani Energy Solutions Ltd</v>
+        <v>Container Corporation Of India Limited</v>
       </c>
       <c r="C39" t="str">
-        <v>ADANIENSOL</v>
+        <v>CONCOR</v>
       </c>
       <c r="D39" s="1">
-        <v>1273</v>
+        <v>449.75</v>
       </c>
       <c r="E39" s="2">
-        <v>0.87</v>
+        <v>2.04</v>
       </c>
       <c r="F39" s="1">
-        <v>220309</v>
-      </c>
-      <c r="G39" t="str">
+        <v>428849</v>
+      </c>
+      <c r="G39" s="1">
+        <v>490.59</v>
+      </c>
+      <c r="H39" s="1">
+        <v>446.97</v>
+      </c>
+      <c r="I39" s="1">
+        <v>491.4</v>
+      </c>
+      <c r="J39" t="str">
         <v/>
       </c>
     </row>
@@ -1305,21 +1656,30 @@
         <v>39</v>
       </c>
       <c r="B40" t="str">
-        <v>Pi Industries Limited</v>
+        <v>Jio Financial Services Ltd</v>
       </c>
       <c r="C40" t="str">
-        <v>PIIND</v>
+        <v>JIOFIN</v>
       </c>
       <c r="D40" s="1">
-        <v>2136.1</v>
+        <v>217.8</v>
       </c>
       <c r="E40" s="2">
-        <v>0.85</v>
+        <v>2.04</v>
       </c>
       <c r="F40" s="1">
-        <v>27594</v>
-      </c>
-      <c r="G40" t="str">
+        <v>16639006</v>
+      </c>
+      <c r="G40" s="1">
+        <v>246.49</v>
+      </c>
+      <c r="H40" s="1">
+        <v>216.76</v>
+      </c>
+      <c r="I40" s="1">
+        <v>235.69</v>
+      </c>
+      <c r="J40" t="str">
         <v/>
       </c>
     </row>
@@ -1328,21 +1688,30 @@
         <v>40</v>
       </c>
       <c r="B41" t="str">
-        <v>Upl Limited</v>
+        <v>Varun Beverages Limited</v>
       </c>
       <c r="C41" t="str">
-        <v>UPL</v>
+        <v>VBL</v>
       </c>
       <c r="D41" s="1">
-        <v>492.6</v>
+        <v>442</v>
       </c>
       <c r="E41" s="2">
-        <v>0.85</v>
+        <v>2.01</v>
       </c>
       <c r="F41" s="1">
-        <v>830602</v>
-      </c>
-      <c r="G41" t="str">
+        <v>2447008</v>
+      </c>
+      <c r="G41" s="1">
+        <v>463.67</v>
+      </c>
+      <c r="H41" s="1">
+        <v>435.6</v>
+      </c>
+      <c r="I41" s="1">
+        <v>427.61</v>
+      </c>
+      <c r="J41" t="str">
         <v/>
       </c>
     </row>
@@ -1351,21 +1720,30 @@
         <v>41</v>
       </c>
       <c r="B42" t="str">
-        <v>Indian Oil Corporation Limited</v>
+        <v>Yes Bank Limited</v>
       </c>
       <c r="C42" t="str">
-        <v>IOC</v>
+        <v>YESBANK</v>
       </c>
       <c r="D42" s="1">
-        <v>127.4</v>
+        <v>20.85</v>
       </c>
       <c r="E42" s="2">
-        <v>0.83</v>
+        <v>2.01</v>
       </c>
       <c r="F42" s="1">
-        <v>2466772</v>
-      </c>
-      <c r="G42" t="str">
+        <v>61130054</v>
+      </c>
+      <c r="G42" s="1">
+        <v>21.81</v>
+      </c>
+      <c r="H42" s="1">
+        <v>20.94</v>
+      </c>
+      <c r="I42" s="1">
+        <v>22.29</v>
+      </c>
+      <c r="J42" t="str">
         <v/>
       </c>
     </row>
@@ -1374,21 +1752,30 @@
         <v>42</v>
       </c>
       <c r="B43" t="str">
-        <v>KFin Technologies Ltd</v>
+        <v>REC Ltd</v>
       </c>
       <c r="C43" t="str">
-        <v>KFINTECH</v>
+        <v>RECLTD</v>
       </c>
       <c r="D43" s="1">
-        <v>849.2</v>
+        <v>307</v>
       </c>
       <c r="E43" s="2">
-        <v>0.81</v>
+        <v>1.99</v>
       </c>
       <c r="F43" s="1">
-        <v>67328</v>
-      </c>
-      <c r="G43" t="str">
+        <v>15270362</v>
+      </c>
+      <c r="G43" s="1">
+        <v>345.73</v>
+      </c>
+      <c r="H43" s="1">
+        <v>301.14</v>
+      </c>
+      <c r="I43" s="1">
+        <v>321.31</v>
+      </c>
+      <c r="J43" t="str">
         <v/>
       </c>
     </row>
@@ -1397,21 +1784,30 @@
         <v>43</v>
       </c>
       <c r="B44" t="str">
-        <v>HDFC Life Insurance Company Ltd</v>
+        <v>Godrej Consumer Products Limited</v>
       </c>
       <c r="C44" t="str">
-        <v>HDFCLIFE</v>
+        <v>GODREJCP</v>
       </c>
       <c r="D44" s="1">
-        <v>561.15</v>
+        <v>868.75</v>
       </c>
       <c r="E44" s="2">
-        <v>0.81</v>
+        <v>1.96</v>
       </c>
       <c r="F44" s="1">
-        <v>803057</v>
-      </c>
-      <c r="G44" t="str">
+        <v>855889</v>
+      </c>
+      <c r="G44" s="1">
+        <v>1054.59</v>
+      </c>
+      <c r="H44" s="1">
+        <v>861.52</v>
+      </c>
+      <c r="I44" s="1">
+        <v>910.91</v>
+      </c>
+      <c r="J44" t="str">
         <v/>
       </c>
     </row>
@@ -1420,21 +1816,30 @@
         <v>44</v>
       </c>
       <c r="B45" t="str">
-        <v>Jsw Steel Limited</v>
+        <v>Indian Energy Exchange Ltd</v>
       </c>
       <c r="C45" t="str">
-        <v>JSWSTEEL</v>
+        <v>IEX</v>
       </c>
       <c r="D45" s="1">
-        <v>1177.1</v>
+        <v>106.4</v>
       </c>
       <c r="E45" s="2">
-        <v>0.78</v>
+        <v>1.95</v>
       </c>
       <c r="F45" s="1">
-        <v>306452</v>
-      </c>
-      <c r="G45" t="str">
+        <v>3925108</v>
+      </c>
+      <c r="G45" s="1">
+        <v>124.34</v>
+      </c>
+      <c r="H45" s="1">
+        <v>106.3</v>
+      </c>
+      <c r="I45" s="1">
+        <v>117.3</v>
+      </c>
+      <c r="J45" t="str">
         <v/>
       </c>
     </row>
@@ -1443,21 +1848,30 @@
         <v>45</v>
       </c>
       <c r="B46" t="str">
-        <v>Eicher Motors Limited</v>
+        <v>Asian Paints Limited</v>
       </c>
       <c r="C46" t="str">
-        <v>EICHERMOT</v>
+        <v>ASIANPAINT</v>
       </c>
       <c r="D46" s="1">
-        <v>7104</v>
+        <v>2376</v>
       </c>
       <c r="E46" s="2">
-        <v>0.77</v>
+        <v>1.93</v>
       </c>
       <c r="F46" s="1">
-        <v>118807</v>
-      </c>
-      <c r="G46" t="str">
+        <v>519870</v>
+      </c>
+      <c r="G46" s="1">
+        <v>2548.14</v>
+      </c>
+      <c r="H46" s="1">
+        <v>2373.4</v>
+      </c>
+      <c r="I46" s="1">
+        <v>2544.17</v>
+      </c>
+      <c r="J46" t="str">
         <v/>
       </c>
     </row>
@@ -1466,21 +1880,30 @@
         <v>46</v>
       </c>
       <c r="B47" t="str">
-        <v>Jsw Energy Limited</v>
+        <v>Colgate Palmolive (india) Limited</v>
       </c>
       <c r="C47" t="str">
-        <v>JSWENERGY</v>
+        <v>COLPAL</v>
       </c>
       <c r="D47" s="1">
-        <v>465.55</v>
+        <v>1801</v>
       </c>
       <c r="E47" s="2">
-        <v>0.7</v>
+        <v>1.92</v>
       </c>
       <c r="F47" s="1">
-        <v>397169</v>
-      </c>
-      <c r="G47" t="str">
+        <v>349916</v>
+      </c>
+      <c r="G47" s="1">
+        <v>2025.91</v>
+      </c>
+      <c r="H47" s="1">
+        <v>1790.01</v>
+      </c>
+      <c r="I47" s="1">
+        <v>1875.09</v>
+      </c>
+      <c r="J47" t="str">
         <v/>
       </c>
     </row>
@@ -1489,21 +1912,30 @@
         <v>47</v>
       </c>
       <c r="B48" t="str">
-        <v>Icici Prudential Life Insurance Company Limited</v>
+        <v>PB Fintech Ltd</v>
       </c>
       <c r="C48" t="str">
-        <v>ICICIPRULI</v>
+        <v>POLICYBZR</v>
       </c>
       <c r="D48" s="1">
-        <v>463.65</v>
+        <v>1067</v>
       </c>
       <c r="E48" s="2">
-        <v>0.67</v>
+        <v>1.91</v>
       </c>
       <c r="F48" s="1">
-        <v>126736</v>
-      </c>
-      <c r="G48" t="str">
+        <v>3289560</v>
+      </c>
+      <c r="G48" s="1">
+        <v>1598.55</v>
+      </c>
+      <c r="H48" s="1">
+        <v>1098.3</v>
+      </c>
+      <c r="I48" s="1">
+        <v>1584.35</v>
+      </c>
+      <c r="J48" t="str">
         <v/>
       </c>
     </row>
@@ -1512,21 +1944,30 @@
         <v>48</v>
       </c>
       <c r="B49" t="str">
-        <v>Hyundai Motor India Ltd</v>
+        <v>Upl Limited</v>
       </c>
       <c r="C49" t="str">
-        <v>HYUNDAI</v>
+        <v>UPL</v>
       </c>
       <c r="D49" s="1">
-        <v>1952.8</v>
+        <v>524.7</v>
       </c>
       <c r="E49" s="2">
-        <v>0.66</v>
+        <v>1.91</v>
       </c>
       <c r="F49" s="1">
-        <v>154981</v>
-      </c>
-      <c r="G49" t="str">
+        <v>1856087</v>
+      </c>
+      <c r="G49" s="1">
+        <v>634.55</v>
+      </c>
+      <c r="H49" s="1">
+        <v>514.81</v>
+      </c>
+      <c r="I49" s="1">
+        <v>558.42</v>
+      </c>
+      <c r="J49" t="str">
         <v/>
       </c>
     </row>
@@ -1535,21 +1976,30 @@
         <v>49</v>
       </c>
       <c r="B50" t="str">
-        <v>Indian Renewable Energy Development Agency Ltd</v>
+        <v>Jindal Steel Ltd</v>
       </c>
       <c r="C50" t="str">
-        <v>IREDA</v>
+        <v>JINDALSTEL</v>
       </c>
       <c r="D50" s="1">
-        <v>105.09</v>
+        <v>1031.7</v>
       </c>
       <c r="E50" s="2">
-        <v>0.66</v>
+        <v>1.9</v>
       </c>
       <c r="F50" s="1">
-        <v>1706044</v>
-      </c>
-      <c r="G50" t="str">
+        <v>537045</v>
+      </c>
+      <c r="G50" s="1">
+        <v>1137.61</v>
+      </c>
+      <c r="H50" s="1">
+        <v>1059.42</v>
+      </c>
+      <c r="I50" s="1">
+        <v>1120.46</v>
+      </c>
+      <c r="J50" t="str">
         <v/>
       </c>
     </row>
@@ -1558,21 +2008,30 @@
         <v>50</v>
       </c>
       <c r="B51" t="str">
-        <v>Swiggy Ltd</v>
+        <v>Grasim Industries Limited</v>
       </c>
       <c r="C51" t="str">
-        <v>SWIGGY</v>
+        <v>GRASIM</v>
       </c>
       <c r="D51" s="1">
-        <v>235.4</v>
+        <v>2912</v>
       </c>
       <c r="E51" s="2">
-        <v>0.51</v>
+        <v>1.89</v>
       </c>
       <c r="F51" s="1">
-        <v>1816838</v>
-      </c>
-      <c r="G51" t="str">
+        <v>306048</v>
+      </c>
+      <c r="G51" s="1">
+        <v>2978.38</v>
+      </c>
+      <c r="H51" s="1">
+        <v>2954.02</v>
+      </c>
+      <c r="I51" s="1">
+        <v>3197.2</v>
+      </c>
+      <c r="J51" t="str">
         <v/>
       </c>
     </row>
@@ -1581,21 +2040,30 @@
         <v>51</v>
       </c>
       <c r="B52" t="str">
-        <v>Indian Energy Exchange Ltd</v>
+        <v>L&amp;T Finance Ltd</v>
       </c>
       <c r="C52" t="str">
-        <v>IEX</v>
+        <v>LTF</v>
       </c>
       <c r="D52" s="1">
-        <v>105.28</v>
+        <v>267.6</v>
       </c>
       <c r="E52" s="2">
-        <v>0.48</v>
+        <v>1.87</v>
       </c>
       <c r="F52" s="1">
-        <v>797992</v>
-      </c>
-      <c r="G52" t="str">
+        <v>2223420</v>
+      </c>
+      <c r="G52" s="1">
+        <v>291.82</v>
+      </c>
+      <c r="H52" s="1">
+        <v>267.74</v>
+      </c>
+      <c r="I52" s="1">
+        <v>301.34</v>
+      </c>
+      <c r="J52" t="str">
         <v/>
       </c>
     </row>
@@ -1604,21 +2072,30 @@
         <v>52</v>
       </c>
       <c r="B53" t="str">
-        <v>KPIT Technologies Ltd</v>
+        <v>Mahindra &amp; Mahindra Limited</v>
       </c>
       <c r="C53" t="str">
-        <v>KPITTECH</v>
+        <v>M&amp;M</v>
       </c>
       <c r="D53" s="1">
-        <v>481.25</v>
+        <v>2864.4</v>
       </c>
       <c r="E53" s="2">
-        <v>0.47</v>
+        <v>1.83</v>
       </c>
       <c r="F53" s="1">
-        <v>478752</v>
-      </c>
-      <c r="G53" t="str">
+        <v>2560591</v>
+      </c>
+      <c r="G53" s="1">
+        <v>3251.75</v>
+      </c>
+      <c r="H53" s="1">
+        <v>2860.94</v>
+      </c>
+      <c r="I53" s="1">
+        <v>3181.36</v>
+      </c>
+      <c r="J53" t="str">
         <v/>
       </c>
     </row>
@@ -1627,21 +2104,30 @@
         <v>53</v>
       </c>
       <c r="B54" t="str">
-        <v>Bharat Forge Limited</v>
+        <v>HDFC Asset Management Company Ltd</v>
       </c>
       <c r="C54" t="str">
-        <v>BHARATFORG</v>
+        <v>HDFCAMC</v>
       </c>
       <c r="D54" s="1">
-        <v>1823.9</v>
+        <v>2330</v>
       </c>
       <c r="E54" s="2">
-        <v>0.39</v>
+        <v>1.76</v>
       </c>
       <c r="F54" s="1">
-        <v>147071</v>
-      </c>
-      <c r="G54" t="str">
+        <v>700082</v>
+      </c>
+      <c r="G54" s="1">
+        <v>2579.14</v>
+      </c>
+      <c r="H54" s="1">
+        <v>2311.39</v>
+      </c>
+      <c r="I54" s="1">
+        <v>2461.16</v>
+      </c>
+      <c r="J54" t="str">
         <v/>
       </c>
     </row>
@@ -1650,21 +2136,30 @@
         <v>54</v>
       </c>
       <c r="B55" t="str">
-        <v>Cholamandalam Investment And Finance Company Limited</v>
+        <v>Canara Bank Ltd</v>
       </c>
       <c r="C55" t="str">
-        <v>CHOLAFIN</v>
+        <v>CANBK</v>
       </c>
       <c r="D55" s="1">
-        <v>1593.8</v>
+        <v>120.44</v>
       </c>
       <c r="E55" s="2">
-        <v>0.39</v>
+        <v>1.74</v>
       </c>
       <c r="F55" s="1">
-        <v>353297</v>
-      </c>
-      <c r="G55" t="str">
+        <v>12794878</v>
+      </c>
+      <c r="G55" s="1">
+        <v>135.38</v>
+      </c>
+      <c r="H55" s="1">
+        <v>119.65</v>
+      </c>
+      <c r="I55" s="1">
+        <v>125.41</v>
+      </c>
+      <c r="J55" t="str">
         <v/>
       </c>
     </row>
@@ -1673,21 +2168,30 @@
         <v>55</v>
       </c>
       <c r="B56" t="str">
-        <v>Muthoot Finance Limited</v>
+        <v>Amber Enterprises India Ltd</v>
       </c>
       <c r="C56" t="str">
-        <v>MUTHOOTFIN</v>
+        <v>AMBER</v>
       </c>
       <c r="D56" s="1">
-        <v>2634.7</v>
+        <v>6640</v>
       </c>
       <c r="E56" s="2">
-        <v>0.38</v>
+        <v>1.72</v>
       </c>
       <c r="F56" s="1">
-        <v>54521</v>
-      </c>
-      <c r="G56" t="str">
+        <v>131675</v>
+      </c>
+      <c r="G56" s="1">
+        <v>7231.11</v>
+      </c>
+      <c r="H56" s="1">
+        <v>6675.37</v>
+      </c>
+      <c r="I56" s="1">
+        <v>7144.64</v>
+      </c>
+      <c r="J56" t="str">
         <v/>
       </c>
     </row>
@@ -1696,21 +2200,30 @@
         <v>56</v>
       </c>
       <c r="B57" t="str">
-        <v>Ultratech Cement Limited</v>
+        <v>State Bank Of India Ltd</v>
       </c>
       <c r="C57" t="str">
-        <v>ULTRACEMCO</v>
+        <v>SBIN</v>
       </c>
       <c r="D57" s="1">
-        <v>10714</v>
+        <v>957</v>
       </c>
       <c r="E57" s="2">
-        <v>0.37</v>
+        <v>1.7</v>
       </c>
       <c r="F57" s="1">
-        <v>17649</v>
-      </c>
-      <c r="G57" t="str">
+        <v>6759074</v>
+      </c>
+      <c r="G57" s="1">
+        <v>1040.51</v>
+      </c>
+      <c r="H57" s="1">
+        <v>957.21</v>
+      </c>
+      <c r="I57" s="1">
+        <v>1015</v>
+      </c>
+      <c r="J57" t="str">
         <v/>
       </c>
     </row>
@@ -1719,21 +2232,30 @@
         <v>57</v>
       </c>
       <c r="B58" t="str">
-        <v>TATA Consumer Products Ltd</v>
+        <v>Patanjali Foods Ltd</v>
       </c>
       <c r="C58" t="str">
-        <v>TATACONSUM</v>
+        <v>PATANJALI</v>
       </c>
       <c r="D58" s="1">
-        <v>958.55</v>
+        <v>367.5</v>
       </c>
       <c r="E58" s="2">
-        <v>0.37</v>
+        <v>1.7</v>
       </c>
       <c r="F58" s="1">
-        <v>155149</v>
-      </c>
-      <c r="G58" t="str">
+        <v>1973274</v>
+      </c>
+      <c r="G58" s="1">
+        <v>440.67</v>
+      </c>
+      <c r="H58" s="1">
+        <v>364.88</v>
+      </c>
+      <c r="I58" s="1">
+        <v>358.72</v>
+      </c>
+      <c r="J58" t="str">
         <v/>
       </c>
     </row>
@@ -1742,21 +2264,30 @@
         <v>58</v>
       </c>
       <c r="B59" t="str">
-        <v>Cipla Limited</v>
+        <v>Nbcc (india) Limited</v>
       </c>
       <c r="C59" t="str">
-        <v>CIPLA</v>
+        <v>NBCC</v>
       </c>
       <c r="D59" s="1">
-        <v>1305.3</v>
+        <v>77.2</v>
       </c>
       <c r="E59" s="2">
-        <v>0.33</v>
+        <v>1.69</v>
       </c>
       <c r="F59" s="1">
-        <v>99631</v>
-      </c>
-      <c r="G59" t="str">
+        <v>3059363</v>
+      </c>
+      <c r="G59" s="1">
+        <v>94.89</v>
+      </c>
+      <c r="H59" s="1">
+        <v>77.05</v>
+      </c>
+      <c r="I59" s="1">
+        <v>85.28</v>
+      </c>
+      <c r="J59" t="str">
         <v/>
       </c>
     </row>
@@ -1765,21 +2296,30 @@
         <v>59</v>
       </c>
       <c r="B60" t="str">
-        <v>Tata Steel Limited</v>
+        <v>Shree Cements Limited</v>
       </c>
       <c r="C60" t="str">
-        <v>TATASTEEL</v>
+        <v>SHREECEM</v>
       </c>
       <c r="D60" s="1">
-        <v>174.36</v>
+        <v>22225</v>
       </c>
       <c r="E60" s="2">
-        <v>0.32</v>
+        <v>1.67</v>
       </c>
       <c r="F60" s="1">
-        <v>16724030</v>
-      </c>
-      <c r="G60" t="str">
+        <v>18662</v>
+      </c>
+      <c r="G60" s="1">
+        <v>25098.73</v>
+      </c>
+      <c r="H60" s="1">
+        <v>22051</v>
+      </c>
+      <c r="I60" s="1">
+        <v>23593.3</v>
+      </c>
+      <c r="J60" t="str">
         <v/>
       </c>
     </row>
@@ -1788,21 +2328,30 @@
         <v>60</v>
       </c>
       <c r="B61" t="str">
-        <v>Shree Cements Limited</v>
+        <v>Bharat Electronics Limited</v>
       </c>
       <c r="C61" t="str">
-        <v>SHREECEM</v>
+        <v>BEL</v>
       </c>
       <c r="D61" s="1">
-        <v>22145</v>
+        <v>380</v>
       </c>
       <c r="E61" s="2">
-        <v>0.29</v>
+        <v>1.63</v>
       </c>
       <c r="F61" s="1">
-        <v>3475</v>
-      </c>
-      <c r="G61" t="str">
+        <v>7732384</v>
+      </c>
+      <c r="G61" s="1">
+        <v>417.48</v>
+      </c>
+      <c r="H61" s="1">
+        <v>379.57</v>
+      </c>
+      <c r="I61" s="1">
+        <v>398.31</v>
+      </c>
+      <c r="J61" t="str">
         <v/>
       </c>
     </row>
@@ -1811,21 +2360,30 @@
         <v>61</v>
       </c>
       <c r="B62" t="str">
-        <v>Blue Star Limited</v>
+        <v>NIFTY</v>
       </c>
       <c r="C62" t="str">
-        <v>BLUESTARCO</v>
+        <v>NIFTY</v>
       </c>
       <c r="D62" s="1">
-        <v>1578.4</v>
+        <v>22721.95</v>
       </c>
       <c r="E62" s="2">
-        <v>0.28</v>
+        <v>1.6</v>
       </c>
       <c r="F62" s="1">
-        <v>68814</v>
-      </c>
-      <c r="G62" t="str">
+        <v>0</v>
+      </c>
+      <c r="G62" s="1">
+        <v>24232.79</v>
+      </c>
+      <c r="H62" s="1">
+        <v>22630.49</v>
+      </c>
+      <c r="I62" s="1">
+        <v>23654.16</v>
+      </c>
+      <c r="J62" t="str">
         <v/>
       </c>
     </row>
@@ -1834,21 +2392,30 @@
         <v>62</v>
       </c>
       <c r="B63" t="str">
-        <v>Max Healthcare Institute Ltd</v>
+        <v>Tata Steel Limited</v>
       </c>
       <c r="C63" t="str">
-        <v>MAXHEALTH</v>
+        <v>TATASTEEL</v>
       </c>
       <c r="D63" s="1">
-        <v>886.2</v>
+        <v>175</v>
       </c>
       <c r="E63" s="2">
-        <v>0.27</v>
+        <v>1.6</v>
       </c>
       <c r="F63" s="1">
-        <v>306635</v>
-      </c>
-      <c r="G63" t="str">
+        <v>19991053</v>
+      </c>
+      <c r="G63" s="1">
+        <v>194.12</v>
+      </c>
+      <c r="H63" s="1">
+        <v>177.03</v>
+      </c>
+      <c r="I63" s="1">
+        <v>184.63</v>
+      </c>
+      <c r="J63" t="str">
         <v/>
       </c>
     </row>
@@ -1857,21 +2424,30 @@
         <v>63</v>
       </c>
       <c r="B64" t="str">
-        <v>Asian Paints Limited</v>
+        <v>United Spirits Ltd</v>
       </c>
       <c r="C64" t="str">
-        <v>ASIANPAINT</v>
+        <v>UNITDSPR</v>
       </c>
       <c r="D64" s="1">
-        <v>2345.2</v>
+        <v>1371.1</v>
       </c>
       <c r="E64" s="2">
-        <v>0.26</v>
+        <v>1.59</v>
       </c>
       <c r="F64" s="1">
-        <v>113301</v>
-      </c>
-      <c r="G64" t="str">
+        <v>745760</v>
+      </c>
+      <c r="G64" s="1">
+        <v>1371.77</v>
+      </c>
+      <c r="H64" s="1">
+        <v>1362.31</v>
+      </c>
+      <c r="I64" s="1">
+        <v>1453.05</v>
+      </c>
+      <c r="J64" t="str">
         <v/>
       </c>
     </row>
@@ -1880,21 +2456,30 @@
         <v>64</v>
       </c>
       <c r="B65" t="str">
-        <v>Uno Minda Ltd</v>
+        <v>Suzlon Energy Limited</v>
       </c>
       <c r="C65" t="str">
-        <v>UNOMINDA</v>
+        <v>SUZLON</v>
       </c>
       <c r="D65" s="1">
-        <v>1110.7</v>
+        <v>40.19</v>
       </c>
       <c r="E65" s="2">
-        <v>0.24</v>
+        <v>1.57</v>
       </c>
       <c r="F65" s="1">
-        <v>81274</v>
-      </c>
-      <c r="G65" t="str">
+        <v>82775076</v>
+      </c>
+      <c r="G65" s="1">
+        <v>48.67</v>
+      </c>
+      <c r="H65" s="1">
+        <v>39.26</v>
+      </c>
+      <c r="I65" s="1">
+        <v>44.27</v>
+      </c>
+      <c r="J65" t="str">
         <v/>
       </c>
     </row>
@@ -1903,21 +2488,30 @@
         <v>65</v>
       </c>
       <c r="B66" t="str">
-        <v>Bharat Petroleum Corporation Limited</v>
+        <v>Bharti Airtel Limited</v>
       </c>
       <c r="C66" t="str">
-        <v>BPCL</v>
+        <v>BHARTIARTL</v>
       </c>
       <c r="D66" s="1">
-        <v>288.5</v>
+        <v>1806.5</v>
       </c>
       <c r="E66" s="2">
-        <v>0.24</v>
+        <v>1.56</v>
       </c>
       <c r="F66" s="1">
-        <v>701419</v>
-      </c>
-      <c r="G66" t="str">
+        <v>5381884</v>
+      </c>
+      <c r="G66" s="1">
+        <v>1900.89</v>
+      </c>
+      <c r="H66" s="1">
+        <v>1798.35</v>
+      </c>
+      <c r="I66" s="1">
+        <v>1867.58</v>
+      </c>
+      <c r="J66" t="str">
         <v/>
       </c>
     </row>
@@ -1926,21 +2520,30 @@
         <v>66</v>
       </c>
       <c r="B67" t="str">
-        <v>Crompton Greaves Consumer Electricals Limited</v>
+        <v>Blue Star Limited</v>
       </c>
       <c r="C67" t="str">
-        <v>CROMPTON</v>
+        <v>BLUESTARCO</v>
       </c>
       <c r="D67" s="1">
-        <v>205.56</v>
+        <v>1594</v>
       </c>
       <c r="E67" s="2">
-        <v>0.22</v>
+        <v>1.53</v>
       </c>
       <c r="F67" s="1">
-        <v>394888</v>
-      </c>
-      <c r="G67" t="str">
+        <v>229346</v>
+      </c>
+      <c r="G67" s="1">
+        <v>1690.53</v>
+      </c>
+      <c r="H67" s="1">
+        <v>1551.21</v>
+      </c>
+      <c r="I67" s="1">
+        <v>1525.41</v>
+      </c>
+      <c r="J67" t="str">
         <v/>
       </c>
     </row>
@@ -1949,21 +2552,30 @@
         <v>67</v>
       </c>
       <c r="B68" t="str">
-        <v>SBI Cards &amp; Payment Services Ltd</v>
+        <v>Bharat Forge Limited</v>
       </c>
       <c r="C68" t="str">
-        <v>SBICARD</v>
+        <v>BHARATFORG</v>
       </c>
       <c r="D68" s="1">
-        <v>563.2</v>
+        <v>1842.2</v>
       </c>
       <c r="E68" s="2">
-        <v>0.21</v>
+        <v>1.48</v>
       </c>
       <c r="F68" s="1">
-        <v>134356</v>
-      </c>
-      <c r="G68" t="str">
+        <v>418744</v>
+      </c>
+      <c r="G68" s="1">
+        <v>1864.89</v>
+      </c>
+      <c r="H68" s="1">
+        <v>1857.6</v>
+      </c>
+      <c r="I68" s="1">
+        <v>2002.89</v>
+      </c>
+      <c r="J68" t="str">
         <v/>
       </c>
     </row>
@@ -1972,21 +2584,30 @@
         <v>68</v>
       </c>
       <c r="B69" t="str">
-        <v>Tata Consultancy Services Limited</v>
+        <v>AU Small Finance Bank Ltd</v>
       </c>
       <c r="C69" t="str">
-        <v>TCS</v>
+        <v>AUBANK</v>
       </c>
       <c r="D69" s="1">
-        <v>2159.3</v>
+        <v>991.5</v>
       </c>
       <c r="E69" s="2">
-        <v>0.15</v>
+        <v>1.46</v>
       </c>
       <c r="F69" s="1">
-        <v>1409739</v>
-      </c>
-      <c r="G69" t="str">
+        <v>1178074</v>
+      </c>
+      <c r="G69" s="1">
+        <v>1005.75</v>
+      </c>
+      <c r="H69" s="1">
+        <v>997.11</v>
+      </c>
+      <c r="I69" s="1">
+        <v>1052.76</v>
+      </c>
+      <c r="J69" t="str">
         <v/>
       </c>
     </row>
@@ -1995,21 +2616,30 @@
         <v>69</v>
       </c>
       <c r="B70" t="str">
-        <v>Voltas Limited</v>
+        <v>Max Financial Services Limited</v>
       </c>
       <c r="C70" t="str">
-        <v>VOLTAS</v>
+        <v>MFSL</v>
       </c>
       <c r="D70" s="1">
-        <v>1035.3</v>
+        <v>1325.4</v>
       </c>
       <c r="E70" s="2">
-        <v>0.15</v>
+        <v>1.45</v>
       </c>
       <c r="F70" s="1">
-        <v>89238</v>
-      </c>
-      <c r="G70" t="str">
+        <v>1143295</v>
+      </c>
+      <c r="G70" s="1">
+        <v>1607.63</v>
+      </c>
+      <c r="H70" s="1">
+        <v>1354.71</v>
+      </c>
+      <c r="I70" s="1">
+        <v>1491.62</v>
+      </c>
+      <c r="J70" t="str">
         <v/>
       </c>
     </row>
@@ -2018,21 +2648,30 @@
         <v>70</v>
       </c>
       <c r="B71" t="str">
-        <v>Godrej Properties Limited</v>
+        <v>Nmdc Limited</v>
       </c>
       <c r="C71" t="str">
-        <v>GODREJPROP</v>
+        <v>NMDC</v>
       </c>
       <c r="D71" s="1">
-        <v>1552</v>
+        <v>71.34</v>
       </c>
       <c r="E71" s="2">
-        <v>0.13</v>
+        <v>1.42</v>
       </c>
       <c r="F71" s="1">
-        <v>79373</v>
-      </c>
-      <c r="G71" t="str">
+        <v>11680322</v>
+      </c>
+      <c r="G71" s="1">
+        <v>83.75</v>
+      </c>
+      <c r="H71" s="1">
+        <v>73.37</v>
+      </c>
+      <c r="I71" s="1">
+        <v>81.79</v>
+      </c>
+      <c r="J71" t="str">
         <v/>
       </c>
     </row>
@@ -2041,21 +2680,30 @@
         <v>71</v>
       </c>
       <c r="B72" t="str">
-        <v>Force Motors Ltd</v>
+        <v>Cipla Limited</v>
       </c>
       <c r="C72" t="str">
-        <v>FORCEMOT</v>
+        <v>CIPLA</v>
       </c>
       <c r="D72" s="1">
-        <v>16921</v>
+        <v>1329.6</v>
       </c>
       <c r="E72" s="2">
-        <v>0.12</v>
+        <v>1.4</v>
       </c>
       <c r="F72" s="1">
-        <v>12136</v>
-      </c>
-      <c r="G72" t="str">
+        <v>438013</v>
+      </c>
+      <c r="G72" s="1">
+        <v>1374.31</v>
+      </c>
+      <c r="H72" s="1">
+        <v>1332.39</v>
+      </c>
+      <c r="I72" s="1">
+        <v>1398.8</v>
+      </c>
+      <c r="J72" t="str">
         <v/>
       </c>
     </row>
@@ -2064,21 +2712,30 @@
         <v>72</v>
       </c>
       <c r="B73" t="str">
-        <v>Max Financial Services Limited</v>
+        <v>Pidilite Industries Limited</v>
       </c>
       <c r="C73" t="str">
-        <v>MFSL</v>
+        <v>PIDILITIND</v>
       </c>
       <c r="D73" s="1">
-        <v>1311</v>
+        <v>1497.6</v>
       </c>
       <c r="E73" s="2">
-        <v>0.1</v>
+        <v>1.35</v>
       </c>
       <c r="F73" s="1">
-        <v>72611</v>
-      </c>
-      <c r="G73" t="str">
+        <v>507286</v>
+      </c>
+      <c r="G73" s="1">
+        <v>1499.79</v>
+      </c>
+      <c r="H73" s="1">
+        <v>1492.15</v>
+      </c>
+      <c r="I73" s="1">
+        <v>1593.29</v>
+      </c>
+      <c r="J73" t="str">
         <v/>
       </c>
     </row>
@@ -2087,21 +2744,30 @@
         <v>73</v>
       </c>
       <c r="B74" t="str">
-        <v>Central Depository Services Ltd</v>
+        <v>Biocon Limited</v>
       </c>
       <c r="C74" t="str">
-        <v>CDSL</v>
+        <v>BIOCON</v>
       </c>
       <c r="D74" s="1">
-        <v>1261.2</v>
+        <v>351</v>
       </c>
       <c r="E74" s="2">
-        <v>0.1</v>
+        <v>1.34</v>
       </c>
       <c r="F74" s="1">
-        <v>252216</v>
-      </c>
-      <c r="G74" t="str">
+        <v>2338512</v>
+      </c>
+      <c r="G74" s="1">
+        <v>393.82</v>
+      </c>
+      <c r="H74" s="1">
+        <v>360.05</v>
+      </c>
+      <c r="I74" s="1">
+        <v>396.62</v>
+      </c>
+      <c r="J74" t="str">
         <v/>
       </c>
     </row>
@@ -2110,21 +2776,30 @@
         <v>74</v>
       </c>
       <c r="B75" t="str">
-        <v>Power Grid Corporation Of India Limited</v>
+        <v>Larsen &amp; Toubro Limited</v>
       </c>
       <c r="C75" t="str">
-        <v>POWERGRID</v>
+        <v>LT</v>
       </c>
       <c r="D75" s="1">
-        <v>249.35</v>
+        <v>3675</v>
       </c>
       <c r="E75" s="2">
-        <v>0.08</v>
+        <v>1.31</v>
       </c>
       <c r="F75" s="1">
-        <v>1830610</v>
-      </c>
-      <c r="G75" t="str">
+        <v>2158677</v>
+      </c>
+      <c r="G75" s="1">
+        <v>3955.66</v>
+      </c>
+      <c r="H75" s="1">
+        <v>3711.14</v>
+      </c>
+      <c r="I75" s="1">
+        <v>3929.52</v>
+      </c>
+      <c r="J75" t="str">
         <v/>
       </c>
     </row>
@@ -2133,21 +2808,30 @@
         <v>75</v>
       </c>
       <c r="B76" t="str">
-        <v>Container Corporation Of India Limited</v>
+        <v>Hdfc Bank Limited</v>
       </c>
       <c r="C76" t="str">
-        <v>CONCOR</v>
+        <v>HDFCBANK</v>
       </c>
       <c r="D76" s="1">
-        <v>442.25</v>
+        <v>714</v>
       </c>
       <c r="E76" s="2">
-        <v>0.06</v>
+        <v>1.29</v>
       </c>
       <c r="F76" s="1">
-        <v>126678</v>
-      </c>
-      <c r="G76" t="str">
+        <v>17226354</v>
+      </c>
+      <c r="G76" s="1">
+        <v>806.64</v>
+      </c>
+      <c r="H76" s="1">
+        <v>710.08</v>
+      </c>
+      <c r="I76" s="1">
+        <v>719.79</v>
+      </c>
+      <c r="J76" t="str">
         <v/>
       </c>
     </row>
@@ -2156,21 +2840,30 @@
         <v>76</v>
       </c>
       <c r="B77" t="str">
-        <v>Vedanta Limited</v>
+        <v>Bank Of Baroda Ltd</v>
       </c>
       <c r="C77" t="str">
-        <v>VEDL</v>
+        <v>BANKBARODA</v>
       </c>
       <c r="D77" s="1">
-        <v>264.1</v>
+        <v>238.43</v>
       </c>
       <c r="E77" s="2">
-        <v>0.04</v>
+        <v>1.29</v>
       </c>
       <c r="F77" s="1">
-        <v>3986903</v>
-      </c>
-      <c r="G77" t="str">
+        <v>3694562</v>
+      </c>
+      <c r="G77" s="1">
+        <v>268.19</v>
+      </c>
+      <c r="H77" s="1">
+        <v>234.66</v>
+      </c>
+      <c r="I77" s="1">
+        <v>239.31</v>
+      </c>
+      <c r="J77" t="str">
         <v/>
       </c>
     </row>
@@ -2179,21 +2872,30 @@
         <v>77</v>
       </c>
       <c r="B78" t="str">
-        <v>Tata Power Company Limited</v>
+        <v>Apollo Hospitals Enterprise Limited</v>
       </c>
       <c r="C78" t="str">
-        <v>TATAPOWER</v>
+        <v>APOLLOHOSP</v>
       </c>
       <c r="D78" s="1">
-        <v>342.25</v>
+        <v>7871</v>
       </c>
       <c r="E78" s="2">
-        <v>0.03</v>
+        <v>1.23</v>
       </c>
       <c r="F78" s="1">
-        <v>751591</v>
-      </c>
-      <c r="G78" t="str">
+        <v>460672</v>
+      </c>
+      <c r="G78" s="1">
+        <v>8049.77</v>
+      </c>
+      <c r="H78" s="1">
+        <v>8049.24</v>
+      </c>
+      <c r="I78" s="1">
+        <v>8660.05</v>
+      </c>
+      <c r="J78" t="str">
         <v/>
       </c>
     </row>
@@ -2202,21 +2904,30 @@
         <v>78</v>
       </c>
       <c r="B79" t="str">
-        <v>Wipro Limited</v>
+        <v>Hero Motocorp Limited</v>
       </c>
       <c r="C79" t="str">
-        <v>WIPRO</v>
+        <v>HEROMOTOCO</v>
       </c>
       <c r="D79" s="1">
-        <v>162.62</v>
+        <v>4997.5</v>
       </c>
       <c r="E79" s="2">
-        <v>0.03</v>
+        <v>1.23</v>
       </c>
       <c r="F79" s="1">
-        <v>2571699</v>
-      </c>
-      <c r="G79" t="str">
+        <v>401814</v>
+      </c>
+      <c r="G79" s="1">
+        <v>5313.37</v>
+      </c>
+      <c r="H79" s="1">
+        <v>5042.48</v>
+      </c>
+      <c r="I79" s="1">
+        <v>5418.32</v>
+      </c>
+      <c r="J79" t="str">
         <v/>
       </c>
     </row>
@@ -2225,21 +2936,30 @@
         <v>79</v>
       </c>
       <c r="B80" t="str">
-        <v>Vishal Mega Mart Ltd</v>
+        <v>Hyundai Motor India Ltd</v>
       </c>
       <c r="C80" t="str">
-        <v>VMM</v>
+        <v>HYUNDAI</v>
       </c>
       <c r="D80" s="1">
-        <v>97.52</v>
+        <v>1964.9</v>
       </c>
       <c r="E80" s="2">
-        <v>0.02</v>
+        <v>1.23</v>
       </c>
       <c r="F80" s="1">
-        <v>1151216</v>
-      </c>
-      <c r="G80" t="str">
+        <v>775850</v>
+      </c>
+      <c r="G80" s="1">
+        <v>2051.63</v>
+      </c>
+      <c r="H80" s="1">
+        <v>1984.61</v>
+      </c>
+      <c r="I80" s="1">
+        <v>2146.61</v>
+      </c>
+      <c r="J80" t="str">
         <v/>
       </c>
     </row>
@@ -2248,21 +2968,30 @@
         <v>80</v>
       </c>
       <c r="B81" t="str">
-        <v>Jio Financial Services Ltd</v>
+        <v>Axis Bank Limited</v>
       </c>
       <c r="C81" t="str">
-        <v>JIOFIN</v>
+        <v>AXISBANK</v>
       </c>
       <c r="D81" s="1">
-        <v>214.62</v>
+        <v>1268.4</v>
       </c>
       <c r="E81" s="2">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="F81" s="1">
-        <v>3267960</v>
-      </c>
-      <c r="G81" t="str">
+        <v>5319369</v>
+      </c>
+      <c r="G81" s="1">
+        <v>1284.7</v>
+      </c>
+      <c r="H81" s="1">
+        <v>1245.8</v>
+      </c>
+      <c r="I81" s="1">
+        <v>1243.59</v>
+      </c>
+      <c r="J81" t="str">
         <v/>
       </c>
     </row>
@@ -2271,21 +3000,30 @@
         <v>81</v>
       </c>
       <c r="B82" t="str">
-        <v>Maruti Suzuki India Limited</v>
+        <v>Power Finance Corporation Limited</v>
       </c>
       <c r="C82" t="str">
-        <v>MARUTI</v>
+        <v>PFC</v>
       </c>
       <c r="D82" s="1">
-        <v>11418</v>
+        <v>342.05</v>
       </c>
       <c r="E82" s="2">
-        <v>-0.02</v>
+        <v>1.23</v>
       </c>
       <c r="F82" s="1">
-        <v>78725</v>
-      </c>
-      <c r="G82" t="str">
+        <v>19754726</v>
+      </c>
+      <c r="G82" s="1">
+        <v>399.39</v>
+      </c>
+      <c r="H82" s="1">
+        <v>331.88</v>
+      </c>
+      <c r="I82" s="1">
+        <v>356.7</v>
+      </c>
+      <c r="J82" t="str">
         <v/>
       </c>
     </row>
@@ -2294,21 +3032,30 @@
         <v>82</v>
       </c>
       <c r="B83" t="str">
-        <v>Bajaj Finserv Limited</v>
+        <v>Itc Limited</v>
       </c>
       <c r="C83" t="str">
-        <v>BAJAJFINSV</v>
+        <v>ITC</v>
       </c>
       <c r="D83" s="1">
-        <v>1734</v>
+        <v>261</v>
       </c>
       <c r="E83" s="2">
-        <v>-0.04</v>
+        <v>1.2</v>
       </c>
       <c r="F83" s="1">
-        <v>142596</v>
-      </c>
-      <c r="G83" t="str">
+        <v>13041566</v>
+      </c>
+      <c r="G83" s="1">
+        <v>298.91</v>
+      </c>
+      <c r="H83" s="1">
+        <v>262.39</v>
+      </c>
+      <c r="I83" s="1">
+        <v>268.6</v>
+      </c>
+      <c r="J83" t="str">
         <v/>
       </c>
     </row>
@@ -2317,21 +3064,30 @@
         <v>83</v>
       </c>
       <c r="B84" t="str">
-        <v>Tata Motors Passenger Vehicles Ltd</v>
+        <v>Oil &amp; Natural Gas Corporation Limited</v>
       </c>
       <c r="C84" t="str">
-        <v>TMPV</v>
+        <v>ONGC</v>
       </c>
       <c r="D84" s="1">
-        <v>279.8</v>
+        <v>222.65</v>
       </c>
       <c r="E84" s="2">
-        <v>-0.04</v>
+        <v>1.2</v>
       </c>
       <c r="F84" s="1">
-        <v>2196490</v>
-      </c>
-      <c r="G84" t="str">
+        <v>5379165</v>
+      </c>
+      <c r="G84" s="1">
+        <v>256.08</v>
+      </c>
+      <c r="H84" s="1">
+        <v>223.93</v>
+      </c>
+      <c r="I84" s="1">
+        <v>233.75</v>
+      </c>
+      <c r="J84" t="str">
         <v/>
       </c>
     </row>
@@ -2340,21 +3096,30 @@
         <v>84</v>
       </c>
       <c r="B85" t="str">
-        <v>Bajaj Finance Limited</v>
+        <v>Dabur India Limited</v>
       </c>
       <c r="C85" t="str">
-        <v>BAJFINANCE</v>
+        <v>DABUR</v>
       </c>
       <c r="D85" s="1">
-        <v>959.4</v>
+        <v>378.75</v>
       </c>
       <c r="E85" s="2">
-        <v>-0.06</v>
+        <v>1.16</v>
       </c>
       <c r="F85" s="1">
-        <v>1388307</v>
-      </c>
-      <c r="G85" t="str">
+        <v>1006898</v>
+      </c>
+      <c r="G85" s="1">
+        <v>445.27</v>
+      </c>
+      <c r="H85" s="1">
+        <v>380.75</v>
+      </c>
+      <c r="I85" s="1">
+        <v>390.82</v>
+      </c>
+      <c r="J85" t="str">
         <v/>
       </c>
     </row>
@@ -2363,21 +3128,30 @@
         <v>85</v>
       </c>
       <c r="B86" t="str">
-        <v>Oil India Limited</v>
+        <v>ICICI Lombard General Insurance Company Ltd</v>
       </c>
       <c r="C86" t="str">
-        <v>OIL</v>
+        <v>ICICIGI</v>
       </c>
       <c r="D86" s="1">
-        <v>443.25</v>
+        <v>1691.8</v>
       </c>
       <c r="E86" s="2">
-        <v>-0.06</v>
+        <v>1.06</v>
       </c>
       <c r="F86" s="1">
-        <v>277233</v>
-      </c>
-      <c r="G86" t="str">
+        <v>590465</v>
+      </c>
+      <c r="G86" s="1">
+        <v>1757.86</v>
+      </c>
+      <c r="H86" s="1">
+        <v>1624.43</v>
+      </c>
+      <c r="I86" s="1">
+        <v>1575.3</v>
+      </c>
+      <c r="J86" t="str">
         <v/>
       </c>
     </row>
@@ -2386,21 +3160,30 @@
         <v>86</v>
       </c>
       <c r="B87" t="str">
-        <v>LTIMindtree Ltd</v>
+        <v>Swiggy Ltd</v>
       </c>
       <c r="C87" t="str">
-        <v>LTM</v>
+        <v>SWIGGY</v>
       </c>
       <c r="D87" s="1">
-        <v>4065.3</v>
+        <v>232.4</v>
       </c>
       <c r="E87" s="2">
-        <v>-0.12</v>
+        <v>1.04</v>
       </c>
       <c r="F87" s="1">
-        <v>105649</v>
-      </c>
-      <c r="G87" t="str">
+        <v>6063507</v>
+      </c>
+      <c r="G87" s="1">
+        <v>286.6</v>
+      </c>
+      <c r="H87" s="1">
+        <v>241.38</v>
+      </c>
+      <c r="I87" s="1">
+        <v>270.53</v>
+      </c>
+      <c r="J87" t="str">
         <v/>
       </c>
     </row>
@@ -2409,21 +3192,30 @@
         <v>87</v>
       </c>
       <c r="B88" t="str">
-        <v>Alkem Laboratories Limited</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="C88" t="str">
-        <v>ALKEM</v>
+        <v>BANKNIFTY</v>
       </c>
       <c r="D88" s="1">
-        <v>5272</v>
+        <v>55481.05</v>
       </c>
       <c r="E88" s="2">
-        <v>-0.13</v>
+        <v>1.03</v>
       </c>
       <c r="F88" s="1">
-        <v>64534</v>
-      </c>
-      <c r="G88" t="str">
+        <v>0</v>
+      </c>
+      <c r="G88" s="1">
+        <v>56982.16</v>
+      </c>
+      <c r="H88" s="1">
+        <v>55109.35</v>
+      </c>
+      <c r="I88" s="1">
+        <v>56623.5</v>
+      </c>
+      <c r="J88" t="str">
         <v/>
       </c>
     </row>
@@ -2432,21 +3224,30 @@
         <v>88</v>
       </c>
       <c r="B89" t="str">
-        <v>Godfrey Phillips India Limited</v>
+        <v>Delhivery Ltd</v>
       </c>
       <c r="C89" t="str">
-        <v>GODFRYPHLP</v>
+        <v>DELHIVERY</v>
       </c>
       <c r="D89" s="1">
-        <v>1810.9</v>
+        <v>416.4</v>
       </c>
       <c r="E89" s="2">
-        <v>-0.13</v>
+        <v>1.03</v>
       </c>
       <c r="F89" s="1">
-        <v>41067</v>
-      </c>
-      <c r="G89" t="str">
+        <v>1797486</v>
+      </c>
+      <c r="G89" s="1">
+        <v>444.32</v>
+      </c>
+      <c r="H89" s="1">
+        <v>409.46</v>
+      </c>
+      <c r="I89" s="1">
+        <v>441.95</v>
+      </c>
+      <c r="J89" t="str">
         <v/>
       </c>
     </row>
@@ -2455,21 +3256,30 @@
         <v>89</v>
       </c>
       <c r="B90" t="str">
-        <v>Nestle India Limited</v>
+        <v>Bharat Petroleum Corporation Limited</v>
       </c>
       <c r="C90" t="str">
-        <v>NESTLEIND</v>
+        <v>BPCL</v>
       </c>
       <c r="D90" s="1">
-        <v>1331.3</v>
+        <v>287.4</v>
       </c>
       <c r="E90" s="2">
-        <v>-0.13</v>
+        <v>1.02</v>
       </c>
       <c r="F90" s="1">
-        <v>279890</v>
-      </c>
-      <c r="G90" t="str">
+        <v>1659173</v>
+      </c>
+      <c r="G90" s="1">
+        <v>322.1</v>
+      </c>
+      <c r="H90" s="1">
+        <v>293.39</v>
+      </c>
+      <c r="I90" s="1">
+        <v>310.05</v>
+      </c>
+      <c r="J90" t="str">
         <v/>
       </c>
     </row>
@@ -2478,21 +3288,30 @@
         <v>90</v>
       </c>
       <c r="B91" t="str">
-        <v>Jubilant Foodworks Limited</v>
+        <v>Lupin Limited</v>
       </c>
       <c r="C91" t="str">
-        <v>JUBLFOOD</v>
+        <v>LUPIN</v>
       </c>
       <c r="D91" s="1">
-        <v>422.2</v>
+        <v>1953.6</v>
       </c>
       <c r="E91" s="2">
-        <v>-0.13</v>
+        <v>0.96</v>
       </c>
       <c r="F91" s="1">
-        <v>279837</v>
-      </c>
-      <c r="G91" t="str">
+        <v>701254</v>
+      </c>
+      <c r="G91" s="1">
+        <v>2252.47</v>
+      </c>
+      <c r="H91" s="1">
+        <v>1990.78</v>
+      </c>
+      <c r="I91" s="1">
+        <v>2147.16</v>
+      </c>
+      <c r="J91" t="str">
         <v/>
       </c>
     </row>
@@ -2501,21 +3320,30 @@
         <v>91</v>
       </c>
       <c r="B92" t="str">
-        <v>Shriram Finance Ltd</v>
+        <v>Force Motors Ltd</v>
       </c>
       <c r="C92" t="str">
-        <v>SHRIRAMFIN</v>
+        <v>FORCEMOT</v>
       </c>
       <c r="D92" s="1">
-        <v>939</v>
+        <v>17170</v>
       </c>
       <c r="E92" s="2">
-        <v>-0.15</v>
+        <v>0.94</v>
       </c>
       <c r="F92" s="1">
-        <v>399522</v>
-      </c>
-      <c r="G92" t="str">
+        <v>53428</v>
+      </c>
+      <c r="G92" s="1">
+        <v>19539</v>
+      </c>
+      <c r="H92" s="1">
+        <v>17012.77</v>
+      </c>
+      <c r="I92" s="1">
+        <v>17644.16</v>
+      </c>
+      <c r="J92" t="str">
         <v/>
       </c>
     </row>
@@ -2524,21 +3352,30 @@
         <v>92</v>
       </c>
       <c r="B93" t="str">
-        <v>Godrej Consumer Products Limited</v>
+        <v>GMR Airports Ltd</v>
       </c>
       <c r="C93" t="str">
-        <v>GODREJCP</v>
+        <v>GMRAIRPORT</v>
       </c>
       <c r="D93" s="1">
-        <v>859.1</v>
+        <v>90.34</v>
       </c>
       <c r="E93" s="2">
-        <v>-0.16</v>
+        <v>0.94</v>
       </c>
       <c r="F93" s="1">
-        <v>74669</v>
-      </c>
-      <c r="G93" t="str">
+        <v>13092457</v>
+      </c>
+      <c r="G93" s="1">
+        <v>99.49</v>
+      </c>
+      <c r="H93" s="1">
+        <v>91.89</v>
+      </c>
+      <c r="I93" s="1">
+        <v>98.02</v>
+      </c>
+      <c r="J93" t="str">
         <v/>
       </c>
     </row>
@@ -2547,21 +3384,30 @@
         <v>93</v>
       </c>
       <c r="B94" t="str">
-        <v>Grasim Industries Limited</v>
+        <v>Coal India Limited</v>
       </c>
       <c r="C94" t="str">
-        <v>GRASIM</v>
+        <v>COALINDIA</v>
       </c>
       <c r="D94" s="1">
-        <v>2883.9</v>
+        <v>408.5</v>
       </c>
       <c r="E94" s="2">
-        <v>-0.21</v>
+        <v>0.91</v>
       </c>
       <c r="F94" s="1">
-        <v>35017</v>
-      </c>
-      <c r="G94" t="str">
+        <v>4345847</v>
+      </c>
+      <c r="G94" s="1">
+        <v>433.67</v>
+      </c>
+      <c r="H94" s="1">
+        <v>413.43</v>
+      </c>
+      <c r="I94" s="1">
+        <v>414.34</v>
+      </c>
+      <c r="J94" t="str">
         <v/>
       </c>
     </row>
@@ -2570,21 +3416,30 @@
         <v>94</v>
       </c>
       <c r="B95" t="str">
-        <v>Hdfc Bank Limited</v>
+        <v>Alkem Laboratories Limited</v>
       </c>
       <c r="C95" t="str">
-        <v>HDFCBANK</v>
+        <v>ALKEM</v>
       </c>
       <c r="D95" s="1">
-        <v>705.7</v>
+        <v>5250</v>
       </c>
       <c r="E95" s="2">
-        <v>-0.22</v>
+        <v>0.86</v>
       </c>
       <c r="F95" s="1">
-        <v>7070219</v>
-      </c>
-      <c r="G95" t="str">
+        <v>101145</v>
+      </c>
+      <c r="G95" s="1">
+        <v>5474.26</v>
+      </c>
+      <c r="H95" s="1">
+        <v>5254.66</v>
+      </c>
+      <c r="I95" s="1">
+        <v>5337.64</v>
+      </c>
+      <c r="J95" t="str">
         <v/>
       </c>
     </row>
@@ -2593,21 +3448,30 @@
         <v>95</v>
       </c>
       <c r="B96" t="str">
-        <v>National Aluminium Company Limited</v>
+        <v>Dr. Reddy's Laboratories Limited</v>
       </c>
       <c r="C96" t="str">
-        <v>NATIONALUM</v>
+        <v>DRREDDY</v>
       </c>
       <c r="D96" s="1">
-        <v>315.2</v>
+        <v>1240</v>
       </c>
       <c r="E96" s="2">
-        <v>-0.22</v>
+        <v>0.86</v>
       </c>
       <c r="F96" s="1">
-        <v>895834</v>
-      </c>
-      <c r="G96" t="str">
+        <v>2374664</v>
+      </c>
+      <c r="G96" s="1">
+        <v>1244.73</v>
+      </c>
+      <c r="H96" s="1">
+        <v>1212.56</v>
+      </c>
+      <c r="I96" s="1">
+        <v>1184.68</v>
+      </c>
+      <c r="J96" t="str">
         <v/>
       </c>
     </row>
@@ -2616,21 +3480,30 @@
         <v>96</v>
       </c>
       <c r="B97" t="str">
-        <v>Mphasis Limited</v>
+        <v>Indus Towers Ltd (Bharti Infratel)</v>
       </c>
       <c r="C97" t="str">
-        <v>MPHASIS</v>
+        <v>INDUSTOWER</v>
       </c>
       <c r="D97" s="1">
-        <v>2354.6</v>
+        <v>378.75</v>
       </c>
       <c r="E97" s="2">
-        <v>-0.23</v>
+        <v>0.83</v>
       </c>
       <c r="F97" s="1">
-        <v>164677</v>
-      </c>
-      <c r="G97" t="str">
+        <v>1628164</v>
+      </c>
+      <c r="G97" s="1">
+        <v>412.5</v>
+      </c>
+      <c r="H97" s="1">
+        <v>378.16</v>
+      </c>
+      <c r="I97" s="1">
+        <v>378.51</v>
+      </c>
+      <c r="J97" t="str">
         <v/>
       </c>
     </row>
@@ -2639,21 +3512,30 @@
         <v>97</v>
       </c>
       <c r="B98" t="str">
-        <v>AU Small Finance Bank Ltd</v>
+        <v>360 ONE WAM Ltd</v>
       </c>
       <c r="C98" t="str">
-        <v>AUBANK</v>
+        <v>360ONE</v>
       </c>
       <c r="D98" s="1">
-        <v>979.5</v>
+        <v>1077.5</v>
       </c>
       <c r="E98" s="2">
-        <v>-0.25</v>
+        <v>0.82</v>
       </c>
       <c r="F98" s="1">
-        <v>177673</v>
-      </c>
-      <c r="G98" t="str">
+        <v>429283</v>
+      </c>
+      <c r="G98" s="1">
+        <v>1104.23</v>
+      </c>
+      <c r="H98" s="1">
+        <v>1060.9</v>
+      </c>
+      <c r="I98" s="1">
+        <v>1123.46</v>
+      </c>
+      <c r="J98" t="str">
         <v/>
       </c>
     </row>
@@ -2662,21 +3544,30 @@
         <v>98</v>
       </c>
       <c r="B99" t="str">
-        <v>Hcl Technologies Limited</v>
+        <v>Astral Ltd</v>
       </c>
       <c r="C99" t="str">
-        <v>HCLTECH</v>
+        <v>ASTRAL</v>
       </c>
       <c r="D99" s="1">
-        <v>1213.4</v>
+        <v>1442</v>
       </c>
       <c r="E99" s="2">
-        <v>-0.27</v>
+        <v>0.81</v>
       </c>
       <c r="F99" s="1">
-        <v>824092</v>
-      </c>
-      <c r="G99" t="str">
+        <v>260945</v>
+      </c>
+      <c r="G99" s="1">
+        <v>1502.22</v>
+      </c>
+      <c r="H99" s="1">
+        <v>1410.51</v>
+      </c>
+      <c r="I99" s="1">
+        <v>1455.02</v>
+      </c>
+      <c r="J99" t="str">
         <v/>
       </c>
     </row>
@@ -2685,21 +3576,30 @@
         <v>99</v>
       </c>
       <c r="B100" t="str">
-        <v>Infosys Limited</v>
+        <v>Oil India Limited</v>
       </c>
       <c r="C100" t="str">
-        <v>INFY</v>
+        <v>OIL</v>
       </c>
       <c r="D100" s="1">
-        <v>1020.6</v>
+        <v>445</v>
       </c>
       <c r="E100" s="2">
-        <v>-0.27</v>
+        <v>0.78</v>
       </c>
       <c r="F100" s="1">
-        <v>2603857</v>
-      </c>
-      <c r="G100" t="str">
+        <v>1102839</v>
+      </c>
+      <c r="G100" s="1">
+        <v>462.04</v>
+      </c>
+      <c r="H100" s="1">
+        <v>450.22</v>
+      </c>
+      <c r="I100" s="1">
+        <v>469.82</v>
+      </c>
+      <c r="J100" t="str">
         <v/>
       </c>
     </row>
@@ -2708,21 +3608,30 @@
         <v>100</v>
       </c>
       <c r="B101" t="str">
-        <v>Sun Pharmaceuticals Industries Limited</v>
+        <v>Vishal Mega Mart Ltd</v>
       </c>
       <c r="C101" t="str">
-        <v>SUNPHARMA</v>
+        <v>VMM</v>
       </c>
       <c r="D101" s="1">
-        <v>1755</v>
+        <v>97</v>
       </c>
       <c r="E101" s="2">
-        <v>-0.28</v>
+        <v>0.73</v>
       </c>
       <c r="F101" s="1">
-        <v>314714</v>
-      </c>
-      <c r="G101" t="str">
+        <v>6738626</v>
+      </c>
+      <c r="G101" s="1">
+        <v>115.64</v>
+      </c>
+      <c r="H101" s="1">
+        <v>98.89</v>
+      </c>
+      <c r="I101" s="1">
+        <v>104.69</v>
+      </c>
+      <c r="J101" t="str">
         <v/>
       </c>
     </row>
@@ -2731,21 +3640,30 @@
         <v>101</v>
       </c>
       <c r="B102" t="str">
-        <v>Titan Company Limited</v>
+        <v>Nestle India Limited</v>
       </c>
       <c r="C102" t="str">
-        <v>TITAN</v>
+        <v>NESTLEIND</v>
       </c>
       <c r="D102" s="1">
-        <v>4395.4</v>
+        <v>1334</v>
       </c>
       <c r="E102" s="2">
-        <v>-0.33</v>
+        <v>0.7</v>
       </c>
       <c r="F102" s="1">
-        <v>119347</v>
-      </c>
-      <c r="G102" t="str">
+        <v>3009096</v>
+      </c>
+      <c r="G102" s="1">
+        <v>1364.47</v>
+      </c>
+      <c r="H102" s="1">
+        <v>1331.84</v>
+      </c>
+      <c r="I102" s="1">
+        <v>1417.76</v>
+      </c>
+      <c r="J102" t="str">
         <v/>
       </c>
     </row>
@@ -2754,21 +3672,30 @@
         <v>102</v>
       </c>
       <c r="B103" t="str">
-        <v>Indusind Bank Limited</v>
+        <v>Bank Of India Ltd</v>
       </c>
       <c r="C103" t="str">
-        <v>INDUSINDBK</v>
+        <v>BANKINDIA</v>
       </c>
       <c r="D103" s="1">
-        <v>858.7</v>
+        <v>134.34</v>
       </c>
       <c r="E103" s="2">
-        <v>-0.34</v>
+        <v>0.7</v>
       </c>
       <c r="F103" s="1">
-        <v>2374609</v>
-      </c>
-      <c r="G103" t="str">
+        <v>7310473</v>
+      </c>
+      <c r="G103" s="1">
+        <v>146.77</v>
+      </c>
+      <c r="H103" s="1">
+        <v>133.66</v>
+      </c>
+      <c r="I103" s="1">
+        <v>139.64</v>
+      </c>
+      <c r="J103" t="str">
         <v/>
       </c>
     </row>
@@ -2777,21 +3704,30 @@
         <v>103</v>
       </c>
       <c r="B104" t="str">
-        <v>Premier Energies Ltd</v>
+        <v>Reliance Industries Limited</v>
       </c>
       <c r="C104" t="str">
-        <v>PREMIERENE</v>
+        <v>RELIANCE</v>
       </c>
       <c r="D104" s="1">
-        <v>892.1</v>
+        <v>1166.7</v>
       </c>
       <c r="E104" s="2">
-        <v>-0.36</v>
+        <v>0.67</v>
       </c>
       <c r="F104" s="1">
-        <v>695204</v>
-      </c>
-      <c r="G104" t="str">
+        <v>10530652</v>
+      </c>
+      <c r="G104" s="1">
+        <v>1350.78</v>
+      </c>
+      <c r="H104" s="1">
+        <v>1185.33</v>
+      </c>
+      <c r="I104" s="1">
+        <v>1266.29</v>
+      </c>
+      <c r="J104" t="str">
         <v/>
       </c>
     </row>
@@ -2800,21 +3736,30 @@
         <v>104</v>
       </c>
       <c r="B105" t="str">
-        <v>NIFTY</v>
+        <v>Life Insurance Corporation of India Ltd</v>
       </c>
       <c r="C105" t="str">
-        <v>NIFTY</v>
+        <v>LICI</v>
       </c>
       <c r="D105" s="1">
-        <v>22430.35</v>
+        <v>394.05</v>
       </c>
       <c r="E105" s="2">
-        <v>-0.4</v>
+        <v>0.65</v>
       </c>
       <c r="F105" s="1">
-        <v>0</v>
-      </c>
-      <c r="G105" t="str">
+        <v>4671031</v>
+      </c>
+      <c r="G105" s="1">
+        <v>411.84</v>
+      </c>
+      <c r="H105" s="1">
+        <v>392.28</v>
+      </c>
+      <c r="I105" s="1">
+        <v>404.82</v>
+      </c>
+      <c r="J105" t="str">
         <v/>
       </c>
     </row>
@@ -2823,21 +3768,30 @@
         <v>105</v>
       </c>
       <c r="B106" t="str">
-        <v>Kaynes Technology India Ltd</v>
+        <v>Indian Oil Corporation Limited</v>
       </c>
       <c r="C106" t="str">
-        <v>KAYNES</v>
+        <v>IOC</v>
       </c>
       <c r="D106" s="1">
-        <v>3250.2</v>
+        <v>126.14</v>
       </c>
       <c r="E106" s="2">
-        <v>-0.42</v>
+        <v>0.63</v>
       </c>
       <c r="F106" s="1">
-        <v>227700</v>
-      </c>
-      <c r="G106" t="str">
+        <v>5183996</v>
+      </c>
+      <c r="G106" s="1">
+        <v>147.43</v>
+      </c>
+      <c r="H106" s="1">
+        <v>128.97</v>
+      </c>
+      <c r="I106" s="1">
+        <v>136.16</v>
+      </c>
+      <c r="J106" t="str">
         <v/>
       </c>
     </row>
@@ -2846,21 +3800,30 @@
         <v>106</v>
       </c>
       <c r="B107" t="str">
-        <v>ICICI Lombard General Insurance Company Ltd</v>
+        <v>Eicher Motors Limited</v>
       </c>
       <c r="C107" t="str">
-        <v>ICICIGI</v>
+        <v>EICHERMOT</v>
       </c>
       <c r="D107" s="1">
-        <v>1683.1</v>
+        <v>7163</v>
       </c>
       <c r="E107" s="2">
-        <v>-0.42</v>
+        <v>0.62</v>
       </c>
       <c r="F107" s="1">
-        <v>74003</v>
-      </c>
-      <c r="G107" t="str">
+        <v>334413</v>
+      </c>
+      <c r="G107" s="1">
+        <v>7401.3</v>
+      </c>
+      <c r="H107" s="1">
+        <v>7096.64</v>
+      </c>
+      <c r="I107" s="1">
+        <v>7651.15</v>
+      </c>
+      <c r="J107" t="str">
         <v/>
       </c>
     </row>
@@ -2869,21 +3832,30 @@
         <v>107</v>
       </c>
       <c r="B108" t="str">
-        <v>United Spirits Ltd</v>
+        <v>Sun Pharmaceuticals Industries Limited</v>
       </c>
       <c r="C108" t="str">
-        <v>UNITDSPR</v>
+        <v>SUNPHARMA</v>
       </c>
       <c r="D108" s="1">
-        <v>1360</v>
+        <v>1770.7</v>
       </c>
       <c r="E108" s="2">
-        <v>-0.44</v>
+        <v>0.61</v>
       </c>
       <c r="F108" s="1">
-        <v>67084</v>
-      </c>
-      <c r="G108" t="str">
+        <v>1091078</v>
+      </c>
+      <c r="G108" s="1">
+        <v>1807.46</v>
+      </c>
+      <c r="H108" s="1">
+        <v>1787.46</v>
+      </c>
+      <c r="I108" s="1">
+        <v>1878.06</v>
+      </c>
+      <c r="J108" t="str">
         <v/>
       </c>
     </row>
@@ -2892,21 +3864,30 @@
         <v>108</v>
       </c>
       <c r="B109" t="str">
-        <v>SBI Life Insurance Company Ltd</v>
+        <v>Power Grid Corporation Of India Limited</v>
       </c>
       <c r="C109" t="str">
-        <v>SBILIFE</v>
+        <v>POWERGRID</v>
       </c>
       <c r="D109" s="1">
-        <v>1677.1</v>
+        <v>250.5</v>
       </c>
       <c r="E109" s="2">
-        <v>-0.45</v>
+        <v>0.6</v>
       </c>
       <c r="F109" s="1">
-        <v>71035</v>
-      </c>
-      <c r="G109" t="str">
+        <v>11688774</v>
+      </c>
+      <c r="G109" s="1">
+        <v>283.44</v>
+      </c>
+      <c r="H109" s="1">
+        <v>253.55</v>
+      </c>
+      <c r="I109" s="1">
+        <v>265.4</v>
+      </c>
+      <c r="J109" t="str">
         <v/>
       </c>
     </row>
@@ -2915,21 +3896,30 @@
         <v>109</v>
       </c>
       <c r="B110" t="str">
-        <v>Lupin Limited</v>
+        <v>Ambuja Cements Limited</v>
       </c>
       <c r="C110" t="str">
-        <v>LUPIN</v>
+        <v>AMBUJACEM</v>
       </c>
       <c r="D110" s="1">
-        <v>1947.2</v>
+        <v>350</v>
       </c>
       <c r="E110" s="2">
-        <v>-0.48</v>
+        <v>0.57</v>
       </c>
       <c r="F110" s="1">
-        <v>69216</v>
-      </c>
-      <c r="G110" t="str">
+        <v>2446887</v>
+      </c>
+      <c r="G110" s="1">
+        <v>450</v>
+      </c>
+      <c r="H110" s="1">
+        <v>357.95</v>
+      </c>
+      <c r="I110" s="1">
+        <v>397.1</v>
+      </c>
+      <c r="J110" t="str">
         <v/>
       </c>
     </row>
@@ -2938,21 +3928,30 @@
         <v>110</v>
       </c>
       <c r="B111" t="str">
-        <v>Nhpc Limited</v>
+        <v>Britannia Industries Limited</v>
       </c>
       <c r="C111" t="str">
-        <v>NHPC</v>
+        <v>BRITANNIA</v>
       </c>
       <c r="D111" s="1">
-        <v>72.63</v>
+        <v>4801.3</v>
       </c>
       <c r="E111" s="2">
-        <v>-0.49</v>
+        <v>0.56</v>
       </c>
       <c r="F111" s="1">
-        <v>1270613</v>
-      </c>
-      <c r="G111" t="str">
+        <v>55722</v>
+      </c>
+      <c r="G111" s="1">
+        <v>5518.11</v>
+      </c>
+      <c r="H111" s="1">
+        <v>4819.25</v>
+      </c>
+      <c r="I111" s="1">
+        <v>5159.05</v>
+      </c>
+      <c r="J111" t="str">
         <v/>
       </c>
     </row>
@@ -2961,21 +3960,30 @@
         <v>111</v>
       </c>
       <c r="B112" t="str">
-        <v>Hindalco Industries Limited</v>
+        <v>Avenue Supermarts Ltd</v>
       </c>
       <c r="C112" t="str">
-        <v>HINDALCO</v>
+        <v>DMART</v>
       </c>
       <c r="D112" s="1">
-        <v>895.45</v>
+        <v>3383</v>
       </c>
       <c r="E112" s="2">
-        <v>-0.54</v>
+        <v>0.54</v>
       </c>
       <c r="F112" s="1">
-        <v>768519</v>
-      </c>
-      <c r="G112" t="str">
+        <v>419296</v>
+      </c>
+      <c r="G112" s="1">
+        <v>3985.57</v>
+      </c>
+      <c r="H112" s="1">
+        <v>3560.29</v>
+      </c>
+      <c r="I112" s="1">
+        <v>3811.33</v>
+      </c>
+      <c r="J112" t="str">
         <v/>
       </c>
     </row>
@@ -2984,21 +3992,30 @@
         <v>112</v>
       </c>
       <c r="B113" t="str">
-        <v>Sagility India Ltd</v>
+        <v>Union Bank Of India Ltd</v>
       </c>
       <c r="C113" t="str">
-        <v>SAGILITY</v>
+        <v>UNIONBANK</v>
       </c>
       <c r="D113" s="1">
-        <v>43.76</v>
+        <v>172.22</v>
       </c>
       <c r="E113" s="2">
-        <v>-0.55</v>
+        <v>0.52</v>
       </c>
       <c r="F113" s="1">
-        <v>1950154</v>
-      </c>
-      <c r="G113" t="str">
+        <v>11426781</v>
+      </c>
+      <c r="G113" s="1">
+        <v>174.75</v>
+      </c>
+      <c r="H113" s="1">
+        <v>172.07</v>
+      </c>
+      <c r="I113" s="1">
+        <v>179.94</v>
+      </c>
+      <c r="J113" t="str">
         <v/>
       </c>
     </row>
@@ -3007,21 +4024,30 @@
         <v>113</v>
       </c>
       <c r="B114" t="str">
-        <v>Coal India Limited</v>
+        <v>Uno Minda Ltd</v>
       </c>
       <c r="C114" t="str">
-        <v>COALINDIA</v>
+        <v>UNOMINDA</v>
       </c>
       <c r="D114" s="1">
-        <v>409.05</v>
+        <v>1110</v>
       </c>
       <c r="E114" s="2">
-        <v>-0.61</v>
+        <v>0.51</v>
       </c>
       <c r="F114" s="1">
-        <v>523739</v>
-      </c>
-      <c r="G114" t="str">
+        <v>473604</v>
+      </c>
+      <c r="G114" s="1">
+        <v>1161.1</v>
+      </c>
+      <c r="H114" s="1">
+        <v>1124.09</v>
+      </c>
+      <c r="I114" s="1">
+        <v>1218.57</v>
+      </c>
+      <c r="J114" t="str">
         <v/>
       </c>
     </row>
@@ -3030,21 +4056,30 @@
         <v>114</v>
       </c>
       <c r="B115" t="str">
-        <v>Ambuja Cements Limited</v>
+        <v>Hindustan Zinc Limited</v>
       </c>
       <c r="C115" t="str">
-        <v>AMBUJACEM</v>
+        <v>HINDZINC</v>
       </c>
       <c r="D115" s="1">
-        <v>349.35</v>
+        <v>549.6</v>
       </c>
       <c r="E115" s="2">
-        <v>-0.61</v>
+        <v>0.49</v>
       </c>
       <c r="F115" s="1">
-        <v>635153</v>
-      </c>
-      <c r="G115" t="str">
+        <v>1348145</v>
+      </c>
+      <c r="G115" s="1">
+        <v>586.3</v>
+      </c>
+      <c r="H115" s="1">
+        <v>554</v>
+      </c>
+      <c r="I115" s="1">
+        <v>579.84</v>
+      </c>
+      <c r="J115" t="str">
         <v/>
       </c>
     </row>
@@ -3053,21 +4088,30 @@
         <v>115</v>
       </c>
       <c r="B116" t="str">
-        <v>Apollo Hospitals Enterprise Limited</v>
+        <v>Tata Motors Passenger Vehicles Ltd</v>
       </c>
       <c r="C116" t="str">
-        <v>APOLLOHOSP</v>
+        <v>TMPV</v>
       </c>
       <c r="D116" s="1">
-        <v>7978</v>
+        <v>285.85</v>
       </c>
       <c r="E116" s="2">
-        <v>-0.62</v>
+        <v>0.49</v>
       </c>
       <c r="F116" s="1">
-        <v>258835</v>
-      </c>
-      <c r="G116" t="str">
+        <v>9083879</v>
+      </c>
+      <c r="G116" s="1">
+        <v>342.4</v>
+      </c>
+      <c r="H116" s="1">
+        <v>284.51</v>
+      </c>
+      <c r="I116" s="1">
+        <v>310.83</v>
+      </c>
+      <c r="J116" t="str">
         <v/>
       </c>
     </row>
@@ -3076,21 +4120,30 @@
         <v>116</v>
       </c>
       <c r="B117" t="str">
-        <v>Nmdc Limited</v>
+        <v>SBI Life Insurance Company Ltd</v>
       </c>
       <c r="C117" t="str">
-        <v>NMDC</v>
+        <v>SBILIFE</v>
       </c>
       <c r="D117" s="1">
-        <v>71.35</v>
+        <v>1687.2</v>
       </c>
       <c r="E117" s="2">
-        <v>-0.63</v>
+        <v>0.38</v>
       </c>
       <c r="F117" s="1">
-        <v>4615481</v>
-      </c>
-      <c r="G117" t="str">
+        <v>1566802</v>
+      </c>
+      <c r="G117" s="1">
+        <v>1872.17</v>
+      </c>
+      <c r="H117" s="1">
+        <v>1704.16</v>
+      </c>
+      <c r="I117" s="1">
+        <v>1757.84</v>
+      </c>
+      <c r="J117" t="str">
         <v/>
       </c>
     </row>
@@ -3099,21 +4152,30 @@
         <v>117</v>
       </c>
       <c r="B118" t="str">
-        <v>Reliance Industries Limited</v>
+        <v>Tata Power Company Limited</v>
       </c>
       <c r="C118" t="str">
-        <v>RELIANCE</v>
+        <v>TATAPOWER</v>
       </c>
       <c r="D118" s="1">
-        <v>1162.7</v>
+        <v>345</v>
       </c>
       <c r="E118" s="2">
-        <v>-0.65</v>
+        <v>0.38</v>
       </c>
       <c r="F118" s="1">
-        <v>3246642</v>
-      </c>
-      <c r="G118" t="str">
+        <v>2311910</v>
+      </c>
+      <c r="G118" s="1">
+        <v>384.79</v>
+      </c>
+      <c r="H118" s="1">
+        <v>348.3</v>
+      </c>
+      <c r="I118" s="1">
+        <v>365.75</v>
+      </c>
+      <c r="J118" t="str">
         <v/>
       </c>
     </row>
@@ -3122,21 +4184,30 @@
         <v>118</v>
       </c>
       <c r="B119" t="str">
-        <v>Varun Beverages Limited</v>
+        <v>Supreme Industries Limited</v>
       </c>
       <c r="C119" t="str">
-        <v>VBL</v>
+        <v>SUPREMEIND</v>
       </c>
       <c r="D119" s="1">
-        <v>438.15</v>
+        <v>3506.9</v>
       </c>
       <c r="E119" s="2">
-        <v>-0.65</v>
+        <v>0.37</v>
       </c>
       <c r="F119" s="1">
-        <v>1015791</v>
-      </c>
-      <c r="G119" t="str">
+        <v>76164</v>
+      </c>
+      <c r="G119" s="1">
+        <v>3576.08</v>
+      </c>
+      <c r="H119" s="1">
+        <v>3480.62</v>
+      </c>
+      <c r="I119" s="1">
+        <v>3505.11</v>
+      </c>
+      <c r="J119" t="str">
         <v/>
       </c>
     </row>
@@ -3145,21 +4216,30 @@
         <v>119</v>
       </c>
       <c r="B120" t="str">
-        <v>Pidilite Industries Limited</v>
+        <v>Ntpc Limited</v>
       </c>
       <c r="C120" t="str">
-        <v>PIDILITIND</v>
+        <v>NTPC</v>
       </c>
       <c r="D120" s="1">
-        <v>1472</v>
+        <v>311</v>
       </c>
       <c r="E120" s="2">
-        <v>-0.67</v>
+        <v>0.32</v>
       </c>
       <c r="F120" s="1">
-        <v>187352</v>
-      </c>
-      <c r="G120" t="str">
+        <v>5742612</v>
+      </c>
+      <c r="G120" s="1">
+        <v>357.25</v>
+      </c>
+      <c r="H120" s="1">
+        <v>315.67</v>
+      </c>
+      <c r="I120" s="1">
+        <v>330.8</v>
+      </c>
+      <c r="J120" t="str">
         <v/>
       </c>
     </row>
@@ -3168,21 +4248,30 @@
         <v>120</v>
       </c>
       <c r="B121" t="str">
-        <v>BANKNIFTY</v>
+        <v>Jsw Steel Limited</v>
       </c>
       <c r="C121" t="str">
-        <v>BANKNIFTY</v>
+        <v>JSWSTEEL</v>
       </c>
       <c r="D121" s="1">
-        <v>54875</v>
+        <v>1176.6</v>
       </c>
       <c r="E121" s="2">
-        <v>-0.69</v>
+        <v>0.31</v>
       </c>
       <c r="F121" s="1">
-        <v>0</v>
-      </c>
-      <c r="G121" t="str">
+        <v>722404</v>
+      </c>
+      <c r="G121" s="1">
+        <v>1239.45</v>
+      </c>
+      <c r="H121" s="1">
+        <v>1209.3</v>
+      </c>
+      <c r="I121" s="1">
+        <v>1277.69</v>
+      </c>
+      <c r="J121" t="str">
         <v/>
       </c>
     </row>
@@ -3191,21 +4280,30 @@
         <v>121</v>
       </c>
       <c r="B122" t="str">
-        <v>Biocon Limited</v>
+        <v>Srf Limited</v>
       </c>
       <c r="C122" t="str">
-        <v>BIOCON</v>
+        <v>SRF</v>
       </c>
       <c r="D122" s="1">
-        <v>346.95</v>
+        <v>2492</v>
       </c>
       <c r="E122" s="2">
-        <v>-0.7</v>
+        <v>0.14</v>
       </c>
       <c r="F122" s="1">
-        <v>558267</v>
-      </c>
-      <c r="G122" t="str">
+        <v>127025</v>
+      </c>
+      <c r="G122" s="1">
+        <v>2675.44</v>
+      </c>
+      <c r="H122" s="1">
+        <v>2489.6</v>
+      </c>
+      <c r="I122" s="1">
+        <v>2549.73</v>
+      </c>
+      <c r="J122" t="str">
         <v/>
       </c>
     </row>
@@ -3214,21 +4312,30 @@
         <v>122</v>
       </c>
       <c r="B123" t="str">
-        <v>Oil &amp; Natural Gas Corporation Limited</v>
+        <v>TATA Consumer Products Ltd</v>
       </c>
       <c r="C123" t="str">
-        <v>ONGC</v>
+        <v>TATACONSUM</v>
       </c>
       <c r="D123" s="1">
-        <v>219.72</v>
+        <v>960</v>
       </c>
       <c r="E123" s="2">
-        <v>-0.7</v>
+        <v>0.13</v>
       </c>
       <c r="F123" s="1">
-        <v>2016053</v>
-      </c>
-      <c r="G123" t="str">
+        <v>1701492</v>
+      </c>
+      <c r="G123" s="1">
+        <v>1106.19</v>
+      </c>
+      <c r="H123" s="1">
+        <v>963.36</v>
+      </c>
+      <c r="I123" s="1">
+        <v>1021.64</v>
+      </c>
+      <c r="J123" t="str">
         <v/>
       </c>
     </row>
@@ -3237,21 +4344,30 @@
         <v>123</v>
       </c>
       <c r="B124" t="str">
-        <v>Adani Power Limited</v>
+        <v>HDFC Life Insurance Company Ltd</v>
       </c>
       <c r="C124" t="str">
-        <v>ADANIPOWER</v>
+        <v>HDFCLIFE</v>
       </c>
       <c r="D124" s="1">
-        <v>187.65</v>
+        <v>560</v>
       </c>
       <c r="E124" s="2">
-        <v>-0.71</v>
+        <v>0.13</v>
       </c>
       <c r="F124" s="1">
-        <v>5758954</v>
-      </c>
-      <c r="G124" t="str">
+        <v>1531011</v>
+      </c>
+      <c r="G124" s="1">
+        <v>614.78</v>
+      </c>
+      <c r="H124" s="1">
+        <v>547.78</v>
+      </c>
+      <c r="I124" s="1">
+        <v>540.89</v>
+      </c>
+      <c r="J124" t="str">
         <v/>
       </c>
     </row>
@@ -3260,21 +4376,30 @@
         <v>124</v>
       </c>
       <c r="B125" t="str">
-        <v>Britannia Industries Limited</v>
+        <v>Nhpc Limited</v>
       </c>
       <c r="C125" t="str">
-        <v>BRITANNIA</v>
+        <v>NHPC</v>
       </c>
       <c r="D125" s="1">
-        <v>4788.4</v>
+        <v>73.49</v>
       </c>
       <c r="E125" s="2">
-        <v>-0.76</v>
+        <v>0.12</v>
       </c>
       <c r="F125" s="1">
-        <v>12448</v>
-      </c>
-      <c r="G125" t="str">
+        <v>3216456</v>
+      </c>
+      <c r="G125" s="1">
+        <v>77.56</v>
+      </c>
+      <c r="H125" s="1">
+        <v>73.26</v>
+      </c>
+      <c r="I125" s="1">
+        <v>75.79</v>
+      </c>
+      <c r="J125" t="str">
         <v/>
       </c>
     </row>
@@ -3283,21 +4408,30 @@
         <v>125</v>
       </c>
       <c r="B126" t="str">
-        <v>Axis Bank Limited</v>
+        <v>Interglobe Aviation Limited</v>
       </c>
       <c r="C126" t="str">
-        <v>AXISBANK</v>
+        <v>INDIGO</v>
       </c>
       <c r="D126" s="1">
-        <v>1249.5</v>
+        <v>4800.4</v>
       </c>
       <c r="E126" s="2">
-        <v>-0.76</v>
+        <v>0.11</v>
       </c>
       <c r="F126" s="1">
-        <v>2035872</v>
-      </c>
-      <c r="G126" t="str">
+        <v>389201</v>
+      </c>
+      <c r="G126" s="1">
+        <v>4820.15</v>
+      </c>
+      <c r="H126" s="1">
+        <v>4876.47</v>
+      </c>
+      <c r="I126" s="1">
+        <v>5069.61</v>
+      </c>
+      <c r="J126" t="str">
         <v/>
       </c>
     </row>
@@ -3306,21 +4440,30 @@
         <v>126</v>
       </c>
       <c r="B127" t="str">
-        <v>Yes Bank Limited</v>
+        <v>Marico Limited</v>
       </c>
       <c r="C127" t="str">
-        <v>YESBANK</v>
+        <v>MARICO</v>
       </c>
       <c r="D127" s="1">
-        <v>20.34</v>
+        <v>782.8</v>
       </c>
       <c r="E127" s="2">
-        <v>-0.78</v>
+        <v>0.05</v>
       </c>
       <c r="F127" s="1">
-        <v>24727698</v>
-      </c>
-      <c r="G127" t="str">
+        <v>2262029</v>
+      </c>
+      <c r="G127" s="1">
+        <v>799.4</v>
+      </c>
+      <c r="H127" s="1">
+        <v>789.14</v>
+      </c>
+      <c r="I127" s="1">
+        <v>825.47</v>
+      </c>
+      <c r="J127" t="str">
         <v/>
       </c>
     </row>
@@ -3329,21 +4472,30 @@
         <v>127</v>
       </c>
       <c r="B128" t="str">
-        <v>Indian Bank Ltd</v>
+        <v>Adani Power Limited</v>
       </c>
       <c r="C128" t="str">
-        <v>INDIANB</v>
+        <v>ADANIPOWER</v>
       </c>
       <c r="D128" s="1">
-        <v>823.15</v>
+        <v>185.96</v>
       </c>
       <c r="E128" s="2">
-        <v>-0.8</v>
+        <v>0.03</v>
       </c>
       <c r="F128" s="1">
-        <v>205942</v>
-      </c>
-      <c r="G128" t="str">
+        <v>14707972</v>
+      </c>
+      <c r="G128" s="1">
+        <v>188.87</v>
+      </c>
+      <c r="H128" s="1">
+        <v>193.07</v>
+      </c>
+      <c r="I128" s="1">
+        <v>204.23</v>
+      </c>
+      <c r="J128" t="str">
         <v/>
       </c>
     </row>
@@ -3352,21 +4504,30 @@
         <v>128</v>
       </c>
       <c r="B129" t="str">
-        <v>Marico Limited</v>
+        <v>Cummins India Limited</v>
       </c>
       <c r="C129" t="str">
-        <v>MARICO</v>
+        <v>CUMMINSIND</v>
       </c>
       <c r="D129" s="1">
-        <v>779.65</v>
+        <v>4834.6</v>
       </c>
       <c r="E129" s="2">
-        <v>-0.83</v>
+        <v>-0.01</v>
       </c>
       <c r="F129" s="1">
-        <v>228041</v>
-      </c>
-      <c r="G129" t="str">
+        <v>287245</v>
+      </c>
+      <c r="G129" s="1">
+        <v>5010.28</v>
+      </c>
+      <c r="H129" s="1">
+        <v>4850.25</v>
+      </c>
+      <c r="I129" s="1">
+        <v>5110.39</v>
+      </c>
+      <c r="J129" t="str">
         <v/>
       </c>
     </row>
@@ -3375,21 +4536,30 @@
         <v>129</v>
       </c>
       <c r="B130" t="str">
-        <v>Life Insurance Corporation of India Ltd</v>
+        <v>Pi Industries Limited</v>
       </c>
       <c r="C130" t="str">
-        <v>LICI</v>
+        <v>PIIND</v>
       </c>
       <c r="D130" s="1">
-        <v>390.95</v>
+        <v>2130</v>
       </c>
       <c r="E130" s="2">
-        <v>-0.84</v>
+        <v>-0.07</v>
       </c>
       <c r="F130" s="1">
-        <v>1141131</v>
-      </c>
-      <c r="G130" t="str">
+        <v>334072</v>
+      </c>
+      <c r="G130" s="1">
+        <v>2825.24</v>
+      </c>
+      <c r="H130" s="1">
+        <v>2193.12</v>
+      </c>
+      <c r="I130" s="1">
+        <v>2421.71</v>
+      </c>
+      <c r="J130" t="str">
         <v/>
       </c>
     </row>
@@ -3398,21 +4568,30 @@
         <v>130</v>
       </c>
       <c r="B131" t="str">
-        <v>Bank Of Baroda Ltd</v>
+        <v>Fortis Healthcare Limited</v>
       </c>
       <c r="C131" t="str">
-        <v>BANKBARODA</v>
+        <v>FORTIS</v>
       </c>
       <c r="D131" s="1">
-        <v>233.8</v>
+        <v>756.4</v>
       </c>
       <c r="E131" s="2">
-        <v>-0.85</v>
+        <v>-0.11</v>
       </c>
       <c r="F131" s="1">
-        <v>1124252</v>
-      </c>
-      <c r="G131" t="str">
+        <v>2074542</v>
+      </c>
+      <c r="G131" s="1">
+        <v>905.92</v>
+      </c>
+      <c r="H131" s="1">
+        <v>782.84</v>
+      </c>
+      <c r="I131" s="1">
+        <v>880.59</v>
+      </c>
+      <c r="J131" t="str">
         <v/>
       </c>
     </row>
@@ -3421,21 +4600,30 @@
         <v>131</v>
       </c>
       <c r="B132" t="str">
-        <v>Fortis Healthcare Limited</v>
+        <v>Pg Electroplast Limited</v>
       </c>
       <c r="C132" t="str">
-        <v>FORTIS</v>
+        <v>PGEL</v>
       </c>
       <c r="D132" s="1">
-        <v>779.2</v>
+        <v>524.05</v>
       </c>
       <c r="E132" s="2">
-        <v>-0.9</v>
+        <v>-0.18</v>
       </c>
       <c r="F132" s="1">
-        <v>165258</v>
-      </c>
-      <c r="G132" t="str">
+        <v>575641</v>
+      </c>
+      <c r="G132" s="1">
+        <v>551.89</v>
+      </c>
+      <c r="H132" s="1">
+        <v>515.49</v>
+      </c>
+      <c r="I132" s="1">
+        <v>559.77</v>
+      </c>
+      <c r="J132" t="str">
         <v/>
       </c>
     </row>
@@ -3444,21 +4632,30 @@
         <v>132</v>
       </c>
       <c r="B133" t="str">
-        <v>Larsen &amp; Toubro Limited</v>
+        <v>Kei Industries Limited</v>
       </c>
       <c r="C133" t="str">
-        <v>LT</v>
+        <v>KEI</v>
       </c>
       <c r="D133" s="1">
-        <v>3669.5</v>
+        <v>4640.6</v>
       </c>
       <c r="E133" s="2">
-        <v>-0.91</v>
+        <v>-0.29</v>
       </c>
       <c r="F133" s="1">
-        <v>233863</v>
-      </c>
-      <c r="G133" t="str">
+        <v>329969</v>
+      </c>
+      <c r="G133" s="1">
+        <v>4838.99</v>
+      </c>
+      <c r="H133" s="1">
+        <v>4609.48</v>
+      </c>
+      <c r="I133" s="1">
+        <v>5070.57</v>
+      </c>
+      <c r="J133" t="str">
         <v/>
       </c>
     </row>
@@ -3467,21 +4664,30 @@
         <v>133</v>
       </c>
       <c r="B134" t="str">
-        <v>Colgate Palmolive (india) Limited</v>
+        <v>Muthoot Finance Limited</v>
       </c>
       <c r="C134" t="str">
-        <v>COLPAL</v>
+        <v>MUTHOOTFIN</v>
       </c>
       <c r="D134" s="1">
-        <v>1801.2</v>
+        <v>2626</v>
       </c>
       <c r="E134" s="2">
-        <v>-0.91</v>
+        <v>-0.31</v>
       </c>
       <c r="F134" s="1">
-        <v>123331</v>
-      </c>
-      <c r="G134" t="str">
+        <v>654434</v>
+      </c>
+      <c r="G134" s="1">
+        <v>3272.41</v>
+      </c>
+      <c r="H134" s="1">
+        <v>2668.6</v>
+      </c>
+      <c r="I134" s="1">
+        <v>2858.17</v>
+      </c>
+      <c r="J134" t="str">
         <v/>
       </c>
     </row>
@@ -3490,21 +4696,30 @@
         <v>134</v>
       </c>
       <c r="B135" t="str">
-        <v>Patanjali Foods Ltd</v>
+        <v>Premier Energies Ltd</v>
       </c>
       <c r="C135" t="str">
-        <v>PATANJALI</v>
+        <v>PREMIERENE</v>
       </c>
       <c r="D135" s="1">
-        <v>357.15</v>
+        <v>906</v>
       </c>
       <c r="E135" s="2">
-        <v>-0.92</v>
+        <v>-0.31</v>
       </c>
       <c r="F135" s="1">
-        <v>651653</v>
-      </c>
-      <c r="G135" t="str">
+        <v>785500</v>
+      </c>
+      <c r="G135" s="1">
+        <v>931.39</v>
+      </c>
+      <c r="H135" s="1">
+        <v>900.39</v>
+      </c>
+      <c r="I135" s="1">
+        <v>970.4</v>
+      </c>
+      <c r="J135" t="str">
         <v/>
       </c>
     </row>
@@ -3513,21 +4728,30 @@
         <v>135</v>
       </c>
       <c r="B136" t="str">
-        <v>Icici Bank Limited</v>
+        <v>Max Healthcare Institute Ltd</v>
       </c>
       <c r="C136" t="str">
-        <v>ICICIBANK</v>
+        <v>MAXHEALTH</v>
       </c>
       <c r="D136" s="1">
-        <v>1342</v>
+        <v>861</v>
       </c>
       <c r="E136" s="2">
-        <v>-0.96</v>
+        <v>-0.57</v>
       </c>
       <c r="F136" s="1">
-        <v>3282871</v>
-      </c>
-      <c r="G136" t="str">
+        <v>3899078</v>
+      </c>
+      <c r="G136" s="1">
+        <v>1026.9</v>
+      </c>
+      <c r="H136" s="1">
+        <v>907.97</v>
+      </c>
+      <c r="I136" s="1">
+        <v>1003.05</v>
+      </c>
+      <c r="J136" t="str">
         <v/>
       </c>
     </row>
@@ -3536,21 +4760,30 @@
         <v>136</v>
       </c>
       <c r="B137" t="str">
-        <v>Srf Limited</v>
+        <v>Maruti Suzuki India Limited</v>
       </c>
       <c r="C137" t="str">
-        <v>SRF</v>
+        <v>MARUTI</v>
       </c>
       <c r="D137" s="1">
-        <v>2495</v>
+        <v>11245</v>
       </c>
       <c r="E137" s="2">
-        <v>-0.97</v>
+        <v>-0.62</v>
       </c>
       <c r="F137" s="1">
-        <v>28696</v>
-      </c>
-      <c r="G137" t="str">
+        <v>743863</v>
+      </c>
+      <c r="G137" s="1">
+        <v>13794.66</v>
+      </c>
+      <c r="H137" s="1">
+        <v>11512.38</v>
+      </c>
+      <c r="I137" s="1">
+        <v>12818</v>
+      </c>
+      <c r="J137" t="str">
         <v/>
       </c>
     </row>
@@ -3559,21 +4792,30 @@
         <v>137</v>
       </c>
       <c r="B138" t="str">
-        <v>Hindustan Unilever Limited</v>
+        <v>Tube Investments of India Ltd</v>
       </c>
       <c r="C138" t="str">
-        <v>HINDUNILVR</v>
+        <v>TIINDIA</v>
       </c>
       <c r="D138" s="1">
-        <v>1838.5</v>
+        <v>2194.9</v>
       </c>
       <c r="E138" s="2">
-        <v>-0.98</v>
+        <v>-0.86</v>
       </c>
       <c r="F138" s="1">
-        <v>309075</v>
-      </c>
-      <c r="G138" t="str">
+        <v>1198038</v>
+      </c>
+      <c r="G138" s="1">
+        <v>2727.54</v>
+      </c>
+      <c r="H138" s="1">
+        <v>2314</v>
+      </c>
+      <c r="I138" s="1">
+        <v>2645.09</v>
+      </c>
+      <c r="J138" t="str">
         <v/>
       </c>
     </row>
@@ -3582,21 +4824,30 @@
         <v>138</v>
       </c>
       <c r="B139" t="str">
-        <v>Canara Bank Ltd</v>
+        <v>Hindustan Petroleum Corporation Limited</v>
       </c>
       <c r="C139" t="str">
-        <v>CANBK</v>
+        <v>HINDPETRO</v>
       </c>
       <c r="D139" s="1">
-        <v>118.35</v>
+        <v>329</v>
       </c>
       <c r="E139" s="2">
-        <v>-1.04</v>
+        <v>-0.98</v>
       </c>
       <c r="F139" s="1">
-        <v>3711831</v>
-      </c>
-      <c r="G139" t="str">
+        <v>4139045</v>
+      </c>
+      <c r="G139" s="1">
+        <v>393.41</v>
+      </c>
+      <c r="H139" s="1">
+        <v>337.47</v>
+      </c>
+      <c r="I139" s="1">
+        <v>361.61</v>
+      </c>
+      <c r="J139" t="str">
         <v/>
       </c>
     </row>
@@ -3605,21 +4856,30 @@
         <v>139</v>
       </c>
       <c r="B140" t="str">
-        <v>Indus Towers Ltd (Bharti Infratel)</v>
+        <v>Polycab India Ltd</v>
       </c>
       <c r="C140" t="str">
-        <v>INDUSTOWER</v>
+        <v>POLYCAB</v>
       </c>
       <c r="D140" s="1">
-        <v>376.7</v>
+        <v>8290</v>
       </c>
       <c r="E140" s="2">
-        <v>-1.09</v>
+        <v>-1.37</v>
       </c>
       <c r="F140" s="1">
-        <v>974392</v>
-      </c>
-      <c r="G140" t="str">
+        <v>794593</v>
+      </c>
+      <c r="G140" s="1">
+        <v>8414.8</v>
+      </c>
+      <c r="H140" s="1">
+        <v>8248.4</v>
+      </c>
+      <c r="I140" s="1">
+        <v>8677.2</v>
+      </c>
+      <c r="J140" t="str">
         <v/>
       </c>
     </row>
@@ -3628,21 +4888,30 @@
         <v>140</v>
       </c>
       <c r="B141" t="str">
-        <v>Bank Of India Ltd</v>
+        <v>Jsw Energy Limited</v>
       </c>
       <c r="C141" t="str">
-        <v>BANKINDIA</v>
+        <v>JSWENERGY</v>
       </c>
       <c r="D141" s="1">
-        <v>132.75</v>
+        <v>460.5</v>
       </c>
       <c r="E141" s="2">
-        <v>-1.27</v>
+        <v>-1.47</v>
       </c>
       <c r="F141" s="1">
-        <v>2947517</v>
-      </c>
-      <c r="G141" t="str">
+        <v>2668808</v>
+      </c>
+      <c r="G141" s="1">
+        <v>523.22</v>
+      </c>
+      <c r="H141" s="1">
+        <v>478.97</v>
+      </c>
+      <c r="I141" s="1">
+        <v>526.54</v>
+      </c>
+      <c r="J141" t="str">
         <v/>
       </c>
     </row>
@@ -3651,21 +4920,30 @@
         <v>141</v>
       </c>
       <c r="B142" t="str">
-        <v>Dabur India Limited</v>
+        <v>Vedanta Limited</v>
       </c>
       <c r="C142" t="str">
-        <v>DABUR</v>
+        <v>VEDL</v>
       </c>
       <c r="D142" s="1">
-        <v>381.45</v>
+        <v>256.3</v>
       </c>
       <c r="E142" s="2">
-        <v>-1.36</v>
+        <v>-3.25</v>
       </c>
       <c r="F142" s="1">
-        <v>194550</v>
-      </c>
-      <c r="G142" t="str">
+        <v>18840262</v>
+      </c>
+      <c r="G142" s="1">
+        <v>268.53</v>
+      </c>
+      <c r="H142" s="1">
+        <v>260.29</v>
+      </c>
+      <c r="I142" s="1">
+        <v>268.37</v>
+      </c>
+      <c r="J142" t="str">
         <v/>
       </c>
     </row>
@@ -3674,188 +4952,36 @@
         <v>142</v>
       </c>
       <c r="B143" t="str">
-        <v>Union Bank Of India Ltd</v>
+        <v>Icici Prudential Life Insurance Company Limited</v>
       </c>
       <c r="C143" t="str">
-        <v>UNIONBANK</v>
+        <v>ICICIPRULI</v>
       </c>
       <c r="D143" s="1">
-        <v>170.7</v>
+        <v>447</v>
       </c>
       <c r="E143" s="2">
-        <v>-1.36</v>
+        <v>-3.54</v>
       </c>
       <c r="F143" s="1">
-        <v>2101493</v>
-      </c>
-      <c r="G143" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144">
-        <v>143</v>
-      </c>
-      <c r="B144" t="str">
-        <v>Ntpc Limited</v>
-      </c>
-      <c r="C144" t="str">
-        <v>NTPC</v>
-      </c>
-      <c r="D144" s="1">
-        <v>307.4</v>
-      </c>
-      <c r="E144" s="2">
-        <v>-1.47</v>
-      </c>
-      <c r="F144" s="1">
-        <v>3661773</v>
-      </c>
-      <c r="G144" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145">
-        <v>144</v>
-      </c>
-      <c r="B145" t="str">
-        <v>Bharti Airtel Limited</v>
-      </c>
-      <c r="C145" t="str">
-        <v>BHARTIARTL</v>
-      </c>
-      <c r="D145" s="1">
-        <v>1773.1</v>
-      </c>
-      <c r="E145" s="2">
-        <v>-1.77</v>
-      </c>
-      <c r="F145" s="1">
-        <v>2055425</v>
-      </c>
-      <c r="G145" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146">
-        <v>145</v>
-      </c>
-      <c r="B146" t="str">
-        <v>State Bank Of India Ltd</v>
-      </c>
-      <c r="C146" t="str">
-        <v>SBIN</v>
-      </c>
-      <c r="D146" s="1">
-        <v>940.9</v>
-      </c>
-      <c r="E146" s="2">
-        <v>-1.9</v>
-      </c>
-      <c r="F146" s="1">
-        <v>2453218</v>
-      </c>
-      <c r="G146" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147">
-        <v>146</v>
-      </c>
-      <c r="B147" t="str">
-        <v>Itc Limited</v>
-      </c>
-      <c r="C147" t="str">
-        <v>ITC</v>
-      </c>
-      <c r="D147" s="1">
-        <v>259.95</v>
-      </c>
-      <c r="E147" s="2">
-        <v>-2.27</v>
-      </c>
-      <c r="F147" s="1">
-        <v>4721248</v>
-      </c>
-      <c r="G147" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148">
-        <v>147</v>
-      </c>
-      <c r="B148" t="str">
-        <v>GMR Airports Ltd</v>
-      </c>
-      <c r="C148" t="str">
-        <v>GMRAIRPORT</v>
-      </c>
-      <c r="D148" s="1">
-        <v>90.17</v>
-      </c>
-      <c r="E148" s="2">
-        <v>-2.32</v>
-      </c>
-      <c r="F148" s="1">
-        <v>5233987</v>
-      </c>
-      <c r="G148" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149">
-        <v>148</v>
-      </c>
-      <c r="B149" t="str">
-        <v>Avenue Supermarts Ltd</v>
-      </c>
-      <c r="C149" t="str">
-        <v>DMART</v>
-      </c>
-      <c r="D149" s="1">
-        <v>3417.4</v>
-      </c>
-      <c r="E149" s="2">
-        <v>-2.83</v>
-      </c>
-      <c r="F149" s="1">
-        <v>1605429</v>
-      </c>
-      <c r="G149" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150">
-        <v>149</v>
-      </c>
-      <c r="B150" t="str">
-        <v>Tech Mahindra Limited</v>
-      </c>
-      <c r="C150" t="str">
-        <v>TECHM</v>
-      </c>
-      <c r="D150" s="1">
-        <v>1464.3</v>
-      </c>
-      <c r="E150" s="2">
-        <v>-3.29</v>
-      </c>
-      <c r="F150" s="1">
-        <v>1966286</v>
-      </c>
-      <c r="G150" t="str">
+        <v>3038743</v>
+      </c>
+      <c r="G143" s="1">
+        <v>547.23</v>
+      </c>
+      <c r="H143" s="1">
+        <v>457.67</v>
+      </c>
+      <c r="I143" s="1">
+        <v>486.03</v>
+      </c>
+      <c r="J143" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G150"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J143"/>
   </ignoredErrors>
 </worksheet>
 </file>